--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97DCBCFB-9C15-4321-B5A6-A85044340A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3119CA1F-3E65-4CA1-B7D3-A73F8E7A09A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>N° déclaration</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>MARIA CELIS 4</t>
+  </si>
+  <si>
+    <t>LA DIOSA</t>
   </si>
   <si>
     <t xml:space="preserve">compagnie </t>
@@ -3861,19 +3864,29 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="10"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="10"/>
+      <c r="A15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{E2910900-9C30-4A18-9496-476E3FB8CC0C}">
       <formula1>"DSK Fish,Poissonnerie Bapte,Delta Transit"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{33C8A05D-5FBB-4930-9B27-20DC68C9FA09}">
-      <formula1>"PATHFINDER,NATHALIA,SAMANTHA DEL VALLEE,ARACELYS MARIA,EL SUR,DON CRUZ,QUEEN MARY,MARIA CELIS 3,MARIA CELIS 2,MARIA CELIS 4,MAYELEWO,EL SUR,DON FAUSTINO"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{9CBFDF41-04DC-4A2C-BFA5-AF229712E91E}">
+      <formula1>"LA DIOSA,PATHFINDER,NATHALIA,SAMANTHA DEL VALLEE,ARACELYS MARIA,EL SUR,DON CRUZ,QUEEN MARY,MARIA CELIS 3,MARIA CELIS 2,MARIA CELIS 4,MAYELEWO,EL SUR,DON FAUSTINO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3894,10 +3907,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3905,7 +3918,7 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" t="str">
         <f>IF(C2&lt;&gt;"",VLOOKUP(C2,Tableau3[#All],2,0),"")</f>
@@ -3917,15 +3930,15 @@
         <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3119CA1F-3E65-4CA1-B7D3-A73F8E7A09A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A394730-F30C-4727-B25F-326997BBEBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Déclaration" sheetId="1" r:id="rId1"/>
+    <sheet name="Declaration" sheetId="1" r:id="rId1"/>
     <sheet name="Caractéristique navire de pêche" sheetId="2" r:id="rId2"/>
     <sheet name="adresse" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -58,10 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
-  <si>
-    <t>N° déclaration</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
   <si>
     <t xml:space="preserve">Mouvement </t>
   </si>
@@ -72,9 +69,6 @@
     <t>Adresse du représentant</t>
   </si>
   <si>
-    <t xml:space="preserve">Pavillon </t>
-  </si>
-  <si>
     <t>Type du navire</t>
   </si>
   <si>
@@ -145,6 +139,9 @@
   </si>
   <si>
     <t>MAYELEWO</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">Compagnie </t>
@@ -644,18 +641,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75829E64-7FC7-4469-8A2D-196525EA991A}" name="Tableau1" displayName="Tableau1" ref="A1:Z38" totalsRowShown="0">
-  <autoFilter ref="A1:Z38" xr:uid="{75829E64-7FC7-4469-8A2D-196525EA991A}"/>
-  <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{B328C68C-5511-47DB-B841-C107245E021F}" name="N° déclaration"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{75829E64-7FC7-4469-8A2D-196525EA991A}" name="Tableau1" displayName="Tableau1" ref="A1:X38" totalsRowShown="0">
+  <autoFilter ref="A1:X38" xr:uid="{75829E64-7FC7-4469-8A2D-196525EA991A}"/>
+  <tableColumns count="24">
     <tableColumn id="7" xr3:uid="{6A803017-4A30-4ADA-B61F-E42074DA2DF4}" name="Mouvement "/>
     <tableColumn id="23" xr3:uid="{93CE2DE0-7C7A-45E1-9724-3207DB2CDB4E}" name="Représentant "/>
     <tableColumn id="22" xr3:uid="{D4BA7D87-6CE6-4C6A-A3E8-963A5AD6FC1A}" name="Adresse du représentant" dataDxfId="25">
-      <calculatedColumnFormula>IF(C2&lt;&gt;"",VLOOKUP(C2,Tableau3[#All],2,0),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(B2&lt;&gt;"",VLOOKUP(B2,Tableau3[#All],2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{4B28227A-132A-44FD-9835-775F0DD488A9}" name="Pavillon "/>
     <tableColumn id="26" xr3:uid="{075FFC9A-0866-419D-AD20-3E7FE0C81DB8}" name="Type du navire" dataDxfId="24">
-      <calculatedColumnFormula>IF(C2&lt;&gt;"","13","")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(B2&lt;&gt;"","13","")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CE31803F-2A93-4154-A7E1-1A9EEC6F3680}" name="Nom du navire"/>
     <tableColumn id="3" xr3:uid="{ACA56DAA-7AE0-43C8-A191-5A1E50CC1777}" name="Date d'entrée"/>
@@ -664,46 +659,44 @@
     <tableColumn id="6" xr3:uid="{622D6CD9-FD42-4F06-A785-55691B48DE2F}" name="Zone DN"/>
     <tableColumn id="8" xr3:uid="{341457F8-4F04-40E8-9537-3EC8F4C746B2}" name="Tonnage"/>
     <tableColumn id="12" xr3:uid="{F62FADB5-4870-4A15-9554-1C372B4A4B20}" name="Largueur " dataDxfId="21">
-      <calculatedColumnFormula>IF(G2&lt;&gt;"",VLOOKUP(G2,'Caractéristique navire de pêche'!$B:$E,3,0),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(E2&lt;&gt;"",VLOOKUP(E2,'Caractéristique navire de pêche'!$B:$E,3,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{2927ADB3-96F0-4BE1-9A79-C990B0CDAE7F}" name="Longueur " dataDxfId="20">
-      <calculatedColumnFormula>IF(G2&lt;&gt;"",VLOOKUP(G2,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="13" xr3:uid="{2927ADB3-96F0-4BE1-9A79-C990B0CDAE7F}" name="Longueur " dataDxfId="20"/>
     <tableColumn id="11" xr3:uid="{EC156DA3-0E82-4235-9B4A-22111E6FA722}" name="Tirant d'eau " dataDxfId="19">
-      <calculatedColumnFormula>IF(G2&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(E2&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{E235AE5E-5CC0-4585-9C97-1A0132BF1A07}" name="Volumme Taxable " dataDxfId="18">
-      <calculatedColumnFormula>IF(AND(M2&lt;&gt;"",N2&lt;&gt;"",O2&lt;&gt;""),ROUNDUP(N2*M2*O2,0),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(AND(K2&lt;&gt;"",L2&lt;&gt;"",M2&lt;&gt;""),ROUNDUP(L2*K2*M2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{C0833D6E-2308-40FA-AD74-2CA2B2ABDF2C}" name="Taux de base" dataDxfId="17">
-      <calculatedColumnFormula>IF(B2&lt;&gt;"",IF(B2="Entrée",0.366,0.228),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(A2&lt;&gt;"",IF(A2="Entrée",0.366,0.228),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{F66A31B8-5F27-4063-8944-FDBC1C894FB8}" name="Redevance Navire" dataDxfId="16">
-      <calculatedColumnFormula>IF(AND(P2&lt;&gt;"",Q2&lt;&gt;""),ROUNDUP(P2*Q2,2),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(AND(N2&lt;&gt;"",O2&lt;&gt;""),ROUNDUP(N2*O2,2),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{A5F8D501-9036-4F46-9EAA-6E8739664B7C}" name="Modulation non cummulable (4)" dataDxfId="15">
-      <calculatedColumnFormula>IF(AND(L2&lt;&gt;"",P2&lt;&gt;""),IF(L2/P2&gt;2/15,0,IF(L2/P2&gt;1/10,-0.1,IF(L2/P2&gt;1/20,-0.3,IF(L2/P2&gt;1/40,-0.5,IF(L2/P2&gt;1/100,-0.6,IF(L2/P2&gt;1/250,-0.7,IF(L2/P2&gt;1/500,-0.8,-0.95))))))),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(AND(J2&lt;&gt;"",N2&lt;&gt;""),IF(J2/N2&gt;2/15,0,IF(J2/N2&gt;1/10,-0.1,IF(J2/N2&gt;1/20,-0.3,IF(J2/N2&gt;1/40,-0.5,IF(J2/N2&gt;1/100,-0.6,IF(J2/N2&gt;1/250,-0.7,IF(J2/N2&gt;1/500,-0.8,-0.95))))))),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="25" xr3:uid="{1254D2F4-AB89-41BD-B0D2-E1438C929EC7}" name="Abattement de fréquence " dataDxfId="14">
-      <calculatedColumnFormula array="1">IF(G2&lt;&gt;"",IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(Q:QH2),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(H2),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(H2),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(H2),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(H2),12,31))&lt;=120,-0.25,-0.3))))),"")</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">IF(E2&lt;&gt;"",IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(Q:QF2),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=120,-0.25,-0.3))))),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{31494260-798A-4AE8-90D6-75F1191C334B}" name="Modulation cummulable (3)" dataDxfId="13">
-      <calculatedColumnFormula>IF(G2&lt;&gt;"",0,"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(E2&lt;&gt;"",0,"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{A421E24A-9428-4D77-A32C-2534ADDB3299}" name="Redevance déchets" dataDxfId="12">
-      <calculatedColumnFormula>IF(AND(G2&lt;&gt;"",B2="Entrée"),65,"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(AND(E2&lt;&gt;"",A2="Entrée"),65,"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{78149C42-BFEE-45D3-BBAA-4327918E2439}" name="Montant Brut" dataDxfId="11">
-      <calculatedColumnFormula>IF(AND(R2&lt;&gt;"",S2&lt;&gt;""),ROUNDUP(R2*(1+S2),2),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(AND(P2&lt;&gt;"",Q2&lt;&gt;""),ROUNDUP(P2*(1+Q2),2),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{3EA6394C-380A-40DC-BDA4-599FB7FBCDF6}" name="Montant Net" dataDxfId="10">
-      <calculatedColumnFormula>IF(W2&lt;&gt;"",W2+V2,"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(U2&lt;&gt;"",U2+T2,"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="20" xr3:uid="{41AF65D6-37C3-4266-B518-CBAFEB68966A}" name="Montant à percevoir " dataDxfId="9">
-      <calculatedColumnFormula>IF(X2&lt;&gt;"",IF(X2&lt;9,0,IF(X2&lt;=16,16,X2)),"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(V2&lt;&gt;"",IF(V2&lt;9,0,IF(V2&lt;=16,16,V2)),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="21" xr3:uid="{20F59A93-CE99-45BF-AAF7-8DAC383C7A12}" name="Montant Final" dataDxfId="8">
-      <calculatedColumnFormula>IF(Y2&lt;&gt;"",Y2,"")</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(W2&lt;&gt;"",W2,"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1032,37 +1025,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z38"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="48.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="32" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32" customWidth="1"/>
-    <col min="21" max="21" width="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="48.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32" customWidth="1"/>
+    <col min="19" max="19" width="28" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75">
+    <row r="1" spans="1:24" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1099,22 +1090,22 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
@@ -1123,2488 +1114,2447 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
-      <c r="B2" t="s">
+      <c r="C2" t="str">
+        <f>IF(B2&lt;&gt;"",VLOOKUP(B2,Tableau3[#All],2,0),"")</f>
+        <v>53 AVENUE DES ARAWAKS, 97200 FORT DE FRANCE.</v>
+      </c>
+      <c r="D2" t="str">
+        <f t="shared" ref="D2:D38" si="0">IF(B2&lt;&gt;"","13","")</f>
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
+      <c r="J2">
+        <v>2.6840000000000002</v>
+      </c>
+      <c r="K2">
+        <f>IF(E2&lt;&gt;"",VLOOKUP(E2,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="L2">
+        <f>IF(E2&lt;&gt;"",VLOOKUP(E2,'Caractéristique navire de pêche'!$B:$E,2,0),"")</f>
+        <v>14.5</v>
+      </c>
+      <c r="M2">
+        <f>IF(E2&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E2,'Caractéristique navire de pêche'!$B:$E,4,0),_xlpm.longueur,VLOOKUP(E2,'Caractéristique navire de pêche'!$B:$E,2,0),_xlpm.largeur,VLOOKUP(E2,'Caractéristique navire de pêche'!$B:$E,3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v>1.8</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:N38" si="1">IF(AND(K2&lt;&gt;"",L2&lt;&gt;"",M2&lt;&gt;""),ROUNDUP(L2*K2*M2,0),"")</f>
+        <v>115</v>
+      </c>
+      <c r="O2">
+        <f>IF(A2&lt;&gt;"",IF(A2="Entrée",0.366,0.228),"")</f>
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="P2">
+        <f t="shared" ref="P2:P38" si="2">IF(AND(N2&lt;&gt;"",O2&lt;&gt;""),ROUNDUP(N2*O2,2),"")</f>
+        <v>42.09</v>
+      </c>
+      <c r="Q2">
+        <f>IF(AND(J2&lt;&gt;"",N2&lt;&gt;""),IF(J2/N2&gt;2/15,0,IF(J2/N2&gt;1/10,-0.1,IF(J2/N2&gt;1/20,-0.3,IF(J2/N2&gt;1/40,-0.5,IF(J2/N2&gt;1/100,-0.6,IF(J2/N2&gt;1/250,-0.7,IF(J2/N2&gt;1/500,-0.8,-0.95))))))),"")</f>
+        <v>-0.6</v>
+      </c>
+      <c r="R2" cm="1">
+        <f t="array" aca="1" ref="R2" ca="1">IF(E2&lt;&gt;"",IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(Q:QF2),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>IF(E2&lt;&gt;"",0,"")</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>IF(AND(E2&lt;&gt;"",A2="Entrée"),65,"")</f>
+        <v>65</v>
+      </c>
+      <c r="U2">
+        <f t="shared" ref="U2:U38" si="3">IF(AND(P2&lt;&gt;"",Q2&lt;&gt;""),ROUNDUP(P2*(1+Q2),2),"")</f>
+        <v>16.84</v>
+      </c>
+      <c r="V2">
+        <f t="shared" ref="V2:V38" si="4">IF(U2&lt;&gt;"",U2+T2,"")</f>
+        <v>81.84</v>
+      </c>
+      <c r="W2">
+        <f t="shared" ref="W2:W38" si="5">IF(V2&lt;&gt;"",IF(V2&lt;9,0,IF(V2&lt;=16,16,V2)),"")</f>
+        <v>81.84</v>
+      </c>
+      <c r="X2">
+        <f t="shared" ref="X2:X38" si="6">IF(W2&lt;&gt;"",W2,"")</f>
+        <v>81.84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="C3" t="str">
+        <f>IF(B3&lt;&gt;"",VLOOKUP(B3,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <f>IF(E3&lt;&gt;"",VLOOKUP(E3,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <f>IF(E3&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E3,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E3,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E3,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <f>IF(A3&lt;&gt;"",IF(A3="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q38" si="7">IF(AND(J3&lt;&gt;"",N3&lt;&gt;""),IF(J3/N3&gt;2/15,0,IF(J3/N3&gt;1/10,-0.1,IF(J3/N3&gt;1/20,-0.3,IF(J3/N3&gt;1/40,-0.5,IF(J3/N3&gt;1/100,-0.6,IF(J3/N3&gt;1/250,-0.7,IF(J3/N3&gt;1/500,-0.8,-0.95))))))),"")</f>
+        <v/>
+      </c>
+      <c r="R3" t="str" cm="1">
+        <f t="array" ref="R3">IF(E3&lt;&gt;"",IF(COUNTIFS($E$2:E3,E3,$F$2:F3,"&gt;="&amp;DATE(YEAR(F3),1,1),$F$2:F3,"&lt;="&amp;DATE(YEAR(Q:QF3),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E3,E3,$F$2:F3,"&gt;="&amp;DATE(YEAR(F3),1,1),$F$2:F3,"&lt;="&amp;DATE(YEAR(F3),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E3,E3,$F$2:F3,"&gt;="&amp;DATE(YEAR(F3),1,1),$F$2:F3,"&lt;="&amp;DATE(YEAR(F3),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E3,E3,$F$2:F3,"&gt;="&amp;DATE(YEAR(F3),1,1),$F$2:F3,"&lt;="&amp;DATE(YEAR(F3),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E3,E3,$F$2:F3,"&gt;="&amp;DATE(YEAR(F3),1,1),$F$2:F3,"&lt;="&amp;DATE(YEAR(F3),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <f>IF(E3&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <f>IF(AND(E3&lt;&gt;"",A3="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="C4" t="str">
+        <f>IF(B4&lt;&gt;"",VLOOKUP(B4,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <f>IF(E4&lt;&gt;"",VLOOKUP(E4,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L4" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="str">
-        <f>IF(C2&lt;&gt;"",VLOOKUP(C2,Tableau3[#All],2,0),"")</f>
-        <v>53 AVENUE DES ARAWAKS, 97200 FORT DE FRANCE.</v>
-      </c>
-      <c r="F2" t="str">
-        <f t="shared" ref="F2:F38" si="0">IF(C2&lt;&gt;"","13","")</f>
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2">
-        <v>2.6840000000000002</v>
-      </c>
-      <c r="M2">
-        <f>IF(G2&lt;&gt;"",VLOOKUP(G2,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="N2">
-        <f>IF(G2&lt;&gt;"",VLOOKUP(G2,'Caractéristique navire de pêche'!$B:$E,2,0),"")</f>
-        <v>14.5</v>
-      </c>
-      <c r="O2">
-        <f>IF(G2&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G2,'Caractéristique navire de pêche'!$B:$E,4,0),_xlpm.longueur,VLOOKUP(G2,'Caractéristique navire de pêche'!$B:$E,2,0),_xlpm.largeur,VLOOKUP(G2,'Caractéristique navire de pêche'!$B:$E,3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v>1.8</v>
-      </c>
-      <c r="P2">
-        <f t="shared" ref="P2:P38" si="1">IF(AND(M2&lt;&gt;"",N2&lt;&gt;"",O2&lt;&gt;""),ROUNDUP(N2*M2*O2,0),"")</f>
-        <v>115</v>
-      </c>
-      <c r="Q2">
-        <f>IF(B2&lt;&gt;"",IF(B2="Entrée",0.366,0.228),"")</f>
-        <v>0.36599999999999999</v>
-      </c>
-      <c r="R2">
-        <f t="shared" ref="R2:R38" si="2">IF(AND(P2&lt;&gt;"",Q2&lt;&gt;""),ROUNDUP(P2*Q2,2),"")</f>
-        <v>42.09</v>
-      </c>
-      <c r="S2">
-        <f>IF(AND(L2&lt;&gt;"",P2&lt;&gt;""),IF(L2/P2&gt;2/15,0,IF(L2/P2&gt;1/10,-0.1,IF(L2/P2&gt;1/20,-0.3,IF(L2/P2&gt;1/40,-0.5,IF(L2/P2&gt;1/100,-0.6,IF(L2/P2&gt;1/250,-0.7,IF(L2/P2&gt;1/500,-0.8,-0.95))))))),"")</f>
-        <v>-0.6</v>
-      </c>
-      <c r="T2" cm="1">
-        <f t="array" aca="1" ref="T2" ca="1">IF(G2&lt;&gt;"",IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(Q:QH2),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(H2),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(H2),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(H2),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G2,G2,$H$2:H2,"&gt;="&amp;DATE(YEAR(H2),1,1),$H$2:H2,"&lt;="&amp;DATE(YEAR(H2),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <f>IF(G2&lt;&gt;"",0,"")</f>
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <f>IF(AND(G2&lt;&gt;"",B2="Entrée"),65,"")</f>
-        <v>65</v>
-      </c>
-      <c r="W2">
-        <f t="shared" ref="W2:W38" si="3">IF(AND(R2&lt;&gt;"",S2&lt;&gt;""),ROUNDUP(R2*(1+S2),2),"")</f>
-        <v>16.84</v>
-      </c>
-      <c r="X2">
-        <f t="shared" ref="X2:X38" si="4">IF(W2&lt;&gt;"",W2+V2,"")</f>
-        <v>81.84</v>
-      </c>
-      <c r="Y2">
-        <f t="shared" ref="Y2:Y38" si="5">IF(X2&lt;&gt;"",IF(X2&lt;9,0,IF(X2&lt;=16,16,X2)),"")</f>
-        <v>81.84</v>
-      </c>
-      <c r="Z2">
-        <f t="shared" ref="Z2:Z38" si="6">IF(Y2&lt;&gt;"",Y2,"")</f>
-        <v>81.84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26">
-      <c r="D3" t="str">
-        <f>IF(C3&lt;&gt;"",VLOOKUP(C3,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F3" t="str">
+      <c r="M4" t="str">
+        <f>IF(E4&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E4,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E4,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E4,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <f>IF(A4&lt;&gt;"",IF(A4="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="R4" t="str" cm="1">
+        <f t="array" ref="R4">IF(E4&lt;&gt;"",IF(COUNTIFS($E$2:E4,E4,$F$2:F4,"&gt;="&amp;DATE(YEAR(F4),1,1),$F$2:F4,"&lt;="&amp;DATE(YEAR(Q:QF4),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E4,E4,$F$2:F4,"&gt;="&amp;DATE(YEAR(F4),1,1),$F$2:F4,"&lt;="&amp;DATE(YEAR(F4),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E4,E4,$F$2:F4,"&gt;="&amp;DATE(YEAR(F4),1,1),$F$2:F4,"&lt;="&amp;DATE(YEAR(F4),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E4,E4,$F$2:F4,"&gt;="&amp;DATE(YEAR(F4),1,1),$F$2:F4,"&lt;="&amp;DATE(YEAR(F4),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E4,E4,$F$2:F4,"&gt;="&amp;DATE(YEAR(F4),1,1),$F$2:F4,"&lt;="&amp;DATE(YEAR(F4),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <f>IF(E4&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <f>IF(AND(E4&lt;&gt;"",A4="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="C5" t="str">
+        <f>IF(B5&lt;&gt;"",VLOOKUP(B5,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M3" t="str">
-        <f>IF(G3&lt;&gt;"",VLOOKUP(G3,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <f>IF(G3&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G3,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G3,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G3,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P3" t="str">
+      <c r="K5" t="str">
+        <f>IF(E5&lt;&gt;"",VLOOKUP(E5,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="str">
+        <f>IF(E5&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E5,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E5,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E5,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q3" t="str">
-        <f>IF(B3&lt;&gt;"",IF(B3="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R3" t="str">
+      <c r="O5" t="str">
+        <f>IF(A5&lt;&gt;"",IF(A5="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S3" t="str">
-        <f t="shared" ref="S3:S38" si="7">IF(AND(L3&lt;&gt;"",P3&lt;&gt;""),IF(L3/P3&gt;2/15,0,IF(L3/P3&gt;1/10,-0.1,IF(L3/P3&gt;1/20,-0.3,IF(L3/P3&gt;1/40,-0.5,IF(L3/P3&gt;1/100,-0.6,IF(L3/P3&gt;1/250,-0.7,IF(L3/P3&gt;1/500,-0.8,-0.95))))))),"")</f>
-        <v/>
-      </c>
-      <c r="T3" t="str" cm="1">
-        <f t="array" ref="T3">IF(G3&lt;&gt;"",IF(COUNTIFS($G$2:G3,G3,$H$2:H3,"&gt;="&amp;DATE(YEAR(H3),1,1),$H$2:H3,"&lt;="&amp;DATE(YEAR(Q:QH3),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G3,G3,$H$2:H3,"&gt;="&amp;DATE(YEAR(H3),1,1),$H$2:H3,"&lt;="&amp;DATE(YEAR(H3),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G3,G3,$H$2:H3,"&gt;="&amp;DATE(YEAR(H3),1,1),$H$2:H3,"&lt;="&amp;DATE(YEAR(H3),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G3,G3,$H$2:H3,"&gt;="&amp;DATE(YEAR(H3),1,1),$H$2:H3,"&lt;="&amp;DATE(YEAR(H3),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G3,G3,$H$2:H3,"&gt;="&amp;DATE(YEAR(H3),1,1),$H$2:H3,"&lt;="&amp;DATE(YEAR(H3),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U3" t="str">
-        <f>IF(G3&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V3" t="str">
-        <f>IF(AND(G3&lt;&gt;"",B3="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W3" t="str">
+      <c r="Q5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="R5" t="str" cm="1">
+        <f t="array" ref="R5">IF(E5&lt;&gt;"",IF(COUNTIFS($E$2:E5,E5,$F$2:F5,"&gt;="&amp;DATE(YEAR(F5),1,1),$F$2:F5,"&lt;="&amp;DATE(YEAR(Q:QF5),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E5,E5,$F$2:F5,"&gt;="&amp;DATE(YEAR(F5),1,1),$F$2:F5,"&lt;="&amp;DATE(YEAR(F5),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E5,E5,$F$2:F5,"&gt;="&amp;DATE(YEAR(F5),1,1),$F$2:F5,"&lt;="&amp;DATE(YEAR(F5),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E5,E5,$F$2:F5,"&gt;="&amp;DATE(YEAR(F5),1,1),$F$2:F5,"&lt;="&amp;DATE(YEAR(F5),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E5,E5,$F$2:F5,"&gt;="&amp;DATE(YEAR(F5),1,1),$F$2:F5,"&lt;="&amp;DATE(YEAR(F5),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <f>IF(E5&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <f>IF(AND(E5&lt;&gt;"",A5="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X3" t="str">
+      <c r="V5" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y3" t="str">
+      <c r="W5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z3" t="str">
+      <c r="X5" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:26">
-      <c r="D4" t="str">
-        <f>IF(C4&lt;&gt;"",VLOOKUP(C4,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F4" t="str">
+    <row r="6" spans="1:24">
+      <c r="C6" t="str">
+        <f>IF(B6&lt;&gt;"",VLOOKUP(B6,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M4" t="str">
-        <f>IF(G4&lt;&gt;"",VLOOKUP(G4,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <f>IF(G4&lt;&gt;"",VLOOKUP(G4,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <f>IF(G4&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G4,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G4,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G4,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P4" t="str">
+      <c r="K6" t="str">
+        <f>IF(E6&lt;&gt;"",VLOOKUP(E6,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="str">
+        <f>IF(E6&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E6,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E6,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E6,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q4" t="str">
-        <f>IF(B4&lt;&gt;"",IF(B4="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R4" t="str">
+      <c r="O6" t="str">
+        <f>IF(A6&lt;&gt;"",IF(A6="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S4" t="str">
+      <c r="Q6" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T4" t="str" cm="1">
-        <f t="array" ref="T4">IF(G4&lt;&gt;"",IF(COUNTIFS($G$2:G4,G4,$H$2:H4,"&gt;="&amp;DATE(YEAR(H4),1,1),$H$2:H4,"&lt;="&amp;DATE(YEAR(Q:QH4),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G4,G4,$H$2:H4,"&gt;="&amp;DATE(YEAR(H4),1,1),$H$2:H4,"&lt;="&amp;DATE(YEAR(H4),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G4,G4,$H$2:H4,"&gt;="&amp;DATE(YEAR(H4),1,1),$H$2:H4,"&lt;="&amp;DATE(YEAR(H4),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G4,G4,$H$2:H4,"&gt;="&amp;DATE(YEAR(H4),1,1),$H$2:H4,"&lt;="&amp;DATE(YEAR(H4),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G4,G4,$H$2:H4,"&gt;="&amp;DATE(YEAR(H4),1,1),$H$2:H4,"&lt;="&amp;DATE(YEAR(H4),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U4" t="str">
-        <f>IF(G4&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V4" t="str">
-        <f>IF(AND(G4&lt;&gt;"",B4="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W4" t="str">
+      <c r="R6" t="str" cm="1">
+        <f t="array" ref="R6">IF(E6&lt;&gt;"",IF(COUNTIFS($E$2:E6,E6,$F$2:F6,"&gt;="&amp;DATE(YEAR(F6),1,1),$F$2:F6,"&lt;="&amp;DATE(YEAR(Q:QF6),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E6,E6,$F$2:F6,"&gt;="&amp;DATE(YEAR(F6),1,1),$F$2:F6,"&lt;="&amp;DATE(YEAR(F6),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E6,E6,$F$2:F6,"&gt;="&amp;DATE(YEAR(F6),1,1),$F$2:F6,"&lt;="&amp;DATE(YEAR(F6),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E6,E6,$F$2:F6,"&gt;="&amp;DATE(YEAR(F6),1,1),$F$2:F6,"&lt;="&amp;DATE(YEAR(F6),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E6,E6,$F$2:F6,"&gt;="&amp;DATE(YEAR(F6),1,1),$F$2:F6,"&lt;="&amp;DATE(YEAR(F6),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <f>IF(E6&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <f>IF(AND(E6&lt;&gt;"",A6="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U6" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X4" t="str">
+      <c r="V6" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y4" t="str">
+      <c r="W6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z4" t="str">
+      <c r="X6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:26">
-      <c r="D5" t="str">
-        <f>IF(C5&lt;&gt;"",VLOOKUP(C5,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F5" t="str">
+    <row r="7" spans="1:24">
+      <c r="C7" t="str">
+        <f>IF(B7&lt;&gt;"",VLOOKUP(B7,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M5" t="str">
-        <f>IF(G5&lt;&gt;"",VLOOKUP(G5,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <f>IF(G5&lt;&gt;"",VLOOKUP(G5,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <f>IF(G5&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G5,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G5,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G5,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P5" t="str">
+      <c r="K7" t="str">
+        <f>IF(E7&lt;&gt;"",VLOOKUP(E7,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" t="str">
+        <f>IF(E7&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E7,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E7,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E7,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q5" t="str">
-        <f>IF(B5&lt;&gt;"",IF(B5="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R5" t="str">
+      <c r="O7" t="str">
+        <f>IF(A7&lt;&gt;"",IF(A7="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S5" t="str">
+      <c r="Q7" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T5" t="str" cm="1">
-        <f t="array" ref="T5">IF(G5&lt;&gt;"",IF(COUNTIFS($G$2:G5,G5,$H$2:H5,"&gt;="&amp;DATE(YEAR(H5),1,1),$H$2:H5,"&lt;="&amp;DATE(YEAR(Q:QH5),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G5,G5,$H$2:H5,"&gt;="&amp;DATE(YEAR(H5),1,1),$H$2:H5,"&lt;="&amp;DATE(YEAR(H5),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G5,G5,$H$2:H5,"&gt;="&amp;DATE(YEAR(H5),1,1),$H$2:H5,"&lt;="&amp;DATE(YEAR(H5),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G5,G5,$H$2:H5,"&gt;="&amp;DATE(YEAR(H5),1,1),$H$2:H5,"&lt;="&amp;DATE(YEAR(H5),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G5,G5,$H$2:H5,"&gt;="&amp;DATE(YEAR(H5),1,1),$H$2:H5,"&lt;="&amp;DATE(YEAR(H5),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <f>IF(G5&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V5" t="str">
-        <f>IF(AND(G5&lt;&gt;"",B5="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W5" t="str">
+      <c r="R7" t="str" cm="1">
+        <f t="array" ref="R7">IF(E7&lt;&gt;"",IF(COUNTIFS($E$2:E7,E7,$F$2:F7,"&gt;="&amp;DATE(YEAR(F7),1,1),$F$2:F7,"&lt;="&amp;DATE(YEAR(Q:QF7),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E7,E7,$F$2:F7,"&gt;="&amp;DATE(YEAR(F7),1,1),$F$2:F7,"&lt;="&amp;DATE(YEAR(F7),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E7,E7,$F$2:F7,"&gt;="&amp;DATE(YEAR(F7),1,1),$F$2:F7,"&lt;="&amp;DATE(YEAR(F7),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E7,E7,$F$2:F7,"&gt;="&amp;DATE(YEAR(F7),1,1),$F$2:F7,"&lt;="&amp;DATE(YEAR(F7),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E7,E7,$F$2:F7,"&gt;="&amp;DATE(YEAR(F7),1,1),$F$2:F7,"&lt;="&amp;DATE(YEAR(F7),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <f>IF(E7&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <f>IF(AND(E7&lt;&gt;"",A7="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X5" t="str">
+      <c r="V7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y5" t="str">
+      <c r="W7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z5" t="str">
+      <c r="X7" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:26">
-      <c r="D6" t="str">
-        <f>IF(C6&lt;&gt;"",VLOOKUP(C6,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F6" t="str">
+    <row r="8" spans="1:24">
+      <c r="C8" t="str">
+        <f>IF(B8&lt;&gt;"",VLOOKUP(B8,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M6" t="str">
-        <f>IF(G6&lt;&gt;"",VLOOKUP(G6,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <f>IF(G6&lt;&gt;"",VLOOKUP(G6,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <f>IF(G6&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G6,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G6,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G6,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P6" t="str">
+      <c r="K8" t="str">
+        <f>IF(E8&lt;&gt;"",VLOOKUP(E8,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" t="str">
+        <f>IF(E8&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E8,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E8,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E8,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q6" t="str">
-        <f>IF(B6&lt;&gt;"",IF(B6="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R6" t="str">
+      <c r="O8" t="str">
+        <f>IF(A8&lt;&gt;"",IF(A8="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S6" t="str">
+      <c r="Q8" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T6" t="str" cm="1">
-        <f t="array" ref="T6">IF(G6&lt;&gt;"",IF(COUNTIFS($G$2:G6,G6,$H$2:H6,"&gt;="&amp;DATE(YEAR(H6),1,1),$H$2:H6,"&lt;="&amp;DATE(YEAR(Q:QH6),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G6,G6,$H$2:H6,"&gt;="&amp;DATE(YEAR(H6),1,1),$H$2:H6,"&lt;="&amp;DATE(YEAR(H6),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G6,G6,$H$2:H6,"&gt;="&amp;DATE(YEAR(H6),1,1),$H$2:H6,"&lt;="&amp;DATE(YEAR(H6),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G6,G6,$H$2:H6,"&gt;="&amp;DATE(YEAR(H6),1,1),$H$2:H6,"&lt;="&amp;DATE(YEAR(H6),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G6,G6,$H$2:H6,"&gt;="&amp;DATE(YEAR(H6),1,1),$H$2:H6,"&lt;="&amp;DATE(YEAR(H6),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U6" t="str">
-        <f>IF(G6&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V6" t="str">
-        <f>IF(AND(G6&lt;&gt;"",B6="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W6" t="str">
+      <c r="R8" t="str" cm="1">
+        <f t="array" ref="R8">IF(E8&lt;&gt;"",IF(COUNTIFS($E$2:E8,E8,$F$2:F8,"&gt;="&amp;DATE(YEAR(F8),1,1),$F$2:F8,"&lt;="&amp;DATE(YEAR(Q:QF8),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E8,E8,$F$2:F8,"&gt;="&amp;DATE(YEAR(F8),1,1),$F$2:F8,"&lt;="&amp;DATE(YEAR(F8),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E8,E8,$F$2:F8,"&gt;="&amp;DATE(YEAR(F8),1,1),$F$2:F8,"&lt;="&amp;DATE(YEAR(F8),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E8,E8,$F$2:F8,"&gt;="&amp;DATE(YEAR(F8),1,1),$F$2:F8,"&lt;="&amp;DATE(YEAR(F8),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E8,E8,$F$2:F8,"&gt;="&amp;DATE(YEAR(F8),1,1),$F$2:F8,"&lt;="&amp;DATE(YEAR(F8),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <f>IF(E8&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <f>IF(AND(E8&lt;&gt;"",A8="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U8" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X6" t="str">
+      <c r="V8" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y6" t="str">
+      <c r="W8" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z6" t="str">
+      <c r="X8" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:26">
-      <c r="D7" t="str">
-        <f>IF(C7&lt;&gt;"",VLOOKUP(C7,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+    <row r="9" spans="1:24">
+      <c r="C9" t="str">
+        <f>IF(B9&lt;&gt;"",VLOOKUP(B9,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M7" t="str">
-        <f>IF(G7&lt;&gt;"",VLOOKUP(G7,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <f>IF(G7&lt;&gt;"",VLOOKUP(G7,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <f>IF(G7&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G7,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G7,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G7,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P7" t="str">
+      <c r="K9" t="str">
+        <f>IF(E9&lt;&gt;"",VLOOKUP(E9,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" t="str">
+        <f>IF(E9&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E9,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E9,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E9,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q7" t="str">
-        <f>IF(B7&lt;&gt;"",IF(B7="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R7" t="str">
+      <c r="O9" t="str">
+        <f>IF(A9&lt;&gt;"",IF(A9="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P9" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S7" t="str">
+      <c r="Q9" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T7" t="str" cm="1">
-        <f t="array" ref="T7">IF(G7&lt;&gt;"",IF(COUNTIFS($G$2:G7,G7,$H$2:H7,"&gt;="&amp;DATE(YEAR(H7),1,1),$H$2:H7,"&lt;="&amp;DATE(YEAR(Q:QH7),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G7,G7,$H$2:H7,"&gt;="&amp;DATE(YEAR(H7),1,1),$H$2:H7,"&lt;="&amp;DATE(YEAR(H7),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G7,G7,$H$2:H7,"&gt;="&amp;DATE(YEAR(H7),1,1),$H$2:H7,"&lt;="&amp;DATE(YEAR(H7),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G7,G7,$H$2:H7,"&gt;="&amp;DATE(YEAR(H7),1,1),$H$2:H7,"&lt;="&amp;DATE(YEAR(H7),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G7,G7,$H$2:H7,"&gt;="&amp;DATE(YEAR(H7),1,1),$H$2:H7,"&lt;="&amp;DATE(YEAR(H7),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U7" t="str">
-        <f>IF(G7&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V7" t="str">
-        <f>IF(AND(G7&lt;&gt;"",B7="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W7" t="str">
+      <c r="R9" t="str" cm="1">
+        <f t="array" ref="R9">IF(E9&lt;&gt;"",IF(COUNTIFS($E$2:E9,E9,$F$2:F9,"&gt;="&amp;DATE(YEAR(F9),1,1),$F$2:F9,"&lt;="&amp;DATE(YEAR(Q:QF9),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E9,E9,$F$2:F9,"&gt;="&amp;DATE(YEAR(F9),1,1),$F$2:F9,"&lt;="&amp;DATE(YEAR(F9),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E9,E9,$F$2:F9,"&gt;="&amp;DATE(YEAR(F9),1,1),$F$2:F9,"&lt;="&amp;DATE(YEAR(F9),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E9,E9,$F$2:F9,"&gt;="&amp;DATE(YEAR(F9),1,1),$F$2:F9,"&lt;="&amp;DATE(YEAR(F9),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E9,E9,$F$2:F9,"&gt;="&amp;DATE(YEAR(F9),1,1),$F$2:F9,"&lt;="&amp;DATE(YEAR(F9),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <f>IF(E9&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <f>IF(AND(E9&lt;&gt;"",A9="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U9" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X7" t="str">
+      <c r="V9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y7" t="str">
+      <c r="W9" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z7" t="str">
+      <c r="X9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:26">
-      <c r="D8" t="str">
-        <f>IF(C8&lt;&gt;"",VLOOKUP(C8,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F8" t="str">
+    <row r="10" spans="1:24">
+      <c r="C10" t="str">
+        <f>IF(B10&lt;&gt;"",VLOOKUP(B10,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M8" t="str">
-        <f>IF(G8&lt;&gt;"",VLOOKUP(G8,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <f>IF(G8&lt;&gt;"",VLOOKUP(G8,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <f>IF(G8&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G8,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G8,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G8,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P8" t="str">
+      <c r="K10" t="str">
+        <f>IF(E10&lt;&gt;"",VLOOKUP(E10,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" t="str">
+        <f>IF(E10&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E10,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E10,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E10,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q8" t="str">
-        <f>IF(B8&lt;&gt;"",IF(B8="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R8" t="str">
+      <c r="O10" t="str">
+        <f>IF(A10&lt;&gt;"",IF(A10="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S8" t="str">
+      <c r="Q10" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T8" t="str" cm="1">
-        <f t="array" ref="T8">IF(G8&lt;&gt;"",IF(COUNTIFS($G$2:G8,G8,$H$2:H8,"&gt;="&amp;DATE(YEAR(H8),1,1),$H$2:H8,"&lt;="&amp;DATE(YEAR(Q:QH8),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G8,G8,$H$2:H8,"&gt;="&amp;DATE(YEAR(H8),1,1),$H$2:H8,"&lt;="&amp;DATE(YEAR(H8),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G8,G8,$H$2:H8,"&gt;="&amp;DATE(YEAR(H8),1,1),$H$2:H8,"&lt;="&amp;DATE(YEAR(H8),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G8,G8,$H$2:H8,"&gt;="&amp;DATE(YEAR(H8),1,1),$H$2:H8,"&lt;="&amp;DATE(YEAR(H8),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G8,G8,$H$2:H8,"&gt;="&amp;DATE(YEAR(H8),1,1),$H$2:H8,"&lt;="&amp;DATE(YEAR(H8),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U8" t="str">
-        <f>IF(G8&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V8" t="str">
-        <f>IF(AND(G8&lt;&gt;"",B8="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W8" t="str">
+      <c r="R10" t="str" cm="1">
+        <f t="array" ref="R10">IF(E10&lt;&gt;"",IF(COUNTIFS($E$2:E10,E10,$F$2:F10,"&gt;="&amp;DATE(YEAR(F10),1,1),$F$2:F10,"&lt;="&amp;DATE(YEAR(Q:QF10),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E10,E10,$F$2:F10,"&gt;="&amp;DATE(YEAR(F10),1,1),$F$2:F10,"&lt;="&amp;DATE(YEAR(F10),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E10,E10,$F$2:F10,"&gt;="&amp;DATE(YEAR(F10),1,1),$F$2:F10,"&lt;="&amp;DATE(YEAR(F10),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E10,E10,$F$2:F10,"&gt;="&amp;DATE(YEAR(F10),1,1),$F$2:F10,"&lt;="&amp;DATE(YEAR(F10),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E10,E10,$F$2:F10,"&gt;="&amp;DATE(YEAR(F10),1,1),$F$2:F10,"&lt;="&amp;DATE(YEAR(F10),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <f>IF(E10&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <f>IF(AND(E10&lt;&gt;"",A10="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X8" t="str">
+      <c r="V10" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y8" t="str">
+      <c r="W10" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z8" t="str">
+      <c r="X10" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:26">
-      <c r="D9" t="str">
-        <f>IF(C9&lt;&gt;"",VLOOKUP(C9,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F9" t="str">
+    <row r="11" spans="1:24">
+      <c r="C11" t="str">
+        <f>IF(B11&lt;&gt;"",VLOOKUP(B11,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M9" t="str">
-        <f>IF(G9&lt;&gt;"",VLOOKUP(G9,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <f>IF(G9&lt;&gt;"",VLOOKUP(G9,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <f>IF(G9&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G9,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G9,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G9,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P9" t="str">
+      <c r="K11" t="str">
+        <f>IF(E11&lt;&gt;"",VLOOKUP(E11,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" t="str">
+        <f>IF(E11&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E11,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E11,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E11,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q9" t="str">
-        <f>IF(B9&lt;&gt;"",IF(B9="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R9" t="str">
+      <c r="O11" t="str">
+        <f>IF(A11&lt;&gt;"",IF(A11="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P11" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S9" t="str">
+      <c r="Q11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T9" t="str" cm="1">
-        <f t="array" ref="T9">IF(G9&lt;&gt;"",IF(COUNTIFS($G$2:G9,G9,$H$2:H9,"&gt;="&amp;DATE(YEAR(H9),1,1),$H$2:H9,"&lt;="&amp;DATE(YEAR(Q:QH9),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G9,G9,$H$2:H9,"&gt;="&amp;DATE(YEAR(H9),1,1),$H$2:H9,"&lt;="&amp;DATE(YEAR(H9),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G9,G9,$H$2:H9,"&gt;="&amp;DATE(YEAR(H9),1,1),$H$2:H9,"&lt;="&amp;DATE(YEAR(H9),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G9,G9,$H$2:H9,"&gt;="&amp;DATE(YEAR(H9),1,1),$H$2:H9,"&lt;="&amp;DATE(YEAR(H9),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G9,G9,$H$2:H9,"&gt;="&amp;DATE(YEAR(H9),1,1),$H$2:H9,"&lt;="&amp;DATE(YEAR(H9),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U9" t="str">
-        <f>IF(G9&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V9" t="str">
-        <f>IF(AND(G9&lt;&gt;"",B9="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W9" t="str">
+      <c r="R11" t="str" cm="1">
+        <f t="array" ref="R11">IF(E11&lt;&gt;"",IF(COUNTIFS($E$2:E11,E11,$F$2:F11,"&gt;="&amp;DATE(YEAR(F11),1,1),$F$2:F11,"&lt;="&amp;DATE(YEAR(Q:QF11),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E11,E11,$F$2:F11,"&gt;="&amp;DATE(YEAR(F11),1,1),$F$2:F11,"&lt;="&amp;DATE(YEAR(F11),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E11,E11,$F$2:F11,"&gt;="&amp;DATE(YEAR(F11),1,1),$F$2:F11,"&lt;="&amp;DATE(YEAR(F11),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E11,E11,$F$2:F11,"&gt;="&amp;DATE(YEAR(F11),1,1),$F$2:F11,"&lt;="&amp;DATE(YEAR(F11),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E11,E11,$F$2:F11,"&gt;="&amp;DATE(YEAR(F11),1,1),$F$2:F11,"&lt;="&amp;DATE(YEAR(F11),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <f>IF(E11&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <f>IF(AND(E11&lt;&gt;"",A11="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U11" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X9" t="str">
+      <c r="V11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y9" t="str">
+      <c r="W11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z9" t="str">
+      <c r="X11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:26">
-      <c r="D10" t="str">
-        <f>IF(C10&lt;&gt;"",VLOOKUP(C10,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F10" t="str">
+    <row r="12" spans="1:24">
+      <c r="C12" t="str">
+        <f>IF(B12&lt;&gt;"",VLOOKUP(B12,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M10" t="str">
-        <f>IF(G10&lt;&gt;"",VLOOKUP(G10,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <f>IF(G10&lt;&gt;"",VLOOKUP(G10,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <f>IF(G10&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G10,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G10,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G10,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P10" t="str">
+      <c r="K12" t="str">
+        <f>IF(E12&lt;&gt;"",VLOOKUP(E12,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" t="str">
+        <f>IF(E12&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E12,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E12,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E12,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q10" t="str">
-        <f>IF(B10&lt;&gt;"",IF(B10="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R10" t="str">
+      <c r="O12" t="str">
+        <f>IF(A12&lt;&gt;"",IF(A12="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S10" t="str">
+      <c r="Q12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T10" t="str" cm="1">
-        <f t="array" ref="T10">IF(G10&lt;&gt;"",IF(COUNTIFS($G$2:G10,G10,$H$2:H10,"&gt;="&amp;DATE(YEAR(H10),1,1),$H$2:H10,"&lt;="&amp;DATE(YEAR(Q:QH10),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G10,G10,$H$2:H10,"&gt;="&amp;DATE(YEAR(H10),1,1),$H$2:H10,"&lt;="&amp;DATE(YEAR(H10),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G10,G10,$H$2:H10,"&gt;="&amp;DATE(YEAR(H10),1,1),$H$2:H10,"&lt;="&amp;DATE(YEAR(H10),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G10,G10,$H$2:H10,"&gt;="&amp;DATE(YEAR(H10),1,1),$H$2:H10,"&lt;="&amp;DATE(YEAR(H10),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G10,G10,$H$2:H10,"&gt;="&amp;DATE(YEAR(H10),1,1),$H$2:H10,"&lt;="&amp;DATE(YEAR(H10),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U10" t="str">
-        <f>IF(G10&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V10" t="str">
-        <f>IF(AND(G10&lt;&gt;"",B10="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W10" t="str">
+      <c r="R12" t="str" cm="1">
+        <f t="array" ref="R12">IF(E12&lt;&gt;"",IF(COUNTIFS($E$2:E12,E12,$F$2:F12,"&gt;="&amp;DATE(YEAR(F12),1,1),$F$2:F12,"&lt;="&amp;DATE(YEAR(Q:QF12),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E12,E12,$F$2:F12,"&gt;="&amp;DATE(YEAR(F12),1,1),$F$2:F12,"&lt;="&amp;DATE(YEAR(F12),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E12,E12,$F$2:F12,"&gt;="&amp;DATE(YEAR(F12),1,1),$F$2:F12,"&lt;="&amp;DATE(YEAR(F12),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E12,E12,$F$2:F12,"&gt;="&amp;DATE(YEAR(F12),1,1),$F$2:F12,"&lt;="&amp;DATE(YEAR(F12),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E12,E12,$F$2:F12,"&gt;="&amp;DATE(YEAR(F12),1,1),$F$2:F12,"&lt;="&amp;DATE(YEAR(F12),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <f>IF(E12&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <f>IF(AND(E12&lt;&gt;"",A12="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X10" t="str">
+      <c r="V12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y10" t="str">
+      <c r="W12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z10" t="str">
+      <c r="X12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:26">
-      <c r="D11" t="str">
-        <f>IF(C11&lt;&gt;"",VLOOKUP(C11,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F11" t="str">
+    <row r="13" spans="1:24">
+      <c r="C13" t="str">
+        <f>IF(B13&lt;&gt;"",VLOOKUP(B13,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M11" t="str">
-        <f>IF(G11&lt;&gt;"",VLOOKUP(G11,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <f>IF(G11&lt;&gt;"",VLOOKUP(G11,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <f>IF(G11&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G11,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G11,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G11,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P11" t="str">
+      <c r="K13" t="str">
+        <f>IF(E13&lt;&gt;"",VLOOKUP(E13,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" t="str">
+        <f>IF(E13&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E13,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E13,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E13,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N13" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q11" t="str">
-        <f>IF(B11&lt;&gt;"",IF(B11="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R11" t="str">
+      <c r="O13" t="str">
+        <f>IF(A13&lt;&gt;"",IF(A13="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S11" t="str">
+      <c r="Q13" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T11" t="str" cm="1">
-        <f t="array" ref="T11">IF(G11&lt;&gt;"",IF(COUNTIFS($G$2:G11,G11,$H$2:H11,"&gt;="&amp;DATE(YEAR(H11),1,1),$H$2:H11,"&lt;="&amp;DATE(YEAR(Q:QH11),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G11,G11,$H$2:H11,"&gt;="&amp;DATE(YEAR(H11),1,1),$H$2:H11,"&lt;="&amp;DATE(YEAR(H11),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G11,G11,$H$2:H11,"&gt;="&amp;DATE(YEAR(H11),1,1),$H$2:H11,"&lt;="&amp;DATE(YEAR(H11),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G11,G11,$H$2:H11,"&gt;="&amp;DATE(YEAR(H11),1,1),$H$2:H11,"&lt;="&amp;DATE(YEAR(H11),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G11,G11,$H$2:H11,"&gt;="&amp;DATE(YEAR(H11),1,1),$H$2:H11,"&lt;="&amp;DATE(YEAR(H11),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U11" t="str">
-        <f>IF(G11&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V11" t="str">
-        <f>IF(AND(G11&lt;&gt;"",B11="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W11" t="str">
+      <c r="R13" t="str" cm="1">
+        <f t="array" ref="R13">IF(E13&lt;&gt;"",IF(COUNTIFS($E$2:E13,E13,$F$2:F13,"&gt;="&amp;DATE(YEAR(F13),1,1),$F$2:F13,"&lt;="&amp;DATE(YEAR(Q:QF13),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E13,E13,$F$2:F13,"&gt;="&amp;DATE(YEAR(F13),1,1),$F$2:F13,"&lt;="&amp;DATE(YEAR(F13),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E13,E13,$F$2:F13,"&gt;="&amp;DATE(YEAR(F13),1,1),$F$2:F13,"&lt;="&amp;DATE(YEAR(F13),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E13,E13,$F$2:F13,"&gt;="&amp;DATE(YEAR(F13),1,1),$F$2:F13,"&lt;="&amp;DATE(YEAR(F13),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E13,E13,$F$2:F13,"&gt;="&amp;DATE(YEAR(F13),1,1),$F$2:F13,"&lt;="&amp;DATE(YEAR(F13),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <f>IF(E13&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <f>IF(AND(E13&lt;&gt;"",A13="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U13" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X11" t="str">
+      <c r="V13" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y11" t="str">
+      <c r="W13" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z11" t="str">
+      <c r="X13" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:26">
-      <c r="D12" t="str">
-        <f>IF(C12&lt;&gt;"",VLOOKUP(C12,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F12" t="str">
+    <row r="14" spans="1:24">
+      <c r="C14" t="str">
+        <f>IF(B14&lt;&gt;"",VLOOKUP(B14,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M12" t="str">
-        <f>IF(G12&lt;&gt;"",VLOOKUP(G12,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N12" t="str">
-        <f>IF(G12&lt;&gt;"",VLOOKUP(G12,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <f>IF(G12&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G12,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G12,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G12,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P12" t="str">
+      <c r="K14" t="str">
+        <f>IF(E14&lt;&gt;"",VLOOKUP(E14,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" t="str">
+        <f>IF(E14&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E14,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E14,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E14,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N14" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q12" t="str">
-        <f>IF(B12&lt;&gt;"",IF(B12="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R12" t="str">
+      <c r="O14" t="str">
+        <f>IF(A14&lt;&gt;"",IF(A14="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P14" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S12" t="str">
+      <c r="Q14" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T12" t="str" cm="1">
-        <f t="array" ref="T12">IF(G12&lt;&gt;"",IF(COUNTIFS($G$2:G12,G12,$H$2:H12,"&gt;="&amp;DATE(YEAR(H12),1,1),$H$2:H12,"&lt;="&amp;DATE(YEAR(Q:QH12),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G12,G12,$H$2:H12,"&gt;="&amp;DATE(YEAR(H12),1,1),$H$2:H12,"&lt;="&amp;DATE(YEAR(H12),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G12,G12,$H$2:H12,"&gt;="&amp;DATE(YEAR(H12),1,1),$H$2:H12,"&lt;="&amp;DATE(YEAR(H12),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G12,G12,$H$2:H12,"&gt;="&amp;DATE(YEAR(H12),1,1),$H$2:H12,"&lt;="&amp;DATE(YEAR(H12),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G12,G12,$H$2:H12,"&gt;="&amp;DATE(YEAR(H12),1,1),$H$2:H12,"&lt;="&amp;DATE(YEAR(H12),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U12" t="str">
-        <f>IF(G12&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V12" t="str">
-        <f>IF(AND(G12&lt;&gt;"",B12="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W12" t="str">
+      <c r="R14" t="str" cm="1">
+        <f t="array" ref="R14">IF(E14&lt;&gt;"",IF(COUNTIFS($E$2:E14,E14,$F$2:F14,"&gt;="&amp;DATE(YEAR(F14),1,1),$F$2:F14,"&lt;="&amp;DATE(YEAR(Q:QF14),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E14,E14,$F$2:F14,"&gt;="&amp;DATE(YEAR(F14),1,1),$F$2:F14,"&lt;="&amp;DATE(YEAR(F14),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E14,E14,$F$2:F14,"&gt;="&amp;DATE(YEAR(F14),1,1),$F$2:F14,"&lt;="&amp;DATE(YEAR(F14),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E14,E14,$F$2:F14,"&gt;="&amp;DATE(YEAR(F14),1,1),$F$2:F14,"&lt;="&amp;DATE(YEAR(F14),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E14,E14,$F$2:F14,"&gt;="&amp;DATE(YEAR(F14),1,1),$F$2:F14,"&lt;="&amp;DATE(YEAR(F14),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <f>IF(E14&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <f>IF(AND(E14&lt;&gt;"",A14="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X12" t="str">
+      <c r="V14" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y12" t="str">
+      <c r="W14" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z12" t="str">
+      <c r="X14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:26">
-      <c r="D13" t="str">
-        <f>IF(C13&lt;&gt;"",VLOOKUP(C13,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F13" t="str">
+    <row r="15" spans="1:24">
+      <c r="C15" t="str">
+        <f>IF(B15&lt;&gt;"",VLOOKUP(B15,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D15" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M13" t="str">
-        <f>IF(G13&lt;&gt;"",VLOOKUP(G13,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <f>IF(G13&lt;&gt;"",VLOOKUP(G13,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <f>IF(G13&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G13,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G13,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G13,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P13" t="str">
+      <c r="K15" t="str">
+        <f>IF(E15&lt;&gt;"",VLOOKUP(E15,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="str">
+        <f>IF(E15&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E15,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E15,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E15,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q13" t="str">
-        <f>IF(B13&lt;&gt;"",IF(B13="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R13" t="str">
+      <c r="O15" t="str">
+        <f>IF(A15&lt;&gt;"",IF(A15="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S13" t="str">
+      <c r="Q15" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T13" t="str" cm="1">
-        <f t="array" ref="T13">IF(G13&lt;&gt;"",IF(COUNTIFS($G$2:G13,G13,$H$2:H13,"&gt;="&amp;DATE(YEAR(H13),1,1),$H$2:H13,"&lt;="&amp;DATE(YEAR(Q:QH13),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G13,G13,$H$2:H13,"&gt;="&amp;DATE(YEAR(H13),1,1),$H$2:H13,"&lt;="&amp;DATE(YEAR(H13),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G13,G13,$H$2:H13,"&gt;="&amp;DATE(YEAR(H13),1,1),$H$2:H13,"&lt;="&amp;DATE(YEAR(H13),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G13,G13,$H$2:H13,"&gt;="&amp;DATE(YEAR(H13),1,1),$H$2:H13,"&lt;="&amp;DATE(YEAR(H13),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G13,G13,$H$2:H13,"&gt;="&amp;DATE(YEAR(H13),1,1),$H$2:H13,"&lt;="&amp;DATE(YEAR(H13),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U13" t="str">
-        <f>IF(G13&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V13" t="str">
-        <f>IF(AND(G13&lt;&gt;"",B13="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W13" t="str">
+      <c r="R15" t="str" cm="1">
+        <f t="array" ref="R15">IF(E15&lt;&gt;"",IF(COUNTIFS($E$2:E15,E15,$F$2:F15,"&gt;="&amp;DATE(YEAR(F15),1,1),$F$2:F15,"&lt;="&amp;DATE(YEAR(Q:QF15),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E15,E15,$F$2:F15,"&gt;="&amp;DATE(YEAR(F15),1,1),$F$2:F15,"&lt;="&amp;DATE(YEAR(F15),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E15,E15,$F$2:F15,"&gt;="&amp;DATE(YEAR(F15),1,1),$F$2:F15,"&lt;="&amp;DATE(YEAR(F15),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E15,E15,$F$2:F15,"&gt;="&amp;DATE(YEAR(F15),1,1),$F$2:F15,"&lt;="&amp;DATE(YEAR(F15),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E15,E15,$F$2:F15,"&gt;="&amp;DATE(YEAR(F15),1,1),$F$2:F15,"&lt;="&amp;DATE(YEAR(F15),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <f>IF(E15&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <f>IF(AND(E15&lt;&gt;"",A15="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U15" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X13" t="str">
+      <c r="V15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y13" t="str">
+      <c r="W15" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z13" t="str">
+      <c r="X15" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:26">
-      <c r="D14" t="str">
-        <f>IF(C14&lt;&gt;"",VLOOKUP(C14,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F14" t="str">
+    <row r="16" spans="1:24">
+      <c r="C16" t="str">
+        <f>IF(B16&lt;&gt;"",VLOOKUP(B16,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D16" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M14" t="str">
-        <f>IF(G14&lt;&gt;"",VLOOKUP(G14,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N14" t="str">
-        <f>IF(G14&lt;&gt;"",VLOOKUP(G14,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <f>IF(G14&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G14,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G14,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G14,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P14" t="str">
+      <c r="K16" t="str">
+        <f>IF(E16&lt;&gt;"",VLOOKUP(E16,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" t="str">
+        <f>IF(E16&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E16,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E16,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E16,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N16" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q14" t="str">
-        <f>IF(B14&lt;&gt;"",IF(B14="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R14" t="str">
+      <c r="O16" t="str">
+        <f>IF(A16&lt;&gt;"",IF(A16="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P16" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S14" t="str">
+      <c r="Q16" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T14" t="str" cm="1">
-        <f t="array" ref="T14">IF(G14&lt;&gt;"",IF(COUNTIFS($G$2:G14,G14,$H$2:H14,"&gt;="&amp;DATE(YEAR(H14),1,1),$H$2:H14,"&lt;="&amp;DATE(YEAR(Q:QH14),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G14,G14,$H$2:H14,"&gt;="&amp;DATE(YEAR(H14),1,1),$H$2:H14,"&lt;="&amp;DATE(YEAR(H14),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G14,G14,$H$2:H14,"&gt;="&amp;DATE(YEAR(H14),1,1),$H$2:H14,"&lt;="&amp;DATE(YEAR(H14),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G14,G14,$H$2:H14,"&gt;="&amp;DATE(YEAR(H14),1,1),$H$2:H14,"&lt;="&amp;DATE(YEAR(H14),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G14,G14,$H$2:H14,"&gt;="&amp;DATE(YEAR(H14),1,1),$H$2:H14,"&lt;="&amp;DATE(YEAR(H14),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U14" t="str">
-        <f>IF(G14&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V14" t="str">
-        <f>IF(AND(G14&lt;&gt;"",B14="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W14" t="str">
+      <c r="R16" t="str" cm="1">
+        <f t="array" ref="R16">IF(E16&lt;&gt;"",IF(COUNTIFS($E$2:E16,E16,$F$2:F16,"&gt;="&amp;DATE(YEAR(F16),1,1),$F$2:F16,"&lt;="&amp;DATE(YEAR(Q:QF16),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E16,E16,$F$2:F16,"&gt;="&amp;DATE(YEAR(F16),1,1),$F$2:F16,"&lt;="&amp;DATE(YEAR(F16),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E16,E16,$F$2:F16,"&gt;="&amp;DATE(YEAR(F16),1,1),$F$2:F16,"&lt;="&amp;DATE(YEAR(F16),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E16,E16,$F$2:F16,"&gt;="&amp;DATE(YEAR(F16),1,1),$F$2:F16,"&lt;="&amp;DATE(YEAR(F16),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E16,E16,$F$2:F16,"&gt;="&amp;DATE(YEAR(F16),1,1),$F$2:F16,"&lt;="&amp;DATE(YEAR(F16),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <f>IF(E16&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <f>IF(AND(E16&lt;&gt;"",A16="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U16" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X14" t="str">
+      <c r="V16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y14" t="str">
+      <c r="W16" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z14" t="str">
+      <c r="X16" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:26">
-      <c r="D15" t="str">
-        <f>IF(C15&lt;&gt;"",VLOOKUP(C15,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F15" t="str">
+    <row r="17" spans="3:24">
+      <c r="C17" t="str">
+        <f>IF(B17&lt;&gt;"",VLOOKUP(B17,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M15" t="str">
-        <f>IF(G15&lt;&gt;"",VLOOKUP(G15,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <f>IF(G15&lt;&gt;"",VLOOKUP(G15,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <f>IF(G15&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G15,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G15,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G15,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P15" t="str">
+      <c r="K17" t="str">
+        <f>IF(E17&lt;&gt;"",VLOOKUP(E17,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" t="str">
+        <f>IF(E17&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E17,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E17,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E17,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q15" t="str">
-        <f>IF(B15&lt;&gt;"",IF(B15="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R15" t="str">
+      <c r="O17" t="str">
+        <f>IF(A17&lt;&gt;"",IF(A17="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P17" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S15" t="str">
+      <c r="Q17" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T15" t="str" cm="1">
-        <f t="array" ref="T15">IF(G15&lt;&gt;"",IF(COUNTIFS($G$2:G15,G15,$H$2:H15,"&gt;="&amp;DATE(YEAR(H15),1,1),$H$2:H15,"&lt;="&amp;DATE(YEAR(Q:QH15),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G15,G15,$H$2:H15,"&gt;="&amp;DATE(YEAR(H15),1,1),$H$2:H15,"&lt;="&amp;DATE(YEAR(H15),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G15,G15,$H$2:H15,"&gt;="&amp;DATE(YEAR(H15),1,1),$H$2:H15,"&lt;="&amp;DATE(YEAR(H15),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G15,G15,$H$2:H15,"&gt;="&amp;DATE(YEAR(H15),1,1),$H$2:H15,"&lt;="&amp;DATE(YEAR(H15),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G15,G15,$H$2:H15,"&gt;="&amp;DATE(YEAR(H15),1,1),$H$2:H15,"&lt;="&amp;DATE(YEAR(H15),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U15" t="str">
-        <f>IF(G15&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V15" t="str">
-        <f>IF(AND(G15&lt;&gt;"",B15="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W15" t="str">
+      <c r="R17" t="str" cm="1">
+        <f t="array" ref="R17">IF(E17&lt;&gt;"",IF(COUNTIFS($E$2:E17,E17,$F$2:F17,"&gt;="&amp;DATE(YEAR(F17),1,1),$F$2:F17,"&lt;="&amp;DATE(YEAR(Q:QF17),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E17,E17,$F$2:F17,"&gt;="&amp;DATE(YEAR(F17),1,1),$F$2:F17,"&lt;="&amp;DATE(YEAR(F17),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E17,E17,$F$2:F17,"&gt;="&amp;DATE(YEAR(F17),1,1),$F$2:F17,"&lt;="&amp;DATE(YEAR(F17),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E17,E17,$F$2:F17,"&gt;="&amp;DATE(YEAR(F17),1,1),$F$2:F17,"&lt;="&amp;DATE(YEAR(F17),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E17,E17,$F$2:F17,"&gt;="&amp;DATE(YEAR(F17),1,1),$F$2:F17,"&lt;="&amp;DATE(YEAR(F17),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <f>IF(E17&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <f>IF(AND(E17&lt;&gt;"",A17="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U17" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X15" t="str">
+      <c r="V17" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y15" t="str">
+      <c r="W17" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z15" t="str">
+      <c r="X17" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:26">
-      <c r="D16" t="str">
-        <f>IF(C16&lt;&gt;"",VLOOKUP(C16,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F16" t="str">
+    <row r="18" spans="3:24">
+      <c r="C18" t="str">
+        <f>IF(B18&lt;&gt;"",VLOOKUP(B18,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M16" t="str">
-        <f>IF(G16&lt;&gt;"",VLOOKUP(G16,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <f>IF(G16&lt;&gt;"",VLOOKUP(G16,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <f>IF(G16&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G16,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G16,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G16,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P16" t="str">
+      <c r="K18" t="str">
+        <f>IF(E18&lt;&gt;"",VLOOKUP(E18,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" t="str">
+        <f>IF(E18&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E18,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E18,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E18,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" t="str">
-        <f>IF(B16&lt;&gt;"",IF(B16="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R16" t="str">
+      <c r="O18" t="str">
+        <f>IF(A18&lt;&gt;"",IF(A18="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S16" t="str">
+      <c r="Q18" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T16" t="str" cm="1">
-        <f t="array" ref="T16">IF(G16&lt;&gt;"",IF(COUNTIFS($G$2:G16,G16,$H$2:H16,"&gt;="&amp;DATE(YEAR(H16),1,1),$H$2:H16,"&lt;="&amp;DATE(YEAR(Q:QH16),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G16,G16,$H$2:H16,"&gt;="&amp;DATE(YEAR(H16),1,1),$H$2:H16,"&lt;="&amp;DATE(YEAR(H16),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G16,G16,$H$2:H16,"&gt;="&amp;DATE(YEAR(H16),1,1),$H$2:H16,"&lt;="&amp;DATE(YEAR(H16),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G16,G16,$H$2:H16,"&gt;="&amp;DATE(YEAR(H16),1,1),$H$2:H16,"&lt;="&amp;DATE(YEAR(H16),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G16,G16,$H$2:H16,"&gt;="&amp;DATE(YEAR(H16),1,1),$H$2:H16,"&lt;="&amp;DATE(YEAR(H16),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U16" t="str">
-        <f>IF(G16&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V16" t="str">
-        <f>IF(AND(G16&lt;&gt;"",B16="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W16" t="str">
+      <c r="R18" t="str" cm="1">
+        <f t="array" ref="R18">IF(E18&lt;&gt;"",IF(COUNTIFS($E$2:E18,E18,$F$2:F18,"&gt;="&amp;DATE(YEAR(F18),1,1),$F$2:F18,"&lt;="&amp;DATE(YEAR(Q:QF18),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E18,E18,$F$2:F18,"&gt;="&amp;DATE(YEAR(F18),1,1),$F$2:F18,"&lt;="&amp;DATE(YEAR(F18),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E18,E18,$F$2:F18,"&gt;="&amp;DATE(YEAR(F18),1,1),$F$2:F18,"&lt;="&amp;DATE(YEAR(F18),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E18,E18,$F$2:F18,"&gt;="&amp;DATE(YEAR(F18),1,1),$F$2:F18,"&lt;="&amp;DATE(YEAR(F18),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E18,E18,$F$2:F18,"&gt;="&amp;DATE(YEAR(F18),1,1),$F$2:F18,"&lt;="&amp;DATE(YEAR(F18),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <f>IF(E18&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <f>IF(AND(E18&lt;&gt;"",A18="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U18" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X16" t="str">
+      <c r="V18" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y16" t="str">
+      <c r="W18" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z16" t="str">
+      <c r="X18" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="17" spans="4:26">
-      <c r="D17" t="str">
-        <f>IF(C17&lt;&gt;"",VLOOKUP(C17,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F17" t="str">
+    <row r="19" spans="3:24">
+      <c r="C19" t="str">
+        <f>IF(B19&lt;&gt;"",VLOOKUP(B19,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D19" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M17" t="str">
-        <f>IF(G17&lt;&gt;"",VLOOKUP(G17,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <f>IF(G17&lt;&gt;"",VLOOKUP(G17,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <f>IF(G17&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G17,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G17,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G17,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P17" t="str">
+      <c r="K19" t="str">
+        <f>IF(E19&lt;&gt;"",VLOOKUP(E19,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" t="str">
+        <f>IF(E19&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E19,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E19,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E19,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q17" t="str">
-        <f>IF(B17&lt;&gt;"",IF(B17="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R17" t="str">
+      <c r="O19" t="str">
+        <f>IF(A19&lt;&gt;"",IF(A19="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S17" t="str">
+      <c r="Q19" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T17" t="str" cm="1">
-        <f t="array" ref="T17">IF(G17&lt;&gt;"",IF(COUNTIFS($G$2:G17,G17,$H$2:H17,"&gt;="&amp;DATE(YEAR(H17),1,1),$H$2:H17,"&lt;="&amp;DATE(YEAR(Q:QH17),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G17,G17,$H$2:H17,"&gt;="&amp;DATE(YEAR(H17),1,1),$H$2:H17,"&lt;="&amp;DATE(YEAR(H17),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G17,G17,$H$2:H17,"&gt;="&amp;DATE(YEAR(H17),1,1),$H$2:H17,"&lt;="&amp;DATE(YEAR(H17),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G17,G17,$H$2:H17,"&gt;="&amp;DATE(YEAR(H17),1,1),$H$2:H17,"&lt;="&amp;DATE(YEAR(H17),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G17,G17,$H$2:H17,"&gt;="&amp;DATE(YEAR(H17),1,1),$H$2:H17,"&lt;="&amp;DATE(YEAR(H17),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U17" t="str">
-        <f>IF(G17&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V17" t="str">
-        <f>IF(AND(G17&lt;&gt;"",B17="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W17" t="str">
+      <c r="R19" t="str" cm="1">
+        <f t="array" ref="R19">IF(E19&lt;&gt;"",IF(COUNTIFS($E$2:E19,E19,$F$2:F19,"&gt;="&amp;DATE(YEAR(F19),1,1),$F$2:F19,"&lt;="&amp;DATE(YEAR(Q:QF19),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E19,E19,$F$2:F19,"&gt;="&amp;DATE(YEAR(F19),1,1),$F$2:F19,"&lt;="&amp;DATE(YEAR(F19),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E19,E19,$F$2:F19,"&gt;="&amp;DATE(YEAR(F19),1,1),$F$2:F19,"&lt;="&amp;DATE(YEAR(F19),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E19,E19,$F$2:F19,"&gt;="&amp;DATE(YEAR(F19),1,1),$F$2:F19,"&lt;="&amp;DATE(YEAR(F19),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E19,E19,$F$2:F19,"&gt;="&amp;DATE(YEAR(F19),1,1),$F$2:F19,"&lt;="&amp;DATE(YEAR(F19),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <f>IF(E19&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <f>IF(AND(E19&lt;&gt;"",A19="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U19" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X17" t="str">
+      <c r="V19" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y17" t="str">
+      <c r="W19" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z17" t="str">
+      <c r="X19" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="18" spans="4:26">
-      <c r="D18" t="str">
-        <f>IF(C18&lt;&gt;"",VLOOKUP(C18,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F18" t="str">
+    <row r="20" spans="3:24">
+      <c r="C20" t="str">
+        <f>IF(B20&lt;&gt;"",VLOOKUP(B20,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M18" t="str">
-        <f>IF(G18&lt;&gt;"",VLOOKUP(G18,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <f>IF(G18&lt;&gt;"",VLOOKUP(G18,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <f>IF(G18&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G18,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G18,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G18,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P18" t="str">
+      <c r="K20" t="str">
+        <f>IF(E20&lt;&gt;"",VLOOKUP(E20,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" t="str">
+        <f>IF(E20&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E20,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E20,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E20,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q18" t="str">
-        <f>IF(B18&lt;&gt;"",IF(B18="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R18" t="str">
+      <c r="O20" t="str">
+        <f>IF(A20&lt;&gt;"",IF(A20="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S18" t="str">
+      <c r="Q20" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T18" t="str" cm="1">
-        <f t="array" ref="T18">IF(G18&lt;&gt;"",IF(COUNTIFS($G$2:G18,G18,$H$2:H18,"&gt;="&amp;DATE(YEAR(H18),1,1),$H$2:H18,"&lt;="&amp;DATE(YEAR(Q:QH18),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G18,G18,$H$2:H18,"&gt;="&amp;DATE(YEAR(H18),1,1),$H$2:H18,"&lt;="&amp;DATE(YEAR(H18),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G18,G18,$H$2:H18,"&gt;="&amp;DATE(YEAR(H18),1,1),$H$2:H18,"&lt;="&amp;DATE(YEAR(H18),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G18,G18,$H$2:H18,"&gt;="&amp;DATE(YEAR(H18),1,1),$H$2:H18,"&lt;="&amp;DATE(YEAR(H18),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G18,G18,$H$2:H18,"&gt;="&amp;DATE(YEAR(H18),1,1),$H$2:H18,"&lt;="&amp;DATE(YEAR(H18),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U18" t="str">
-        <f>IF(G18&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V18" t="str">
-        <f>IF(AND(G18&lt;&gt;"",B18="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W18" t="str">
+      <c r="R20" t="str" cm="1">
+        <f t="array" ref="R20">IF(E20&lt;&gt;"",IF(COUNTIFS($E$2:E20,E20,$F$2:F20,"&gt;="&amp;DATE(YEAR(F20),1,1),$F$2:F20,"&lt;="&amp;DATE(YEAR(Q:QF20),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E20,E20,$F$2:F20,"&gt;="&amp;DATE(YEAR(F20),1,1),$F$2:F20,"&lt;="&amp;DATE(YEAR(F20),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E20,E20,$F$2:F20,"&gt;="&amp;DATE(YEAR(F20),1,1),$F$2:F20,"&lt;="&amp;DATE(YEAR(F20),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E20,E20,$F$2:F20,"&gt;="&amp;DATE(YEAR(F20),1,1),$F$2:F20,"&lt;="&amp;DATE(YEAR(F20),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E20,E20,$F$2:F20,"&gt;="&amp;DATE(YEAR(F20),1,1),$F$2:F20,"&lt;="&amp;DATE(YEAR(F20),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <f>IF(E20&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <f>IF(AND(E20&lt;&gt;"",A20="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X18" t="str">
+      <c r="V20" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y18" t="str">
+      <c r="W20" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z18" t="str">
+      <c r="X20" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="19" spans="4:26">
-      <c r="D19" t="str">
-        <f>IF(C19&lt;&gt;"",VLOOKUP(C19,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F19" t="str">
+    <row r="21" spans="3:24">
+      <c r="C21" t="str">
+        <f>IF(B21&lt;&gt;"",VLOOKUP(B21,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M19" t="str">
-        <f>IF(G19&lt;&gt;"",VLOOKUP(G19,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N19" t="str">
-        <f>IF(G19&lt;&gt;"",VLOOKUP(G19,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <f>IF(G19&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G19,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G19,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G19,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P19" t="str">
+      <c r="K21" t="str">
+        <f>IF(E21&lt;&gt;"",VLOOKUP(E21,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" t="str">
+        <f>IF(E21&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E21,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E21,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E21,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q19" t="str">
-        <f>IF(B19&lt;&gt;"",IF(B19="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R19" t="str">
+      <c r="O21" t="str">
+        <f>IF(A21&lt;&gt;"",IF(A21="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P21" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S19" t="str">
+      <c r="Q21" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T19" t="str" cm="1">
-        <f t="array" ref="T19">IF(G19&lt;&gt;"",IF(COUNTIFS($G$2:G19,G19,$H$2:H19,"&gt;="&amp;DATE(YEAR(H19),1,1),$H$2:H19,"&lt;="&amp;DATE(YEAR(Q:QH19),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G19,G19,$H$2:H19,"&gt;="&amp;DATE(YEAR(H19),1,1),$H$2:H19,"&lt;="&amp;DATE(YEAR(H19),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G19,G19,$H$2:H19,"&gt;="&amp;DATE(YEAR(H19),1,1),$H$2:H19,"&lt;="&amp;DATE(YEAR(H19),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G19,G19,$H$2:H19,"&gt;="&amp;DATE(YEAR(H19),1,1),$H$2:H19,"&lt;="&amp;DATE(YEAR(H19),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G19,G19,$H$2:H19,"&gt;="&amp;DATE(YEAR(H19),1,1),$H$2:H19,"&lt;="&amp;DATE(YEAR(H19),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U19" t="str">
-        <f>IF(G19&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V19" t="str">
-        <f>IF(AND(G19&lt;&gt;"",B19="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W19" t="str">
+      <c r="R21" t="str" cm="1">
+        <f t="array" ref="R21">IF(E21&lt;&gt;"",IF(COUNTIFS($E$2:E21,E21,$F$2:F21,"&gt;="&amp;DATE(YEAR(F21),1,1),$F$2:F21,"&lt;="&amp;DATE(YEAR(Q:QF21),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E21,E21,$F$2:F21,"&gt;="&amp;DATE(YEAR(F21),1,1),$F$2:F21,"&lt;="&amp;DATE(YEAR(F21),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E21,E21,$F$2:F21,"&gt;="&amp;DATE(YEAR(F21),1,1),$F$2:F21,"&lt;="&amp;DATE(YEAR(F21),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E21,E21,$F$2:F21,"&gt;="&amp;DATE(YEAR(F21),1,1),$F$2:F21,"&lt;="&amp;DATE(YEAR(F21),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E21,E21,$F$2:F21,"&gt;="&amp;DATE(YEAR(F21),1,1),$F$2:F21,"&lt;="&amp;DATE(YEAR(F21),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <f>IF(E21&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <f>IF(AND(E21&lt;&gt;"",A21="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U21" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X19" t="str">
+      <c r="V21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y19" t="str">
+      <c r="W21" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z19" t="str">
+      <c r="X21" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="20" spans="4:26">
-      <c r="D20" t="str">
-        <f>IF(C20&lt;&gt;"",VLOOKUP(C20,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F20" t="str">
+    <row r="22" spans="3:24">
+      <c r="C22" t="str">
+        <f>IF(B22&lt;&gt;"",VLOOKUP(B22,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M20" t="str">
-        <f>IF(G20&lt;&gt;"",VLOOKUP(G20,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N20" t="str">
-        <f>IF(G20&lt;&gt;"",VLOOKUP(G20,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O20" t="str">
-        <f>IF(G20&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G20,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G20,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G20,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P20" t="str">
+      <c r="K22" t="str">
+        <f>IF(E22&lt;&gt;"",VLOOKUP(E22,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" t="str">
+        <f>IF(E22&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E22,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E22,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E22,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q20" t="str">
-        <f>IF(B20&lt;&gt;"",IF(B20="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R20" t="str">
+      <c r="O22" t="str">
+        <f>IF(A22&lt;&gt;"",IF(A22="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S20" t="str">
+      <c r="Q22" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T20" t="str" cm="1">
-        <f t="array" ref="T20">IF(G20&lt;&gt;"",IF(COUNTIFS($G$2:G20,G20,$H$2:H20,"&gt;="&amp;DATE(YEAR(H20),1,1),$H$2:H20,"&lt;="&amp;DATE(YEAR(Q:QH20),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G20,G20,$H$2:H20,"&gt;="&amp;DATE(YEAR(H20),1,1),$H$2:H20,"&lt;="&amp;DATE(YEAR(H20),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G20,G20,$H$2:H20,"&gt;="&amp;DATE(YEAR(H20),1,1),$H$2:H20,"&lt;="&amp;DATE(YEAR(H20),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G20,G20,$H$2:H20,"&gt;="&amp;DATE(YEAR(H20),1,1),$H$2:H20,"&lt;="&amp;DATE(YEAR(H20),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G20,G20,$H$2:H20,"&gt;="&amp;DATE(YEAR(H20),1,1),$H$2:H20,"&lt;="&amp;DATE(YEAR(H20),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U20" t="str">
-        <f>IF(G20&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V20" t="str">
-        <f>IF(AND(G20&lt;&gt;"",B20="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W20" t="str">
+      <c r="R22" t="str" cm="1">
+        <f t="array" ref="R22">IF(E22&lt;&gt;"",IF(COUNTIFS($E$2:E22,E22,$F$2:F22,"&gt;="&amp;DATE(YEAR(F22),1,1),$F$2:F22,"&lt;="&amp;DATE(YEAR(Q:QF22),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E22,E22,$F$2:F22,"&gt;="&amp;DATE(YEAR(F22),1,1),$F$2:F22,"&lt;="&amp;DATE(YEAR(F22),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E22,E22,$F$2:F22,"&gt;="&amp;DATE(YEAR(F22),1,1),$F$2:F22,"&lt;="&amp;DATE(YEAR(F22),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E22,E22,$F$2:F22,"&gt;="&amp;DATE(YEAR(F22),1,1),$F$2:F22,"&lt;="&amp;DATE(YEAR(F22),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E22,E22,$F$2:F22,"&gt;="&amp;DATE(YEAR(F22),1,1),$F$2:F22,"&lt;="&amp;DATE(YEAR(F22),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <f>IF(E22&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <f>IF(AND(E22&lt;&gt;"",A22="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X20" t="str">
+      <c r="V22" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y20" t="str">
+      <c r="W22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z20" t="str">
+      <c r="X22" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="21" spans="4:26">
-      <c r="D21" t="str">
-        <f>IF(C21&lt;&gt;"",VLOOKUP(C21,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F21" t="str">
+    <row r="23" spans="3:24">
+      <c r="C23" t="str">
+        <f>IF(B23&lt;&gt;"",VLOOKUP(B23,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M21" t="str">
-        <f>IF(G21&lt;&gt;"",VLOOKUP(G21,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <f>IF(G21&lt;&gt;"",VLOOKUP(G21,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <f>IF(G21&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G21,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G21,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G21,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P21" t="str">
+      <c r="K23" t="str">
+        <f>IF(E23&lt;&gt;"",VLOOKUP(E23,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="str">
+        <f>IF(E23&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E23,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E23,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E23,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q21" t="str">
-        <f>IF(B21&lt;&gt;"",IF(B21="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R21" t="str">
+      <c r="O23" t="str">
+        <f>IF(A23&lt;&gt;"",IF(A23="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S21" t="str">
+      <c r="Q23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T21" t="str" cm="1">
-        <f t="array" ref="T21">IF(G21&lt;&gt;"",IF(COUNTIFS($G$2:G21,G21,$H$2:H21,"&gt;="&amp;DATE(YEAR(H21),1,1),$H$2:H21,"&lt;="&amp;DATE(YEAR(Q:QH21),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G21,G21,$H$2:H21,"&gt;="&amp;DATE(YEAR(H21),1,1),$H$2:H21,"&lt;="&amp;DATE(YEAR(H21),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G21,G21,$H$2:H21,"&gt;="&amp;DATE(YEAR(H21),1,1),$H$2:H21,"&lt;="&amp;DATE(YEAR(H21),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G21,G21,$H$2:H21,"&gt;="&amp;DATE(YEAR(H21),1,1),$H$2:H21,"&lt;="&amp;DATE(YEAR(H21),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G21,G21,$H$2:H21,"&gt;="&amp;DATE(YEAR(H21),1,1),$H$2:H21,"&lt;="&amp;DATE(YEAR(H21),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U21" t="str">
-        <f>IF(G21&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V21" t="str">
-        <f>IF(AND(G21&lt;&gt;"",B21="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W21" t="str">
+      <c r="R23" t="str" cm="1">
+        <f t="array" ref="R23">IF(E23&lt;&gt;"",IF(COUNTIFS($E$2:E23,E23,$F$2:F23,"&gt;="&amp;DATE(YEAR(F23),1,1),$F$2:F23,"&lt;="&amp;DATE(YEAR(Q:QF23),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E23,E23,$F$2:F23,"&gt;="&amp;DATE(YEAR(F23),1,1),$F$2:F23,"&lt;="&amp;DATE(YEAR(F23),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E23,E23,$F$2:F23,"&gt;="&amp;DATE(YEAR(F23),1,1),$F$2:F23,"&lt;="&amp;DATE(YEAR(F23),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E23,E23,$F$2:F23,"&gt;="&amp;DATE(YEAR(F23),1,1),$F$2:F23,"&lt;="&amp;DATE(YEAR(F23),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E23,E23,$F$2:F23,"&gt;="&amp;DATE(YEAR(F23),1,1),$F$2:F23,"&lt;="&amp;DATE(YEAR(F23),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <f>IF(E23&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <f>IF(AND(E23&lt;&gt;"",A23="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X21" t="str">
+      <c r="V23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y21" t="str">
+      <c r="W23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z21" t="str">
+      <c r="X23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="22" spans="4:26">
-      <c r="D22" t="str">
-        <f>IF(C22&lt;&gt;"",VLOOKUP(C22,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F22" t="str">
+    <row r="24" spans="3:24">
+      <c r="C24" t="str">
+        <f>IF(B24&lt;&gt;"",VLOOKUP(B24,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D24" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M22" t="str">
-        <f>IF(G22&lt;&gt;"",VLOOKUP(G22,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <f>IF(G22&lt;&gt;"",VLOOKUP(G22,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <f>IF(G22&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G22,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G22,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G22,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P22" t="str">
+      <c r="K24" t="str">
+        <f>IF(E24&lt;&gt;"",VLOOKUP(E24,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" t="str">
+        <f>IF(E24&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E24,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E24,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E24,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N24" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q22" t="str">
-        <f>IF(B22&lt;&gt;"",IF(B22="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R22" t="str">
+      <c r="O24" t="str">
+        <f>IF(A24&lt;&gt;"",IF(A24="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P24" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S22" t="str">
+      <c r="Q24" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T22" t="str" cm="1">
-        <f t="array" ref="T22">IF(G22&lt;&gt;"",IF(COUNTIFS($G$2:G22,G22,$H$2:H22,"&gt;="&amp;DATE(YEAR(H22),1,1),$H$2:H22,"&lt;="&amp;DATE(YEAR(Q:QH22),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G22,G22,$H$2:H22,"&gt;="&amp;DATE(YEAR(H22),1,1),$H$2:H22,"&lt;="&amp;DATE(YEAR(H22),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G22,G22,$H$2:H22,"&gt;="&amp;DATE(YEAR(H22),1,1),$H$2:H22,"&lt;="&amp;DATE(YEAR(H22),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G22,G22,$H$2:H22,"&gt;="&amp;DATE(YEAR(H22),1,1),$H$2:H22,"&lt;="&amp;DATE(YEAR(H22),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G22,G22,$H$2:H22,"&gt;="&amp;DATE(YEAR(H22),1,1),$H$2:H22,"&lt;="&amp;DATE(YEAR(H22),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U22" t="str">
-        <f>IF(G22&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V22" t="str">
-        <f>IF(AND(G22&lt;&gt;"",B22="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W22" t="str">
+      <c r="R24" t="str" cm="1">
+        <f t="array" ref="R24">IF(E24&lt;&gt;"",IF(COUNTIFS($E$2:E24,E24,$F$2:F24,"&gt;="&amp;DATE(YEAR(F24),1,1),$F$2:F24,"&lt;="&amp;DATE(YEAR(Q:QF24),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E24,E24,$F$2:F24,"&gt;="&amp;DATE(YEAR(F24),1,1),$F$2:F24,"&lt;="&amp;DATE(YEAR(F24),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E24,E24,$F$2:F24,"&gt;="&amp;DATE(YEAR(F24),1,1),$F$2:F24,"&lt;="&amp;DATE(YEAR(F24),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E24,E24,$F$2:F24,"&gt;="&amp;DATE(YEAR(F24),1,1),$F$2:F24,"&lt;="&amp;DATE(YEAR(F24),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E24,E24,$F$2:F24,"&gt;="&amp;DATE(YEAR(F24),1,1),$F$2:F24,"&lt;="&amp;DATE(YEAR(F24),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <f>IF(E24&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <f>IF(AND(E24&lt;&gt;"",A24="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U24" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X22" t="str">
+      <c r="V24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y22" t="str">
+      <c r="W24" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z22" t="str">
+      <c r="X24" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="4:26">
-      <c r="D23" t="str">
-        <f>IF(C23&lt;&gt;"",VLOOKUP(C23,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F23" t="str">
+    <row r="25" spans="3:24">
+      <c r="C25" t="str">
+        <f>IF(B25&lt;&gt;"",VLOOKUP(B25,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M23" t="str">
-        <f>IF(G23&lt;&gt;"",VLOOKUP(G23,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <f>IF(G23&lt;&gt;"",VLOOKUP(G23,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <f>IF(G23&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G23,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G23,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G23,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P23" t="str">
+      <c r="K25" t="str">
+        <f>IF(E25&lt;&gt;"",VLOOKUP(E25,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L25" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" t="str">
+        <f>IF(E25&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E25,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E25,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E25,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q23" t="str">
-        <f>IF(B23&lt;&gt;"",IF(B23="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R23" t="str">
+      <c r="O25" t="str">
+        <f>IF(A25&lt;&gt;"",IF(A25="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P25" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S23" t="str">
+      <c r="Q25" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T23" t="str" cm="1">
-        <f t="array" ref="T23">IF(G23&lt;&gt;"",IF(COUNTIFS($G$2:G23,G23,$H$2:H23,"&gt;="&amp;DATE(YEAR(H23),1,1),$H$2:H23,"&lt;="&amp;DATE(YEAR(Q:QH23),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G23,G23,$H$2:H23,"&gt;="&amp;DATE(YEAR(H23),1,1),$H$2:H23,"&lt;="&amp;DATE(YEAR(H23),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G23,G23,$H$2:H23,"&gt;="&amp;DATE(YEAR(H23),1,1),$H$2:H23,"&lt;="&amp;DATE(YEAR(H23),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G23,G23,$H$2:H23,"&gt;="&amp;DATE(YEAR(H23),1,1),$H$2:H23,"&lt;="&amp;DATE(YEAR(H23),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G23,G23,$H$2:H23,"&gt;="&amp;DATE(YEAR(H23),1,1),$H$2:H23,"&lt;="&amp;DATE(YEAR(H23),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U23" t="str">
-        <f>IF(G23&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V23" t="str">
-        <f>IF(AND(G23&lt;&gt;"",B23="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W23" t="str">
+      <c r="R25" t="str" cm="1">
+        <f t="array" ref="R25">IF(E25&lt;&gt;"",IF(COUNTIFS($E$2:E25,E25,$F$2:F25,"&gt;="&amp;DATE(YEAR(F25),1,1),$F$2:F25,"&lt;="&amp;DATE(YEAR(Q:QF25),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E25,E25,$F$2:F25,"&gt;="&amp;DATE(YEAR(F25),1,1),$F$2:F25,"&lt;="&amp;DATE(YEAR(F25),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E25,E25,$F$2:F25,"&gt;="&amp;DATE(YEAR(F25),1,1),$F$2:F25,"&lt;="&amp;DATE(YEAR(F25),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E25,E25,$F$2:F25,"&gt;="&amp;DATE(YEAR(F25),1,1),$F$2:F25,"&lt;="&amp;DATE(YEAR(F25),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E25,E25,$F$2:F25,"&gt;="&amp;DATE(YEAR(F25),1,1),$F$2:F25,"&lt;="&amp;DATE(YEAR(F25),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <f>IF(E25&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <f>IF(AND(E25&lt;&gt;"",A25="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U25" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X23" t="str">
+      <c r="V25" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y23" t="str">
+      <c r="W25" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z23" t="str">
+      <c r="X25" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="4:26">
-      <c r="D24" t="str">
-        <f>IF(C24&lt;&gt;"",VLOOKUP(C24,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F24" t="str">
+    <row r="26" spans="3:24">
+      <c r="C26" t="str">
+        <f>IF(B26&lt;&gt;"",VLOOKUP(B26,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M24" t="str">
-        <f>IF(G24&lt;&gt;"",VLOOKUP(G24,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <f>IF(G24&lt;&gt;"",VLOOKUP(G24,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <f>IF(G24&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G24,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G24,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G24,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P24" t="str">
+      <c r="K26" t="str">
+        <f>IF(E26&lt;&gt;"",VLOOKUP(E26,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L26" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" t="str">
+        <f>IF(E26&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E26,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E26,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E26,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q24" t="str">
-        <f>IF(B24&lt;&gt;"",IF(B24="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R24" t="str">
+      <c r="O26" t="str">
+        <f>IF(A26&lt;&gt;"",IF(A26="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S24" t="str">
+      <c r="Q26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T24" t="str" cm="1">
-        <f t="array" ref="T24">IF(G24&lt;&gt;"",IF(COUNTIFS($G$2:G24,G24,$H$2:H24,"&gt;="&amp;DATE(YEAR(H24),1,1),$H$2:H24,"&lt;="&amp;DATE(YEAR(Q:QH24),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G24,G24,$H$2:H24,"&gt;="&amp;DATE(YEAR(H24),1,1),$H$2:H24,"&lt;="&amp;DATE(YEAR(H24),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G24,G24,$H$2:H24,"&gt;="&amp;DATE(YEAR(H24),1,1),$H$2:H24,"&lt;="&amp;DATE(YEAR(H24),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G24,G24,$H$2:H24,"&gt;="&amp;DATE(YEAR(H24),1,1),$H$2:H24,"&lt;="&amp;DATE(YEAR(H24),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G24,G24,$H$2:H24,"&gt;="&amp;DATE(YEAR(H24),1,1),$H$2:H24,"&lt;="&amp;DATE(YEAR(H24),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U24" t="str">
-        <f>IF(G24&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V24" t="str">
-        <f>IF(AND(G24&lt;&gt;"",B24="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W24" t="str">
+      <c r="R26" t="str" cm="1">
+        <f t="array" ref="R26">IF(E26&lt;&gt;"",IF(COUNTIFS($E$2:E26,E26,$F$2:F26,"&gt;="&amp;DATE(YEAR(F26),1,1),$F$2:F26,"&lt;="&amp;DATE(YEAR(Q:QF26),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E26,E26,$F$2:F26,"&gt;="&amp;DATE(YEAR(F26),1,1),$F$2:F26,"&lt;="&amp;DATE(YEAR(F26),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E26,E26,$F$2:F26,"&gt;="&amp;DATE(YEAR(F26),1,1),$F$2:F26,"&lt;="&amp;DATE(YEAR(F26),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E26,E26,$F$2:F26,"&gt;="&amp;DATE(YEAR(F26),1,1),$F$2:F26,"&lt;="&amp;DATE(YEAR(F26),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E26,E26,$F$2:F26,"&gt;="&amp;DATE(YEAR(F26),1,1),$F$2:F26,"&lt;="&amp;DATE(YEAR(F26),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <f>IF(E26&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <f>IF(AND(E26&lt;&gt;"",A26="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X24" t="str">
+      <c r="V26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y24" t="str">
+      <c r="W26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z24" t="str">
+      <c r="X26" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="4:26">
-      <c r="D25" t="str">
-        <f>IF(C25&lt;&gt;"",VLOOKUP(C25,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F25" t="str">
+    <row r="27" spans="3:24">
+      <c r="C27" t="str">
+        <f>IF(B27&lt;&gt;"",VLOOKUP(B27,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M25" t="str">
-        <f>IF(G25&lt;&gt;"",VLOOKUP(G25,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <f>IF(G25&lt;&gt;"",VLOOKUP(G25,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <f>IF(G25&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G25,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G25,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G25,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P25" t="str">
+      <c r="K27" t="str">
+        <f>IF(E27&lt;&gt;"",VLOOKUP(E27,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L27" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" t="str">
+        <f>IF(E27&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E27,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E27,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E27,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q25" t="str">
-        <f>IF(B25&lt;&gt;"",IF(B25="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R25" t="str">
+      <c r="O27" t="str">
+        <f>IF(A27&lt;&gt;"",IF(A27="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S25" t="str">
+      <c r="Q27" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T25" t="str" cm="1">
-        <f t="array" ref="T25">IF(G25&lt;&gt;"",IF(COUNTIFS($G$2:G25,G25,$H$2:H25,"&gt;="&amp;DATE(YEAR(H25),1,1),$H$2:H25,"&lt;="&amp;DATE(YEAR(Q:QH25),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G25,G25,$H$2:H25,"&gt;="&amp;DATE(YEAR(H25),1,1),$H$2:H25,"&lt;="&amp;DATE(YEAR(H25),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G25,G25,$H$2:H25,"&gt;="&amp;DATE(YEAR(H25),1,1),$H$2:H25,"&lt;="&amp;DATE(YEAR(H25),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G25,G25,$H$2:H25,"&gt;="&amp;DATE(YEAR(H25),1,1),$H$2:H25,"&lt;="&amp;DATE(YEAR(H25),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G25,G25,$H$2:H25,"&gt;="&amp;DATE(YEAR(H25),1,1),$H$2:H25,"&lt;="&amp;DATE(YEAR(H25),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U25" t="str">
-        <f>IF(G25&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V25" t="str">
-        <f>IF(AND(G25&lt;&gt;"",B25="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W25" t="str">
+      <c r="R27" t="str" cm="1">
+        <f t="array" ref="R27">IF(E27&lt;&gt;"",IF(COUNTIFS($E$2:E27,E27,$F$2:F27,"&gt;="&amp;DATE(YEAR(F27),1,1),$F$2:F27,"&lt;="&amp;DATE(YEAR(Q:QF27),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E27,E27,$F$2:F27,"&gt;="&amp;DATE(YEAR(F27),1,1),$F$2:F27,"&lt;="&amp;DATE(YEAR(F27),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E27,E27,$F$2:F27,"&gt;="&amp;DATE(YEAR(F27),1,1),$F$2:F27,"&lt;="&amp;DATE(YEAR(F27),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E27,E27,$F$2:F27,"&gt;="&amp;DATE(YEAR(F27),1,1),$F$2:F27,"&lt;="&amp;DATE(YEAR(F27),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E27,E27,$F$2:F27,"&gt;="&amp;DATE(YEAR(F27),1,1),$F$2:F27,"&lt;="&amp;DATE(YEAR(F27),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <f>IF(E27&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <f>IF(AND(E27&lt;&gt;"",A27="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X25" t="str">
+      <c r="V27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y25" t="str">
+      <c r="W27" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z25" t="str">
+      <c r="X27" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="4:26">
-      <c r="D26" t="str">
-        <f>IF(C26&lt;&gt;"",VLOOKUP(C26,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F26" t="str">
+    <row r="28" spans="3:24">
+      <c r="C28" t="str">
+        <f>IF(B28&lt;&gt;"",VLOOKUP(B28,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D28" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M26" t="str">
-        <f>IF(G26&lt;&gt;"",VLOOKUP(G26,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <f>IF(G26&lt;&gt;"",VLOOKUP(G26,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <f>IF(G26&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G26,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G26,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G26,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P26" t="str">
+      <c r="K28" t="str">
+        <f>IF(E28&lt;&gt;"",VLOOKUP(E28,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L28" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" t="str">
+        <f>IF(E28&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E28,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E28,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E28,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N28" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q26" t="str">
-        <f>IF(B26&lt;&gt;"",IF(B26="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R26" t="str">
+      <c r="O28" t="str">
+        <f>IF(A28&lt;&gt;"",IF(A28="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S26" t="str">
+      <c r="Q28" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T26" t="str" cm="1">
-        <f t="array" ref="T26">IF(G26&lt;&gt;"",IF(COUNTIFS($G$2:G26,G26,$H$2:H26,"&gt;="&amp;DATE(YEAR(H26),1,1),$H$2:H26,"&lt;="&amp;DATE(YEAR(Q:QH26),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G26,G26,$H$2:H26,"&gt;="&amp;DATE(YEAR(H26),1,1),$H$2:H26,"&lt;="&amp;DATE(YEAR(H26),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G26,G26,$H$2:H26,"&gt;="&amp;DATE(YEAR(H26),1,1),$H$2:H26,"&lt;="&amp;DATE(YEAR(H26),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G26,G26,$H$2:H26,"&gt;="&amp;DATE(YEAR(H26),1,1),$H$2:H26,"&lt;="&amp;DATE(YEAR(H26),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G26,G26,$H$2:H26,"&gt;="&amp;DATE(YEAR(H26),1,1),$H$2:H26,"&lt;="&amp;DATE(YEAR(H26),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U26" t="str">
-        <f>IF(G26&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V26" t="str">
-        <f>IF(AND(G26&lt;&gt;"",B26="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W26" t="str">
+      <c r="R28" t="str" cm="1">
+        <f t="array" ref="R28">IF(E28&lt;&gt;"",IF(COUNTIFS($E$2:E28,E28,$F$2:F28,"&gt;="&amp;DATE(YEAR(F28),1,1),$F$2:F28,"&lt;="&amp;DATE(YEAR(Q:QF28),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E28,E28,$F$2:F28,"&gt;="&amp;DATE(YEAR(F28),1,1),$F$2:F28,"&lt;="&amp;DATE(YEAR(F28),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E28,E28,$F$2:F28,"&gt;="&amp;DATE(YEAR(F28),1,1),$F$2:F28,"&lt;="&amp;DATE(YEAR(F28),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E28,E28,$F$2:F28,"&gt;="&amp;DATE(YEAR(F28),1,1),$F$2:F28,"&lt;="&amp;DATE(YEAR(F28),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E28,E28,$F$2:F28,"&gt;="&amp;DATE(YEAR(F28),1,1),$F$2:F28,"&lt;="&amp;DATE(YEAR(F28),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <f>IF(E28&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <f>IF(AND(E28&lt;&gt;"",A28="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X26" t="str">
+      <c r="V28" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y26" t="str">
+      <c r="W28" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z26" t="str">
+      <c r="X28" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="4:26">
-      <c r="D27" t="str">
-        <f>IF(C27&lt;&gt;"",VLOOKUP(C27,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F27" t="str">
+    <row r="29" spans="3:24">
+      <c r="C29" t="str">
+        <f>IF(B29&lt;&gt;"",VLOOKUP(B29,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M27" t="str">
-        <f>IF(G27&lt;&gt;"",VLOOKUP(G27,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <f>IF(G27&lt;&gt;"",VLOOKUP(G27,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <f>IF(G27&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G27,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G27,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G27,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P27" t="str">
+      <c r="K29" t="str">
+        <f>IF(E29&lt;&gt;"",VLOOKUP(E29,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" t="str">
+        <f>IF(E29&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E29,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E29,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E29,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q27" t="str">
-        <f>IF(B27&lt;&gt;"",IF(B27="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R27" t="str">
+      <c r="O29" t="str">
+        <f>IF(A29&lt;&gt;"",IF(A29="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P29" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S27" t="str">
+      <c r="Q29" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T27" t="str" cm="1">
-        <f t="array" ref="T27">IF(G27&lt;&gt;"",IF(COUNTIFS($G$2:G27,G27,$H$2:H27,"&gt;="&amp;DATE(YEAR(H27),1,1),$H$2:H27,"&lt;="&amp;DATE(YEAR(Q:QH27),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G27,G27,$H$2:H27,"&gt;="&amp;DATE(YEAR(H27),1,1),$H$2:H27,"&lt;="&amp;DATE(YEAR(H27),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G27,G27,$H$2:H27,"&gt;="&amp;DATE(YEAR(H27),1,1),$H$2:H27,"&lt;="&amp;DATE(YEAR(H27),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G27,G27,$H$2:H27,"&gt;="&amp;DATE(YEAR(H27),1,1),$H$2:H27,"&lt;="&amp;DATE(YEAR(H27),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G27,G27,$H$2:H27,"&gt;="&amp;DATE(YEAR(H27),1,1),$H$2:H27,"&lt;="&amp;DATE(YEAR(H27),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U27" t="str">
-        <f>IF(G27&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V27" t="str">
-        <f>IF(AND(G27&lt;&gt;"",B27="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W27" t="str">
+      <c r="R29" t="str" cm="1">
+        <f t="array" ref="R29">IF(E29&lt;&gt;"",IF(COUNTIFS($E$2:E29,E29,$F$2:F29,"&gt;="&amp;DATE(YEAR(F29),1,1),$F$2:F29,"&lt;="&amp;DATE(YEAR(Q:QF29),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E29,E29,$F$2:F29,"&gt;="&amp;DATE(YEAR(F29),1,1),$F$2:F29,"&lt;="&amp;DATE(YEAR(F29),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E29,E29,$F$2:F29,"&gt;="&amp;DATE(YEAR(F29),1,1),$F$2:F29,"&lt;="&amp;DATE(YEAR(F29),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E29,E29,$F$2:F29,"&gt;="&amp;DATE(YEAR(F29),1,1),$F$2:F29,"&lt;="&amp;DATE(YEAR(F29),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E29,E29,$F$2:F29,"&gt;="&amp;DATE(YEAR(F29),1,1),$F$2:F29,"&lt;="&amp;DATE(YEAR(F29),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <f>IF(E29&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <f>IF(AND(E29&lt;&gt;"",A29="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X27" t="str">
+      <c r="V29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y27" t="str">
+      <c r="W29" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z27" t="str">
+      <c r="X29" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="4:26">
-      <c r="D28" t="str">
-        <f>IF(C28&lt;&gt;"",VLOOKUP(C28,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F28" t="str">
+    <row r="30" spans="3:24">
+      <c r="C30" t="str">
+        <f>IF(B30&lt;&gt;"",VLOOKUP(B30,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M28" t="str">
-        <f>IF(G28&lt;&gt;"",VLOOKUP(G28,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <f>IF(G28&lt;&gt;"",VLOOKUP(G28,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O28" t="str">
-        <f>IF(G28&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G28,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G28,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G28,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P28" t="str">
+      <c r="K30" t="str">
+        <f>IF(E30&lt;&gt;"",VLOOKUP(E30,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L30" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" t="str">
+        <f>IF(E30&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E30,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E30,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E30,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q28" t="str">
-        <f>IF(B28&lt;&gt;"",IF(B28="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R28" t="str">
+      <c r="O30" t="str">
+        <f>IF(A30&lt;&gt;"",IF(A30="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P30" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S28" t="str">
+      <c r="Q30" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T28" t="str" cm="1">
-        <f t="array" ref="T28">IF(G28&lt;&gt;"",IF(COUNTIFS($G$2:G28,G28,$H$2:H28,"&gt;="&amp;DATE(YEAR(H28),1,1),$H$2:H28,"&lt;="&amp;DATE(YEAR(Q:QH28),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G28,G28,$H$2:H28,"&gt;="&amp;DATE(YEAR(H28),1,1),$H$2:H28,"&lt;="&amp;DATE(YEAR(H28),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G28,G28,$H$2:H28,"&gt;="&amp;DATE(YEAR(H28),1,1),$H$2:H28,"&lt;="&amp;DATE(YEAR(H28),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G28,G28,$H$2:H28,"&gt;="&amp;DATE(YEAR(H28),1,1),$H$2:H28,"&lt;="&amp;DATE(YEAR(H28),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G28,G28,$H$2:H28,"&gt;="&amp;DATE(YEAR(H28),1,1),$H$2:H28,"&lt;="&amp;DATE(YEAR(H28),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U28" t="str">
-        <f>IF(G28&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V28" t="str">
-        <f>IF(AND(G28&lt;&gt;"",B28="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W28" t="str">
+      <c r="R30" t="str" cm="1">
+        <f t="array" ref="R30">IF(E30&lt;&gt;"",IF(COUNTIFS($E$2:E30,E30,$F$2:F30,"&gt;="&amp;DATE(YEAR(F30),1,1),$F$2:F30,"&lt;="&amp;DATE(YEAR(Q:QF30),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E30,E30,$F$2:F30,"&gt;="&amp;DATE(YEAR(F30),1,1),$F$2:F30,"&lt;="&amp;DATE(YEAR(F30),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E30,E30,$F$2:F30,"&gt;="&amp;DATE(YEAR(F30),1,1),$F$2:F30,"&lt;="&amp;DATE(YEAR(F30),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E30,E30,$F$2:F30,"&gt;="&amp;DATE(YEAR(F30),1,1),$F$2:F30,"&lt;="&amp;DATE(YEAR(F30),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E30,E30,$F$2:F30,"&gt;="&amp;DATE(YEAR(F30),1,1),$F$2:F30,"&lt;="&amp;DATE(YEAR(F30),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <f>IF(E30&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <f>IF(AND(E30&lt;&gt;"",A30="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U30" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X28" t="str">
+      <c r="V30" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y28" t="str">
+      <c r="W30" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z28" t="str">
+      <c r="X30" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="4:26">
-      <c r="D29" t="str">
-        <f>IF(C29&lt;&gt;"",VLOOKUP(C29,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F29" t="str">
+    <row r="31" spans="3:24">
+      <c r="C31" t="str">
+        <f>IF(B31&lt;&gt;"",VLOOKUP(B31,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D31" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M29" t="str">
-        <f>IF(G29&lt;&gt;"",VLOOKUP(G29,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <f>IF(G29&lt;&gt;"",VLOOKUP(G29,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O29" t="str">
-        <f>IF(G29&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G29,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G29,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G29,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P29" t="str">
+      <c r="K31" t="str">
+        <f>IF(E31&lt;&gt;"",VLOOKUP(E31,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L31" t="s">
+        <v>27</v>
+      </c>
+      <c r="M31" t="str">
+        <f>IF(E31&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E31,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E31,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E31,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N31" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q29" t="str">
-        <f>IF(B29&lt;&gt;"",IF(B29="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R29" t="str">
+      <c r="O31" t="str">
+        <f>IF(A31&lt;&gt;"",IF(A31="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S29" t="str">
+      <c r="Q31" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T29" t="str" cm="1">
-        <f t="array" ref="T29">IF(G29&lt;&gt;"",IF(COUNTIFS($G$2:G29,G29,$H$2:H29,"&gt;="&amp;DATE(YEAR(H29),1,1),$H$2:H29,"&lt;="&amp;DATE(YEAR(Q:QH29),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G29,G29,$H$2:H29,"&gt;="&amp;DATE(YEAR(H29),1,1),$H$2:H29,"&lt;="&amp;DATE(YEAR(H29),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G29,G29,$H$2:H29,"&gt;="&amp;DATE(YEAR(H29),1,1),$H$2:H29,"&lt;="&amp;DATE(YEAR(H29),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G29,G29,$H$2:H29,"&gt;="&amp;DATE(YEAR(H29),1,1),$H$2:H29,"&lt;="&amp;DATE(YEAR(H29),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G29,G29,$H$2:H29,"&gt;="&amp;DATE(YEAR(H29),1,1),$H$2:H29,"&lt;="&amp;DATE(YEAR(H29),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U29" t="str">
-        <f>IF(G29&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V29" t="str">
-        <f>IF(AND(G29&lt;&gt;"",B29="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W29" t="str">
+      <c r="R31" t="str" cm="1">
+        <f t="array" ref="R31">IF(E31&lt;&gt;"",IF(COUNTIFS($E$2:E31,E31,$F$2:F31,"&gt;="&amp;DATE(YEAR(F31),1,1),$F$2:F31,"&lt;="&amp;DATE(YEAR(Q:QF31),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E31,E31,$F$2:F31,"&gt;="&amp;DATE(YEAR(F31),1,1),$F$2:F31,"&lt;="&amp;DATE(YEAR(F31),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E31,E31,$F$2:F31,"&gt;="&amp;DATE(YEAR(F31),1,1),$F$2:F31,"&lt;="&amp;DATE(YEAR(F31),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E31,E31,$F$2:F31,"&gt;="&amp;DATE(YEAR(F31),1,1),$F$2:F31,"&lt;="&amp;DATE(YEAR(F31),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E31,E31,$F$2:F31,"&gt;="&amp;DATE(YEAR(F31),1,1),$F$2:F31,"&lt;="&amp;DATE(YEAR(F31),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <f>IF(E31&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <f>IF(AND(E31&lt;&gt;"",A31="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X29" t="str">
+      <c r="V31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y29" t="str">
+      <c r="W31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z29" t="str">
+      <c r="X31" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="4:26">
-      <c r="D30" t="str">
-        <f>IF(C30&lt;&gt;"",VLOOKUP(C30,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F30" t="str">
+    <row r="32" spans="3:24">
+      <c r="C32" t="str">
+        <f>IF(B32&lt;&gt;"",VLOOKUP(B32,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M30" t="str">
-        <f>IF(G30&lt;&gt;"",VLOOKUP(G30,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <f>IF(G30&lt;&gt;"",VLOOKUP(G30,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <f>IF(G30&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G30,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G30,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G30,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P30" t="str">
+      <c r="K32" t="str">
+        <f>IF(E32&lt;&gt;"",VLOOKUP(E32,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L32" t="s">
+        <v>27</v>
+      </c>
+      <c r="M32" t="str">
+        <f>IF(E32&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E32,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E32,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E32,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N32" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q30" t="str">
-        <f>IF(B30&lt;&gt;"",IF(B30="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R30" t="str">
+      <c r="O32" t="str">
+        <f>IF(A32&lt;&gt;"",IF(A32="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P32" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S30" t="str">
+      <c r="Q32" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T30" t="str" cm="1">
-        <f t="array" ref="T30">IF(G30&lt;&gt;"",IF(COUNTIFS($G$2:G30,G30,$H$2:H30,"&gt;="&amp;DATE(YEAR(H30),1,1),$H$2:H30,"&lt;="&amp;DATE(YEAR(Q:QH30),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G30,G30,$H$2:H30,"&gt;="&amp;DATE(YEAR(H30),1,1),$H$2:H30,"&lt;="&amp;DATE(YEAR(H30),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G30,G30,$H$2:H30,"&gt;="&amp;DATE(YEAR(H30),1,1),$H$2:H30,"&lt;="&amp;DATE(YEAR(H30),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G30,G30,$H$2:H30,"&gt;="&amp;DATE(YEAR(H30),1,1),$H$2:H30,"&lt;="&amp;DATE(YEAR(H30),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G30,G30,$H$2:H30,"&gt;="&amp;DATE(YEAR(H30),1,1),$H$2:H30,"&lt;="&amp;DATE(YEAR(H30),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U30" t="str">
-        <f>IF(G30&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V30" t="str">
-        <f>IF(AND(G30&lt;&gt;"",B30="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W30" t="str">
+      <c r="R32" t="str" cm="1">
+        <f t="array" ref="R32">IF(E32&lt;&gt;"",IF(COUNTIFS($E$2:E32,E32,$F$2:F32,"&gt;="&amp;DATE(YEAR(F32),1,1),$F$2:F32,"&lt;="&amp;DATE(YEAR(Q:QF32),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E32,E32,$F$2:F32,"&gt;="&amp;DATE(YEAR(F32),1,1),$F$2:F32,"&lt;="&amp;DATE(YEAR(F32),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E32,E32,$F$2:F32,"&gt;="&amp;DATE(YEAR(F32),1,1),$F$2:F32,"&lt;="&amp;DATE(YEAR(F32),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E32,E32,$F$2:F32,"&gt;="&amp;DATE(YEAR(F32),1,1),$F$2:F32,"&lt;="&amp;DATE(YEAR(F32),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E32,E32,$F$2:F32,"&gt;="&amp;DATE(YEAR(F32),1,1),$F$2:F32,"&lt;="&amp;DATE(YEAR(F32),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S32" t="str">
+        <f>IF(E32&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <f>IF(AND(E32&lt;&gt;"",A32="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U32" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X30" t="str">
+      <c r="V32" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y30" t="str">
+      <c r="W32" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z30" t="str">
+      <c r="X32" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="4:26">
-      <c r="D31" t="str">
-        <f>IF(C31&lt;&gt;"",VLOOKUP(C31,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F31" t="str">
+    <row r="33" spans="3:24">
+      <c r="C33" t="str">
+        <f>IF(B33&lt;&gt;"",VLOOKUP(B33,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M31" t="str">
-        <f>IF(G31&lt;&gt;"",VLOOKUP(G31,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <f>IF(G31&lt;&gt;"",VLOOKUP(G31,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O31" t="str">
-        <f>IF(G31&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G31,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G31,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G31,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P31" t="str">
+      <c r="K33" t="str">
+        <f>IF(E33&lt;&gt;"",VLOOKUP(E33,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" t="str">
+        <f>IF(E33&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E33,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E33,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E33,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N33" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q31" t="str">
-        <f>IF(B31&lt;&gt;"",IF(B31="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R31" t="str">
+      <c r="O33" t="str">
+        <f>IF(A33&lt;&gt;"",IF(A33="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S31" t="str">
+      <c r="Q33" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T31" t="str" cm="1">
-        <f t="array" ref="T31">IF(G31&lt;&gt;"",IF(COUNTIFS($G$2:G31,G31,$H$2:H31,"&gt;="&amp;DATE(YEAR(H31),1,1),$H$2:H31,"&lt;="&amp;DATE(YEAR(Q:QH31),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G31,G31,$H$2:H31,"&gt;="&amp;DATE(YEAR(H31),1,1),$H$2:H31,"&lt;="&amp;DATE(YEAR(H31),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G31,G31,$H$2:H31,"&gt;="&amp;DATE(YEAR(H31),1,1),$H$2:H31,"&lt;="&amp;DATE(YEAR(H31),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G31,G31,$H$2:H31,"&gt;="&amp;DATE(YEAR(H31),1,1),$H$2:H31,"&lt;="&amp;DATE(YEAR(H31),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G31,G31,$H$2:H31,"&gt;="&amp;DATE(YEAR(H31),1,1),$H$2:H31,"&lt;="&amp;DATE(YEAR(H31),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U31" t="str">
-        <f>IF(G31&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V31" t="str">
-        <f>IF(AND(G31&lt;&gt;"",B31="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W31" t="str">
+      <c r="R33" t="str" cm="1">
+        <f t="array" ref="R33">IF(E33&lt;&gt;"",IF(COUNTIFS($E$2:E33,E33,$F$2:F33,"&gt;="&amp;DATE(YEAR(F33),1,1),$F$2:F33,"&lt;="&amp;DATE(YEAR(Q:QF33),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E33,E33,$F$2:F33,"&gt;="&amp;DATE(YEAR(F33),1,1),$F$2:F33,"&lt;="&amp;DATE(YEAR(F33),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E33,E33,$F$2:F33,"&gt;="&amp;DATE(YEAR(F33),1,1),$F$2:F33,"&lt;="&amp;DATE(YEAR(F33),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E33,E33,$F$2:F33,"&gt;="&amp;DATE(YEAR(F33),1,1),$F$2:F33,"&lt;="&amp;DATE(YEAR(F33),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E33,E33,$F$2:F33,"&gt;="&amp;DATE(YEAR(F33),1,1),$F$2:F33,"&lt;="&amp;DATE(YEAR(F33),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S33" t="str">
+        <f>IF(E33&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T33" t="str">
+        <f>IF(AND(E33&lt;&gt;"",A33="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X31" t="str">
+      <c r="V33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y31" t="str">
+      <c r="W33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z31" t="str">
+      <c r="X33" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="4:26">
-      <c r="D32" t="str">
-        <f>IF(C32&lt;&gt;"",VLOOKUP(C32,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F32" t="str">
+    <row r="34" spans="3:24">
+      <c r="C34" t="str">
+        <f>IF(B34&lt;&gt;"",VLOOKUP(B34,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M32" t="str">
-        <f>IF(G32&lt;&gt;"",VLOOKUP(G32,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <f>IF(G32&lt;&gt;"",VLOOKUP(G32,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O32" t="str">
-        <f>IF(G32&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G32,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G32,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G32,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P32" t="str">
+      <c r="K34" t="str">
+        <f>IF(E34&lt;&gt;"",VLOOKUP(E34,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L34" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" t="str">
+        <f>IF(E34&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E34,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E34,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E34,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q32" t="str">
-        <f>IF(B32&lt;&gt;"",IF(B32="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R32" t="str">
+      <c r="O34" t="str">
+        <f>IF(A34&lt;&gt;"",IF(A34="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S32" t="str">
+      <c r="Q34" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T32" t="str" cm="1">
-        <f t="array" ref="T32">IF(G32&lt;&gt;"",IF(COUNTIFS($G$2:G32,G32,$H$2:H32,"&gt;="&amp;DATE(YEAR(H32),1,1),$H$2:H32,"&lt;="&amp;DATE(YEAR(Q:QH32),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G32,G32,$H$2:H32,"&gt;="&amp;DATE(YEAR(H32),1,1),$H$2:H32,"&lt;="&amp;DATE(YEAR(H32),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G32,G32,$H$2:H32,"&gt;="&amp;DATE(YEAR(H32),1,1),$H$2:H32,"&lt;="&amp;DATE(YEAR(H32),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G32,G32,$H$2:H32,"&gt;="&amp;DATE(YEAR(H32),1,1),$H$2:H32,"&lt;="&amp;DATE(YEAR(H32),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G32,G32,$H$2:H32,"&gt;="&amp;DATE(YEAR(H32),1,1),$H$2:H32,"&lt;="&amp;DATE(YEAR(H32),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U32" t="str">
-        <f>IF(G32&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V32" t="str">
-        <f>IF(AND(G32&lt;&gt;"",B32="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W32" t="str">
+      <c r="R34" t="str" cm="1">
+        <f t="array" ref="R34">IF(E34&lt;&gt;"",IF(COUNTIFS($E$2:E34,E34,$F$2:F34,"&gt;="&amp;DATE(YEAR(F34),1,1),$F$2:F34,"&lt;="&amp;DATE(YEAR(Q:QF34),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E34,E34,$F$2:F34,"&gt;="&amp;DATE(YEAR(F34),1,1),$F$2:F34,"&lt;="&amp;DATE(YEAR(F34),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E34,E34,$F$2:F34,"&gt;="&amp;DATE(YEAR(F34),1,1),$F$2:F34,"&lt;="&amp;DATE(YEAR(F34),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E34,E34,$F$2:F34,"&gt;="&amp;DATE(YEAR(F34),1,1),$F$2:F34,"&lt;="&amp;DATE(YEAR(F34),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E34,E34,$F$2:F34,"&gt;="&amp;DATE(YEAR(F34),1,1),$F$2:F34,"&lt;="&amp;DATE(YEAR(F34),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S34" t="str">
+        <f>IF(E34&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T34" t="str">
+        <f>IF(AND(E34&lt;&gt;"",A34="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U34" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X32" t="str">
+      <c r="V34" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y32" t="str">
+      <c r="W34" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z32" t="str">
+      <c r="X34" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="4:26">
-      <c r="D33" t="str">
-        <f>IF(C33&lt;&gt;"",VLOOKUP(C33,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F33" t="str">
+    <row r="35" spans="3:24">
+      <c r="C35" t="str">
+        <f>IF(B35&lt;&gt;"",VLOOKUP(B35,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M33" t="str">
-        <f>IF(G33&lt;&gt;"",VLOOKUP(G33,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N33" t="str">
-        <f>IF(G33&lt;&gt;"",VLOOKUP(G33,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O33" t="str">
-        <f>IF(G33&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G33,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G33,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G33,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P33" t="str">
+      <c r="K35" t="str">
+        <f>IF(E35&lt;&gt;"",VLOOKUP(E35,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L35" t="s">
+        <v>27</v>
+      </c>
+      <c r="M35" t="str">
+        <f>IF(E35&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E35,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E35,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E35,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q33" t="str">
-        <f>IF(B33&lt;&gt;"",IF(B33="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R33" t="str">
+      <c r="O35" t="str">
+        <f>IF(A35&lt;&gt;"",IF(A35="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P35" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S33" t="str">
+      <c r="Q35" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T33" t="str" cm="1">
-        <f t="array" ref="T33">IF(G33&lt;&gt;"",IF(COUNTIFS($G$2:G33,G33,$H$2:H33,"&gt;="&amp;DATE(YEAR(H33),1,1),$H$2:H33,"&lt;="&amp;DATE(YEAR(Q:QH33),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G33,G33,$H$2:H33,"&gt;="&amp;DATE(YEAR(H33),1,1),$H$2:H33,"&lt;="&amp;DATE(YEAR(H33),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G33,G33,$H$2:H33,"&gt;="&amp;DATE(YEAR(H33),1,1),$H$2:H33,"&lt;="&amp;DATE(YEAR(H33),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G33,G33,$H$2:H33,"&gt;="&amp;DATE(YEAR(H33),1,1),$H$2:H33,"&lt;="&amp;DATE(YEAR(H33),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G33,G33,$H$2:H33,"&gt;="&amp;DATE(YEAR(H33),1,1),$H$2:H33,"&lt;="&amp;DATE(YEAR(H33),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U33" t="str">
-        <f>IF(G33&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V33" t="str">
-        <f>IF(AND(G33&lt;&gt;"",B33="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W33" t="str">
+      <c r="R35" t="str" cm="1">
+        <f t="array" ref="R35">IF(E35&lt;&gt;"",IF(COUNTIFS($E$2:E35,E35,$F$2:F35,"&gt;="&amp;DATE(YEAR(F35),1,1),$F$2:F35,"&lt;="&amp;DATE(YEAR(Q:QF35),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E35,E35,$F$2:F35,"&gt;="&amp;DATE(YEAR(F35),1,1),$F$2:F35,"&lt;="&amp;DATE(YEAR(F35),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E35,E35,$F$2:F35,"&gt;="&amp;DATE(YEAR(F35),1,1),$F$2:F35,"&lt;="&amp;DATE(YEAR(F35),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E35,E35,$F$2:F35,"&gt;="&amp;DATE(YEAR(F35),1,1),$F$2:F35,"&lt;="&amp;DATE(YEAR(F35),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E35,E35,$F$2:F35,"&gt;="&amp;DATE(YEAR(F35),1,1),$F$2:F35,"&lt;="&amp;DATE(YEAR(F35),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S35" t="str">
+        <f>IF(E35&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T35" t="str">
+        <f>IF(AND(E35&lt;&gt;"",A35="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U35" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X33" t="str">
+      <c r="V35" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y33" t="str">
+      <c r="W35" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z33" t="str">
+      <c r="X35" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="34" spans="4:26">
-      <c r="D34" t="str">
-        <f>IF(C34&lt;&gt;"",VLOOKUP(C34,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F34" t="str">
+    <row r="36" spans="3:24">
+      <c r="C36" t="str">
+        <f>IF(B36&lt;&gt;"",VLOOKUP(B36,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M34" t="str">
-        <f>IF(G34&lt;&gt;"",VLOOKUP(G34,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N34" t="str">
-        <f>IF(G34&lt;&gt;"",VLOOKUP(G34,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O34" t="str">
-        <f>IF(G34&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G34,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G34,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G34,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P34" t="str">
+      <c r="K36" t="str">
+        <f>IF(E36&lt;&gt;"",VLOOKUP(E36,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L36" t="s">
+        <v>27</v>
+      </c>
+      <c r="M36" t="str">
+        <f>IF(E36&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E36,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E36,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E36,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N36" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q34" t="str">
-        <f>IF(B34&lt;&gt;"",IF(B34="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R34" t="str">
+      <c r="O36" t="str">
+        <f>IF(A36&lt;&gt;"",IF(A36="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P36" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S34" t="str">
+      <c r="Q36" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T34" t="str" cm="1">
-        <f t="array" ref="T34">IF(G34&lt;&gt;"",IF(COUNTIFS($G$2:G34,G34,$H$2:H34,"&gt;="&amp;DATE(YEAR(H34),1,1),$H$2:H34,"&lt;="&amp;DATE(YEAR(Q:QH34),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G34,G34,$H$2:H34,"&gt;="&amp;DATE(YEAR(H34),1,1),$H$2:H34,"&lt;="&amp;DATE(YEAR(H34),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G34,G34,$H$2:H34,"&gt;="&amp;DATE(YEAR(H34),1,1),$H$2:H34,"&lt;="&amp;DATE(YEAR(H34),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G34,G34,$H$2:H34,"&gt;="&amp;DATE(YEAR(H34),1,1),$H$2:H34,"&lt;="&amp;DATE(YEAR(H34),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G34,G34,$H$2:H34,"&gt;="&amp;DATE(YEAR(H34),1,1),$H$2:H34,"&lt;="&amp;DATE(YEAR(H34),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U34" t="str">
-        <f>IF(G34&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V34" t="str">
-        <f>IF(AND(G34&lt;&gt;"",B34="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W34" t="str">
+      <c r="R36" t="str" cm="1">
+        <f t="array" ref="R36">IF(E36&lt;&gt;"",IF(COUNTIFS($E$2:E36,E36,$F$2:F36,"&gt;="&amp;DATE(YEAR(F36),1,1),$F$2:F36,"&lt;="&amp;DATE(YEAR(Q:QF36),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E36,E36,$F$2:F36,"&gt;="&amp;DATE(YEAR(F36),1,1),$F$2:F36,"&lt;="&amp;DATE(YEAR(F36),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E36,E36,$F$2:F36,"&gt;="&amp;DATE(YEAR(F36),1,1),$F$2:F36,"&lt;="&amp;DATE(YEAR(F36),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E36,E36,$F$2:F36,"&gt;="&amp;DATE(YEAR(F36),1,1),$F$2:F36,"&lt;="&amp;DATE(YEAR(F36),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E36,E36,$F$2:F36,"&gt;="&amp;DATE(YEAR(F36),1,1),$F$2:F36,"&lt;="&amp;DATE(YEAR(F36),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S36" t="str">
+        <f>IF(E36&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T36" t="str">
+        <f>IF(AND(E36&lt;&gt;"",A36="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U36" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X34" t="str">
+      <c r="V36" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y34" t="str">
+      <c r="W36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z34" t="str">
+      <c r="X36" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="4:26">
-      <c r="D35" t="str">
-        <f>IF(C35&lt;&gt;"",VLOOKUP(C35,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F35" t="str">
+    <row r="37" spans="3:24">
+      <c r="C37" t="str">
+        <f>IF(B37&lt;&gt;"",VLOOKUP(B37,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M35" t="str">
-        <f>IF(G35&lt;&gt;"",VLOOKUP(G35,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N35" t="str">
-        <f>IF(G35&lt;&gt;"",VLOOKUP(G35,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O35" t="str">
-        <f>IF(G35&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G35,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G35,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G35,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P35" t="str">
+      <c r="K37" t="str">
+        <f>IF(E37&lt;&gt;"",VLOOKUP(E37,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L37" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" t="str">
+        <f>IF(E37&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E37,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E37,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E37,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N37" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q35" t="str">
-        <f>IF(B35&lt;&gt;"",IF(B35="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R35" t="str">
+      <c r="O37" t="str">
+        <f>IF(A37&lt;&gt;"",IF(A37="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P37" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S35" t="str">
+      <c r="Q37" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T35" t="str" cm="1">
-        <f t="array" ref="T35">IF(G35&lt;&gt;"",IF(COUNTIFS($G$2:G35,G35,$H$2:H35,"&gt;="&amp;DATE(YEAR(H35),1,1),$H$2:H35,"&lt;="&amp;DATE(YEAR(Q:QH35),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G35,G35,$H$2:H35,"&gt;="&amp;DATE(YEAR(H35),1,1),$H$2:H35,"&lt;="&amp;DATE(YEAR(H35),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G35,G35,$H$2:H35,"&gt;="&amp;DATE(YEAR(H35),1,1),$H$2:H35,"&lt;="&amp;DATE(YEAR(H35),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G35,G35,$H$2:H35,"&gt;="&amp;DATE(YEAR(H35),1,1),$H$2:H35,"&lt;="&amp;DATE(YEAR(H35),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G35,G35,$H$2:H35,"&gt;="&amp;DATE(YEAR(H35),1,1),$H$2:H35,"&lt;="&amp;DATE(YEAR(H35),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U35" t="str">
-        <f>IF(G35&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V35" t="str">
-        <f>IF(AND(G35&lt;&gt;"",B35="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W35" t="str">
+      <c r="R37" t="str" cm="1">
+        <f t="array" ref="R37">IF(E37&lt;&gt;"",IF(COUNTIFS($E$2:E37,E37,$F$2:F37,"&gt;="&amp;DATE(YEAR(F37),1,1),$F$2:F37,"&lt;="&amp;DATE(YEAR(Q:QF37),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E37,E37,$F$2:F37,"&gt;="&amp;DATE(YEAR(F37),1,1),$F$2:F37,"&lt;="&amp;DATE(YEAR(F37),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E37,E37,$F$2:F37,"&gt;="&amp;DATE(YEAR(F37),1,1),$F$2:F37,"&lt;="&amp;DATE(YEAR(F37),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E37,E37,$F$2:F37,"&gt;="&amp;DATE(YEAR(F37),1,1),$F$2:F37,"&lt;="&amp;DATE(YEAR(F37),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E37,E37,$F$2:F37,"&gt;="&amp;DATE(YEAR(F37),1,1),$F$2:F37,"&lt;="&amp;DATE(YEAR(F37),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S37" t="str">
+        <f>IF(E37&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <f>IF(AND(E37&lt;&gt;"",A37="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U37" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X35" t="str">
+      <c r="V37" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y35" t="str">
+      <c r="W37" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z35" t="str">
+      <c r="X37" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
-    <row r="36" spans="4:26">
-      <c r="D36" t="str">
-        <f>IF(C36&lt;&gt;"",VLOOKUP(C36,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F36" t="str">
+    <row r="38" spans="3:24">
+      <c r="C38" t="str">
+        <f>IF(B38&lt;&gt;"",VLOOKUP(B38,Tableau3[#All],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D38" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="M36" t="str">
-        <f>IF(G36&lt;&gt;"",VLOOKUP(G36,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N36" t="str">
-        <f>IF(G36&lt;&gt;"",VLOOKUP(G36,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O36" t="str">
-        <f>IF(G36&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G36,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G36,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G36,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P36" t="str">
+      <c r="K38" t="str">
+        <f>IF(E38&lt;&gt;"",VLOOKUP(E38,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
+        <v/>
+      </c>
+      <c r="L38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M38" t="str">
+        <f>IF(E38&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E38,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E38,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E38,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
+        <v/>
+      </c>
+      <c r="N38" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q36" t="str">
-        <f>IF(B36&lt;&gt;"",IF(B36="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R36" t="str">
+      <c r="O38" t="str">
+        <f>IF(A38&lt;&gt;"",IF(A38="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P38" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="S36" t="str">
+      <c r="Q38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="T36" t="str" cm="1">
-        <f t="array" ref="T36">IF(G36&lt;&gt;"",IF(COUNTIFS($G$2:G36,G36,$H$2:H36,"&gt;="&amp;DATE(YEAR(H36),1,1),$H$2:H36,"&lt;="&amp;DATE(YEAR(Q:QH36),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G36,G36,$H$2:H36,"&gt;="&amp;DATE(YEAR(H36),1,1),$H$2:H36,"&lt;="&amp;DATE(YEAR(H36),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G36,G36,$H$2:H36,"&gt;="&amp;DATE(YEAR(H36),1,1),$H$2:H36,"&lt;="&amp;DATE(YEAR(H36),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G36,G36,$H$2:H36,"&gt;="&amp;DATE(YEAR(H36),1,1),$H$2:H36,"&lt;="&amp;DATE(YEAR(H36),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G36,G36,$H$2:H36,"&gt;="&amp;DATE(YEAR(H36),1,1),$H$2:H36,"&lt;="&amp;DATE(YEAR(H36),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U36" t="str">
-        <f>IF(G36&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V36" t="str">
-        <f>IF(AND(G36&lt;&gt;"",B36="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W36" t="str">
+      <c r="R38" t="str" cm="1">
+        <f t="array" ref="R38">IF(E38&lt;&gt;"",IF(COUNTIFS($E$2:E38,E38,$F$2:F38,"&gt;="&amp;DATE(YEAR(F38),1,1),$F$2:F38,"&lt;="&amp;DATE(YEAR(Q:QF38),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E38,E38,$F$2:F38,"&gt;="&amp;DATE(YEAR(F38),1,1),$F$2:F38,"&lt;="&amp;DATE(YEAR(F38),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E38,E38,$F$2:F38,"&gt;="&amp;DATE(YEAR(F38),1,1),$F$2:F38,"&lt;="&amp;DATE(YEAR(F38),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E38,E38,$F$2:F38,"&gt;="&amp;DATE(YEAR(F38),1,1),$F$2:F38,"&lt;="&amp;DATE(YEAR(F38),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E38,E38,$F$2:F38,"&gt;="&amp;DATE(YEAR(F38),1,1),$F$2:F38,"&lt;="&amp;DATE(YEAR(F38),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <v/>
+      </c>
+      <c r="S38" t="str">
+        <f>IF(E38&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T38" t="str">
+        <f>IF(AND(E38&lt;&gt;"",A38="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U38" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X36" t="str">
+      <c r="V38" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y36" t="str">
+      <c r="W38" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Z36" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="4:26">
-      <c r="D37" t="str">
-        <f>IF(C37&lt;&gt;"",VLOOKUP(C37,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M37" t="str">
-        <f>IF(G37&lt;&gt;"",VLOOKUP(G37,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N37" t="str">
-        <f>IF(G37&lt;&gt;"",VLOOKUP(G37,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O37" t="str">
-        <f>IF(G37&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G37,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G37,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G37,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P37" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q37" t="str">
-        <f>IF(B37&lt;&gt;"",IF(B37="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R37" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S37" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="T37" t="str" cm="1">
-        <f t="array" ref="T37">IF(G37&lt;&gt;"",IF(COUNTIFS($G$2:G37,G37,$H$2:H37,"&gt;="&amp;DATE(YEAR(H37),1,1),$H$2:H37,"&lt;="&amp;DATE(YEAR(Q:QH37),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G37,G37,$H$2:H37,"&gt;="&amp;DATE(YEAR(H37),1,1),$H$2:H37,"&lt;="&amp;DATE(YEAR(H37),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G37,G37,$H$2:H37,"&gt;="&amp;DATE(YEAR(H37),1,1),$H$2:H37,"&lt;="&amp;DATE(YEAR(H37),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G37,G37,$H$2:H37,"&gt;="&amp;DATE(YEAR(H37),1,1),$H$2:H37,"&lt;="&amp;DATE(YEAR(H37),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G37,G37,$H$2:H37,"&gt;="&amp;DATE(YEAR(H37),1,1),$H$2:H37,"&lt;="&amp;DATE(YEAR(H37),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U37" t="str">
-        <f>IF(G37&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V37" t="str">
-        <f>IF(AND(G37&lt;&gt;"",B37="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W37" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="X37" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y37" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Z37" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="4:26">
-      <c r="D38" t="str">
-        <f>IF(C38&lt;&gt;"",VLOOKUP(C38,Tableau3[#All],2,0),"")</f>
-        <v/>
-      </c>
-      <c r="F38" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M38" t="str">
-        <f>IF(G38&lt;&gt;"",VLOOKUP(G38,'Caractéristique navire de pêche'!$B:$E,3,0),"")</f>
-        <v/>
-      </c>
-      <c r="N38" t="str">
-        <f>IF(G38&lt;&gt;"",VLOOKUP(G38,'[1]caractéristiques Navire de pêch'!$B:$E,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="O38" t="str">
-        <f>IF(G38&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(G38,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(G38,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(G38,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</f>
-        <v/>
-      </c>
-      <c r="P38" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q38" t="str">
-        <f>IF(B38&lt;&gt;"",IF(B38="Entrée",0.366,0.228),"")</f>
-        <v/>
-      </c>
-      <c r="R38" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="S38" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="T38" t="str" cm="1">
-        <f t="array" ref="T38">IF(G38&lt;&gt;"",IF(COUNTIFS($G$2:G38,G38,$H$2:H38,"&gt;="&amp;DATE(YEAR(H38),1,1),$H$2:H38,"&lt;="&amp;DATE(YEAR(Q:QH38),12,31))&lt;=6,0,IF(COUNTIFS($G$2:G38,G38,$H$2:H38,"&gt;="&amp;DATE(YEAR(H38),1,1),$H$2:H38,"&lt;="&amp;DATE(YEAR(H38),12,31))&lt;=15,-0.1,IF(COUNTIFS($G$2:G38,G38,$H$2:H38,"&gt;="&amp;DATE(YEAR(H38),1,1),$H$2:H38,"&lt;="&amp;DATE(YEAR(H38),12,31))&lt;=30,-0.15,IF(COUNTIFS($G$2:G38,G38,$H$2:H38,"&gt;="&amp;DATE(YEAR(H38),1,1),$H$2:H38,"&lt;="&amp;DATE(YEAR(H38),12,31))&lt;=60,-0.2,IF(COUNTIFS($G$2:G38,G38,$H$2:H38,"&gt;="&amp;DATE(YEAR(H38),1,1),$H$2:H38,"&lt;="&amp;DATE(YEAR(H38),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
-        <v/>
-      </c>
-      <c r="U38" t="str">
-        <f>IF(G38&lt;&gt;"",0,"")</f>
-        <v/>
-      </c>
-      <c r="V38" t="str">
-        <f>IF(AND(G38&lt;&gt;"",B38="Entrée"),65,"")</f>
-        <v/>
-      </c>
-      <c r="W38" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="X38" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Z38" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Format incorrect " error="Veuillez entrer le tonnage en tonnes uniquement " promptTitle="Tonnage" prompt="Entrez le tonnage en tonnes (ex:1,5 pour 1,5 tonnes)" sqref="L1:L1048576" xr:uid="{1DC9575D-39AB-4BCE-839B-E9908BB5F13D}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Format incorrect " error="Veuillez entrer le tonnage en tonnes uniquement " promptTitle="Tonnage" prompt="Entrez le tonnage en tonnes (ex:1,5 pour 1,5 tonnes)" sqref="J1:J1048576" xr:uid="{1DC9575D-39AB-4BCE-839B-E9908BB5F13D}">
       <formula1>0</formula1>
       <formula2>50</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{2734802A-40BB-4A87-BEAF-4E02CCBB6D81}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{2734802A-40BB-4A87-BEAF-4E02CCBB6D81}">
       <formula1>"DSK Fish,Poissonnerie Bapte,Delta Transit"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{354C5369-856C-4B47-87A2-14D6AB54ABF4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{354C5369-856C-4B47-87A2-14D6AB54ABF4}">
       <formula1>"PATHFINDER,NATHALIA,SAMANTHA DEL VALLEE;ARACELYS MARIA,EL SUR,DON CRUZ,QUEEN MARY,MARIA CELIS 3;MARIA CELIS 2,MARIA CELIS 4,MAYELEWO,EL SUR,DON FAUSTINO"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:F2" xr:uid="{CD4E53B9-1C11-42A8-B01E-2460C3DFF017}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:D2" xr:uid="{CD4E53B9-1C11-42A8-B01E-2460C3DFF017}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3627,27 +3577,27 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75">
       <c r="A1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="8">
         <v>14.5</v>
@@ -3661,10 +3611,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="8">
         <v>0</v>
@@ -3678,10 +3628,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8">
         <v>0</v>
@@ -3695,10 +3645,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -3712,10 +3662,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="8">
         <v>0</v>
@@ -3729,10 +3679,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -3746,10 +3696,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="8">
         <v>0</v>
@@ -3763,10 +3713,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -3780,10 +3730,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="8">
         <v>0</v>
@@ -3797,10 +3747,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -3814,10 +3764,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="8">
         <v>0</v>
@@ -3831,10 +3781,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -3848,10 +3798,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="8">
         <v>0</v>
@@ -3865,10 +3815,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="11">
         <v>0</v>
@@ -3907,18 +3857,18 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="str">
         <f>IF(C2&lt;&gt;"",VLOOKUP(C2,Tableau3[#All],2,0),"")</f>
@@ -3927,18 +3877,18 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
         <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C99A07A-CEC1-4B14-BF80-B85A651C1A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F45FAF8-17BF-4523-BAE7-C39DC4DC61A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Tirant d'eau </t>
   </si>
   <si>
-    <t xml:space="preserve">Volumme Taxable </t>
+    <t xml:space="preserve">Volume Taxable </t>
   </si>
   <si>
     <t>Taux de base</t>
@@ -647,7 +647,7 @@
     <tableColumn id="11" xr3:uid="{EC156DA3-0E82-4235-9B4A-22111E6FA722}" name="Tirant d'eau " dataDxfId="19">
       <calculatedColumnFormula>IF(E2&lt;&gt;"",_xlfn.LET(_xlpm.te_reel,VLOOKUP(E2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],4,0),_xlpm.longueur,VLOOKUP(E2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],2,0),_xlpm.largeur,VLOOKUP(E2,Tableau13[[#All],[Nom du Navire ]:[Tirant d''eau (m)]],3,0),_xlpm.te_theorique,0.14*SQRT(_xlpm.longueur*_xlpm.largeur),IF(_xlpm.te_reel&gt;=_xlpm.te_theorique,_xlpm.te_reel,ROUND(_xlpm.te_theorique,2))),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E235AE5E-5CC0-4585-9C97-1A0132BF1A07}" name="Volumme Taxable " dataDxfId="18">
+    <tableColumn id="9" xr3:uid="{E235AE5E-5CC0-4585-9C97-1A0132BF1A07}" name="Volume Taxable " dataDxfId="18">
       <calculatedColumnFormula>IF(AND(K2&lt;&gt;"",L2&lt;&gt;"",M2&lt;&gt;""),ROUNDUP(L2*K2*M2,0),"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{C0833D6E-2308-40FA-AD74-2CA2B2ABDF2C}" name="Taux de base" dataDxfId="17">

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F45FAF8-17BF-4523-BAE7-C39DC4DC61A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B05AF42-84A1-4AD9-8E9D-F5CFE9017736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="53">
   <si>
     <t xml:space="preserve">Mouvement </t>
   </si>
@@ -156,16 +156,16 @@
     <t>Tirant d'eau (m)</t>
   </si>
   <si>
+    <t>DON FAUSTINO</t>
+  </si>
+  <si>
+    <t>Delta Transit</t>
+  </si>
+  <si>
+    <t>DON CRUZ</t>
+  </si>
+  <si>
     <t>EL SUR</t>
-  </si>
-  <si>
-    <t>DON FAUSTINO</t>
-  </si>
-  <si>
-    <t>Delta Transit</t>
-  </si>
-  <si>
-    <t>DON CRUZ</t>
   </si>
   <si>
     <t>ARACELYS MARIA</t>
@@ -686,8 +686,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EF6C966-3BDB-42E8-860E-1440AB71A0E5}" name="Tableau13" displayName="Tableau13" ref="A1:E15" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E15" xr:uid="{5EF6C966-3BDB-42E8-860E-1440AB71A0E5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EF6C966-3BDB-42E8-860E-1440AB71A0E5}" name="Tableau13" displayName="Tableau13" ref="A1:E14" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E14" xr:uid="{5EF6C966-3BDB-42E8-860E-1440AB71A0E5}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FEF8928F-5632-49AC-8AA4-1B2179228900}" name="Compagnie " dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{04650E0C-BE4E-4678-A0DD-1DFA856CD2D2}" name="Nom du Navire " dataDxfId="3"/>
@@ -3547,7 +3547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED48872-91E8-49A7-BF70-883F96B227DE}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -3599,72 +3599,72 @@
         <v>33</v>
       </c>
       <c r="C3" s="8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D3" s="8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="E3" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D4" s="8">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="E4" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="8">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="D5" s="8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="E5" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6" s="8">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="D6" s="8">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="E6" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="8">
         <v>0</v>
@@ -3695,36 +3695,36 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D9" s="8">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="E9" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C10" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D10" s="8">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="E10" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3732,7 +3732,7 @@
         <v>41</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>41</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" s="8">
         <v>0</v>
@@ -3766,7 +3766,7 @@
         <v>41</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -3779,45 +3779,28 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="7" t="s">
-        <v>41</v>
+      <c r="A14" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="8">
+        <v>46</v>
+      </c>
+      <c r="C14" s="11">
         <v>0</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="12">
         <v>0</v>
       </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="11">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12">
-        <v>0</v>
-      </c>
-      <c r="E15" s="10">
+      <c r="E14" s="10">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{E2910900-9C30-4A18-9496-476E3FB8CC0C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A14" xr:uid="{E2910900-9C30-4A18-9496-476E3FB8CC0C}">
       <formula1>"DSK Fish,Poissonnerie Bapte,Delta Transit"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{9CBFDF41-04DC-4A2C-BFA5-AF229712E91E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B14" xr:uid="{9CBFDF41-04DC-4A2C-BFA5-AF229712E91E}">
       <formula1>"LA DIOSA,PATHFINDER,NATHALIA,SAMANTHA DEL VALLEE,ARACELYS MARIA,EL SUR,DON CRUZ,QUEEN MARY,MARIA CELIS 3,MARIA CELIS 2,MARIA CELIS 4,MAYELEWO,EL SUR,DON FAUSTINO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B05AF42-84A1-4AD9-8E9D-F5CFE9017736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE7610DA-3FC3-42A1-AE5A-8B433C358D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Declaration" sheetId="1" r:id="rId1"/>
@@ -254,7 +254,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -366,20 +366,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -394,7 +385,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3786,13 +3776,13 @@
         <v>46</v>
       </c>
       <c r="C14" s="11">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12">
-        <v>0</v>
+        <v>13.9</v>
+      </c>
+      <c r="D14" s="9">
+        <v>4.7</v>
       </c>
       <c r="E14" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE7610DA-3FC3-42A1-AE5A-8B433C358D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C4D9DE1-3B8A-4A20-9140-90A2A7987847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -220,7 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,16 +245,28 @@
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF104861"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -366,11 +378,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -385,6 +412,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3540,8 +3569,8 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
     <col min="3" max="3" width="27.5703125" customWidth="1"/>
     <col min="4" max="4" width="26.42578125" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" customWidth="1"/>
@@ -3605,14 +3634,14 @@
       <c r="B4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="8">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0</v>
+      <c r="C4" s="12">
+        <v>18.5</v>
+      </c>
+      <c r="D4" s="12">
+        <v>5.18</v>
+      </c>
+      <c r="E4" s="12">
+        <v>2.4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3639,14 +3668,14 @@
       <c r="B6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="8">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0</v>
+      <c r="C6" s="13">
+        <v>18.7</v>
+      </c>
+      <c r="D6" s="13">
+        <v>5.45</v>
+      </c>
+      <c r="E6" s="13">
+        <v>2.5</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3656,14 +3685,14 @@
       <c r="B7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
+      <c r="C7" s="13">
+        <v>17.8</v>
+      </c>
+      <c r="D7" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1.97</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3707,14 +3736,14 @@
       <c r="B10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0</v>
+      <c r="C10" s="13">
+        <v>14.2</v>
+      </c>
+      <c r="D10" s="13">
+        <v>4.57</v>
+      </c>
+      <c r="E10" s="13">
+        <v>2.13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3742,7 +3771,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="8">
-        <v>0</v>
+        <v>18.77</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C4D9DE1-3B8A-4A20-9140-90A2A7987847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.vaillant.GPHUB\Documents\GPMLM\SDDEP\Stage\Stage 2026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D5972E-C4C1-4C96-8AF2-DD2DC40F8E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-6630" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Declaration" sheetId="1" r:id="rId1"/>
@@ -220,7 +225,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,28 +250,16 @@
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF104861"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
-        <bgColor rgb="FFC0E6F5"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -378,26 +371,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -412,8 +390,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -730,9 +706,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -770,7 +746,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -876,7 +852,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1018,7 +994,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1027,34 +1003,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" customWidth="1"/>
-    <col min="3" max="3" width="48.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" customWidth="1"/>
+    <col min="3" max="3" width="48.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="18.7265625" customWidth="1"/>
+    <col min="6" max="6" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.7265625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="32" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" customWidth="1"/>
     <col min="19" max="19" width="28" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.140625" customWidth="1"/>
+    <col min="20" max="20" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75">
+    <row r="1" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1128,7 +1104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1166,11 +1142,11 @@
         <v>115</v>
       </c>
       <c r="O2">
-        <f>IF(A2&lt;&gt;"",IF(A2="Entrée",0.366,0.228),"")</f>
+        <f t="shared" ref="O2:O38" si="2">IF(A2&lt;&gt;"",IF(A2="Entrée",0.366,0.228),"")</f>
         <v>0.36599999999999999</v>
       </c>
       <c r="P2">
-        <f t="shared" ref="P2:P38" si="2">IF(AND(N2&lt;&gt;"",O2&lt;&gt;""),ROUNDUP(N2*O2,2),"")</f>
+        <f t="shared" ref="P2:P38" si="3">IF(AND(N2&lt;&gt;"",O2&lt;&gt;""),ROUNDUP(N2*O2,2),"")</f>
         <v>42.09</v>
       </c>
       <c r="Q2">
@@ -1178,35 +1154,35 @@
         <v>-0.6</v>
       </c>
       <c r="R2" cm="1">
-        <f t="array" aca="1" ref="R2" ca="1">IF(E2&lt;&gt;"",IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(Q:QF2),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <f t="array" ref="R2">IF(E2&lt;&gt;"",IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(Q:QF2),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
         <v>0</v>
       </c>
       <c r="S2">
-        <f>IF(E2&lt;&gt;"",0,"")</f>
+        <f t="shared" ref="S2:S38" si="4">IF(E2&lt;&gt;"",0,"")</f>
         <v>0</v>
       </c>
       <c r="T2">
-        <f>IF(AND(E2&lt;&gt;"",A2="Entrée"),65,"")</f>
+        <f t="shared" ref="T2:T38" si="5">IF(AND(E2&lt;&gt;"",A2="Entrée"),65,"")</f>
         <v>65</v>
       </c>
       <c r="U2">
-        <f t="shared" ref="U2:U38" si="3">IF(AND(P2&lt;&gt;"",Q2&lt;&gt;""),ROUNDUP(P2*(1+Q2),2),"")</f>
+        <f t="shared" ref="U2:U38" si="6">IF(AND(P2&lt;&gt;"",Q2&lt;&gt;""),ROUNDUP(P2*(1+Q2),2),"")</f>
         <v>16.84</v>
       </c>
       <c r="V2">
-        <f t="shared" ref="V2:V38" si="4">IF(U2&lt;&gt;"",U2+T2,"")</f>
+        <f t="shared" ref="V2:V38" si="7">IF(U2&lt;&gt;"",U2+T2,"")</f>
         <v>81.84</v>
       </c>
       <c r="W2">
-        <f t="shared" ref="W2:W38" si="5">IF(V2&lt;&gt;"",IF(V2&lt;9,0,IF(V2&lt;=16,16,V2)),"")</f>
+        <f t="shared" ref="W2:W38" si="8">IF(V2&lt;&gt;"",IF(V2&lt;9,0,IF(V2&lt;=16,16,V2)),"")</f>
         <v>81.84</v>
       </c>
       <c r="X2">
-        <f t="shared" ref="X2:X38" si="6">IF(W2&lt;&gt;"",W2,"")</f>
+        <f t="shared" ref="X2:X38" si="9">IF(W2&lt;&gt;"",W2,"")</f>
         <v>81.84</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C3" t="str">
         <f>IF(B3&lt;&gt;"",VLOOKUP(B3,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1228,15 +1204,15 @@
         <v/>
       </c>
       <c r="O3" t="str">
-        <f>IF(A3&lt;&gt;"",IF(A3="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q38" si="7">IF(AND(J3&lt;&gt;"",N3&lt;&gt;""),IF(J3/N3&gt;2/15,0,IF(J3/N3&gt;1/10,-0.1,IF(J3/N3&gt;1/20,-0.3,IF(J3/N3&gt;1/40,-0.5,IF(J3/N3&gt;1/100,-0.6,IF(J3/N3&gt;1/250,-0.7,IF(J3/N3&gt;1/500,-0.8,-0.95))))))),"")</f>
+        <f t="shared" ref="Q3:Q38" si="10">IF(AND(J3&lt;&gt;"",N3&lt;&gt;""),IF(J3/N3&gt;2/15,0,IF(J3/N3&gt;1/10,-0.1,IF(J3/N3&gt;1/20,-0.3,IF(J3/N3&gt;1/40,-0.5,IF(J3/N3&gt;1/100,-0.6,IF(J3/N3&gt;1/250,-0.7,IF(J3/N3&gt;1/500,-0.8,-0.95))))))),"")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -1244,31 +1220,31 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <f>IF(E3&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T3" t="str">
-        <f>IF(AND(E3&lt;&gt;"",A3="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V3" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X3" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C4" t="str">
         <f>IF(B4&lt;&gt;"",VLOOKUP(B4,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1293,15 +1269,15 @@
         <v/>
       </c>
       <c r="O4" t="str">
-        <f>IF(A4&lt;&gt;"",IF(A4="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R4" t="str" cm="1">
@@ -1309,31 +1285,31 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <f>IF(E4&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T4" t="str">
-        <f>IF(AND(E4&lt;&gt;"",A4="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C5" t="str">
         <f>IF(B5&lt;&gt;"",VLOOKUP(B5,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1358,15 +1334,15 @@
         <v/>
       </c>
       <c r="O5" t="str">
-        <f>IF(A5&lt;&gt;"",IF(A5="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R5" t="str" cm="1">
@@ -1374,31 +1350,31 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <f>IF(E5&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T5" t="str">
-        <f>IF(AND(E5&lt;&gt;"",A5="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C6" t="str">
         <f>IF(B6&lt;&gt;"",VLOOKUP(B6,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1423,15 +1399,15 @@
         <v/>
       </c>
       <c r="O6" t="str">
-        <f>IF(A6&lt;&gt;"",IF(A6="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R6" t="str" cm="1">
@@ -1439,31 +1415,31 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <f>IF(E6&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T6" t="str">
-        <f>IF(AND(E6&lt;&gt;"",A6="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C7" t="str">
         <f>IF(B7&lt;&gt;"",VLOOKUP(B7,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1488,15 +1464,15 @@
         <v/>
       </c>
       <c r="O7" t="str">
-        <f>IF(A7&lt;&gt;"",IF(A7="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R7" t="str" cm="1">
@@ -1504,31 +1480,31 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <f>IF(E7&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T7" t="str">
-        <f>IF(AND(E7&lt;&gt;"",A7="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C8" t="str">
         <f>IF(B8&lt;&gt;"",VLOOKUP(B8,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1553,15 +1529,15 @@
         <v/>
       </c>
       <c r="O8" t="str">
-        <f>IF(A8&lt;&gt;"",IF(A8="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q8" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R8" t="str" cm="1">
@@ -1569,31 +1545,31 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <f>IF(E8&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T8" t="str">
-        <f>IF(AND(E8&lt;&gt;"",A8="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U8" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V8" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X8" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C9" t="str">
         <f>IF(B9&lt;&gt;"",VLOOKUP(B9,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1618,15 +1594,15 @@
         <v/>
       </c>
       <c r="O9" t="str">
-        <f>IF(A9&lt;&gt;"",IF(A9="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R9" t="str" cm="1">
@@ -1634,31 +1610,31 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <f>IF(E9&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T9" t="str">
-        <f>IF(AND(E9&lt;&gt;"",A9="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U9" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X9" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C10" t="str">
         <f>IF(B10&lt;&gt;"",VLOOKUP(B10,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1683,15 +1659,15 @@
         <v/>
       </c>
       <c r="O10" t="str">
-        <f>IF(A10&lt;&gt;"",IF(A10="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R10" t="str" cm="1">
@@ -1699,31 +1675,31 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <f>IF(E10&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T10" t="str">
-        <f>IF(AND(E10&lt;&gt;"",A10="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C11" t="str">
         <f>IF(B11&lt;&gt;"",VLOOKUP(B11,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1748,15 +1724,15 @@
         <v/>
       </c>
       <c r="O11" t="str">
-        <f>IF(A11&lt;&gt;"",IF(A11="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R11" t="str" cm="1">
@@ -1764,31 +1740,31 @@
         <v/>
       </c>
       <c r="S11" t="str">
-        <f>IF(E11&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T11" t="str">
-        <f>IF(AND(E11&lt;&gt;"",A11="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V11" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W11" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X11" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C12" t="str">
         <f>IF(B12&lt;&gt;"",VLOOKUP(B12,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1813,15 +1789,15 @@
         <v/>
       </c>
       <c r="O12" t="str">
-        <f>IF(A12&lt;&gt;"",IF(A12="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R12" t="str" cm="1">
@@ -1829,31 +1805,31 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <f>IF(E12&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T12" t="str">
-        <f>IF(AND(E12&lt;&gt;"",A12="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C13" t="str">
         <f>IF(B13&lt;&gt;"",VLOOKUP(B13,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1878,15 +1854,15 @@
         <v/>
       </c>
       <c r="O13" t="str">
-        <f>IF(A13&lt;&gt;"",IF(A13="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q13" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R13" t="str" cm="1">
@@ -1894,31 +1870,31 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <f>IF(E13&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T13" t="str">
-        <f>IF(AND(E13&lt;&gt;"",A13="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C14" t="str">
         <f>IF(B14&lt;&gt;"",VLOOKUP(B14,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1943,15 +1919,15 @@
         <v/>
       </c>
       <c r="O14" t="str">
-        <f>IF(A14&lt;&gt;"",IF(A14="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R14" t="str" cm="1">
@@ -1959,31 +1935,31 @@
         <v/>
       </c>
       <c r="S14" t="str">
-        <f>IF(E14&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T14" t="str">
-        <f>IF(AND(E14&lt;&gt;"",A14="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C15" t="str">
         <f>IF(B15&lt;&gt;"",VLOOKUP(B15,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2008,15 +1984,15 @@
         <v/>
       </c>
       <c r="O15" t="str">
-        <f>IF(A15&lt;&gt;"",IF(A15="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R15" t="str" cm="1">
@@ -2024,31 +2000,31 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <f>IF(E15&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T15" t="str">
-        <f>IF(AND(E15&lt;&gt;"",A15="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C16" t="str">
         <f>IF(B16&lt;&gt;"",VLOOKUP(B16,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2073,15 +2049,15 @@
         <v/>
       </c>
       <c r="O16" t="str">
-        <f>IF(A16&lt;&gt;"",IF(A16="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q16" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R16" t="str" cm="1">
@@ -2089,31 +2065,31 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <f>IF(E16&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T16" t="str">
-        <f>IF(AND(E16&lt;&gt;"",A16="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C17" t="str">
         <f>IF(B17&lt;&gt;"",VLOOKUP(B17,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2138,15 +2114,15 @@
         <v/>
       </c>
       <c r="O17" t="str">
-        <f>IF(A17&lt;&gt;"",IF(A17="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q17" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R17" t="str" cm="1">
@@ -2154,31 +2130,31 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <f>IF(E17&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T17" t="str">
-        <f>IF(AND(E17&lt;&gt;"",A17="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X17" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C18" t="str">
         <f>IF(B18&lt;&gt;"",VLOOKUP(B18,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2203,15 +2179,15 @@
         <v/>
       </c>
       <c r="O18" t="str">
-        <f>IF(A18&lt;&gt;"",IF(A18="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q18" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R18" t="str" cm="1">
@@ -2219,31 +2195,31 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <f>IF(E18&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T18" t="str">
-        <f>IF(AND(E18&lt;&gt;"",A18="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V18" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W18" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C19" t="str">
         <f>IF(B19&lt;&gt;"",VLOOKUP(B19,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2268,15 +2244,15 @@
         <v/>
       </c>
       <c r="O19" t="str">
-        <f>IF(A19&lt;&gt;"",IF(A19="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q19" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R19" t="str" cm="1">
@@ -2284,31 +2260,31 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <f>IF(E19&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T19" t="str">
-        <f>IF(AND(E19&lt;&gt;"",A19="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U19" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V19" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X19" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C20" t="str">
         <f>IF(B20&lt;&gt;"",VLOOKUP(B20,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2333,15 +2309,15 @@
         <v/>
       </c>
       <c r="O20" t="str">
-        <f>IF(A20&lt;&gt;"",IF(A20="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q20" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R20" t="str" cm="1">
@@ -2349,31 +2325,31 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <f>IF(E20&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T20" t="str">
-        <f>IF(AND(E20&lt;&gt;"",A20="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V20" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C21" t="str">
         <f>IF(B21&lt;&gt;"",VLOOKUP(B21,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2398,15 +2374,15 @@
         <v/>
       </c>
       <c r="O21" t="str">
-        <f>IF(A21&lt;&gt;"",IF(A21="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R21" t="str" cm="1">
@@ -2414,31 +2390,31 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <f>IF(E21&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T21" t="str">
-        <f>IF(AND(E21&lt;&gt;"",A21="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C22" t="str">
         <f>IF(B22&lt;&gt;"",VLOOKUP(B22,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2463,15 +2439,15 @@
         <v/>
       </c>
       <c r="O22" t="str">
-        <f>IF(A22&lt;&gt;"",IF(A22="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R22" t="str" cm="1">
@@ -2479,31 +2455,31 @@
         <v/>
       </c>
       <c r="S22" t="str">
-        <f>IF(E22&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T22" t="str">
-        <f>IF(AND(E22&lt;&gt;"",A22="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U22" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X22" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C23" t="str">
         <f>IF(B23&lt;&gt;"",VLOOKUP(B23,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2528,15 +2504,15 @@
         <v/>
       </c>
       <c r="O23" t="str">
-        <f>IF(A23&lt;&gt;"",IF(A23="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R23" t="str" cm="1">
@@ -2544,31 +2520,31 @@
         <v/>
       </c>
       <c r="S23" t="str">
-        <f>IF(E23&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T23" t="str">
-        <f>IF(AND(E23&lt;&gt;"",A23="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V23" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X23" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C24" t="str">
         <f>IF(B24&lt;&gt;"",VLOOKUP(B24,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2593,15 +2569,15 @@
         <v/>
       </c>
       <c r="O24" t="str">
-        <f>IF(A24&lt;&gt;"",IF(A24="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q24" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R24" t="str" cm="1">
@@ -2609,31 +2585,31 @@
         <v/>
       </c>
       <c r="S24" t="str">
-        <f>IF(E24&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T24" t="str">
-        <f>IF(AND(E24&lt;&gt;"",A24="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U24" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V24" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W24" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C25" t="str">
         <f>IF(B25&lt;&gt;"",VLOOKUP(B25,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2658,15 +2634,15 @@
         <v/>
       </c>
       <c r="O25" t="str">
-        <f>IF(A25&lt;&gt;"",IF(A25="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q25" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R25" t="str" cm="1">
@@ -2674,31 +2650,31 @@
         <v/>
       </c>
       <c r="S25" t="str">
-        <f>IF(E25&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T25" t="str">
-        <f>IF(AND(E25&lt;&gt;"",A25="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U25" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V25" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X25" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C26" t="str">
         <f>IF(B26&lt;&gt;"",VLOOKUP(B26,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2723,15 +2699,15 @@
         <v/>
       </c>
       <c r="O26" t="str">
-        <f>IF(A26&lt;&gt;"",IF(A26="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q26" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R26" t="str" cm="1">
@@ -2739,31 +2715,31 @@
         <v/>
       </c>
       <c r="S26" t="str">
-        <f>IF(E26&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T26" t="str">
-        <f>IF(AND(E26&lt;&gt;"",A26="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U26" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V26" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W26" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X26" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C27" t="str">
         <f>IF(B27&lt;&gt;"",VLOOKUP(B27,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2788,15 +2764,15 @@
         <v/>
       </c>
       <c r="O27" t="str">
-        <f>IF(A27&lt;&gt;"",IF(A27="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q27" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R27" t="str" cm="1">
@@ -2804,31 +2780,31 @@
         <v/>
       </c>
       <c r="S27" t="str">
-        <f>IF(E27&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T27" t="str">
-        <f>IF(AND(E27&lt;&gt;"",A27="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U27" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V27" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W27" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X27" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C28" t="str">
         <f>IF(B28&lt;&gt;"",VLOOKUP(B28,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2853,15 +2829,15 @@
         <v/>
       </c>
       <c r="O28" t="str">
-        <f>IF(A28&lt;&gt;"",IF(A28="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q28" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R28" t="str" cm="1">
@@ -2869,31 +2845,31 @@
         <v/>
       </c>
       <c r="S28" t="str">
-        <f>IF(E28&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T28" t="str">
-        <f>IF(AND(E28&lt;&gt;"",A28="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U28" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V28" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W28" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X28" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C29" t="str">
         <f>IF(B29&lt;&gt;"",VLOOKUP(B29,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2918,15 +2894,15 @@
         <v/>
       </c>
       <c r="O29" t="str">
-        <f>IF(A29&lt;&gt;"",IF(A29="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q29" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R29" t="str" cm="1">
@@ -2934,31 +2910,31 @@
         <v/>
       </c>
       <c r="S29" t="str">
-        <f>IF(E29&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T29" t="str">
-        <f>IF(AND(E29&lt;&gt;"",A29="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U29" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W29" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X29" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C30" t="str">
         <f>IF(B30&lt;&gt;"",VLOOKUP(B30,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2983,15 +2959,15 @@
         <v/>
       </c>
       <c r="O30" t="str">
-        <f>IF(A30&lt;&gt;"",IF(A30="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R30" t="str" cm="1">
@@ -2999,31 +2975,31 @@
         <v/>
       </c>
       <c r="S30" t="str">
-        <f>IF(E30&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T30" t="str">
-        <f>IF(AND(E30&lt;&gt;"",A30="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U30" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X30" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C31" t="str">
         <f>IF(B31&lt;&gt;"",VLOOKUP(B31,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3048,15 +3024,15 @@
         <v/>
       </c>
       <c r="O31" t="str">
-        <f>IF(A31&lt;&gt;"",IF(A31="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q31" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R31" t="str" cm="1">
@@ -3064,31 +3040,31 @@
         <v/>
       </c>
       <c r="S31" t="str">
-        <f>IF(E31&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T31" t="str">
-        <f>IF(AND(E31&lt;&gt;"",A31="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V31" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W31" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X31" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C32" t="str">
         <f>IF(B32&lt;&gt;"",VLOOKUP(B32,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3113,15 +3089,15 @@
         <v/>
       </c>
       <c r="O32" t="str">
-        <f>IF(A32&lt;&gt;"",IF(A32="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R32" t="str" cm="1">
@@ -3129,31 +3105,31 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <f>IF(E32&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T32" t="str">
-        <f>IF(AND(E32&lt;&gt;"",A32="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V32" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W32" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X32" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C33" t="str">
         <f>IF(B33&lt;&gt;"",VLOOKUP(B33,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3178,15 +3154,15 @@
         <v/>
       </c>
       <c r="O33" t="str">
-        <f>IF(A33&lt;&gt;"",IF(A33="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R33" t="str" cm="1">
@@ -3194,31 +3170,31 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <f>IF(E33&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T33" t="str">
-        <f>IF(AND(E33&lt;&gt;"",A33="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V33" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W33" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X33" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C34" t="str">
         <f>IF(B34&lt;&gt;"",VLOOKUP(B34,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3243,15 +3219,15 @@
         <v/>
       </c>
       <c r="O34" t="str">
-        <f>IF(A34&lt;&gt;"",IF(A34="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R34" t="str" cm="1">
@@ -3259,31 +3235,31 @@
         <v/>
       </c>
       <c r="S34" t="str">
-        <f>IF(E34&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T34" t="str">
-        <f>IF(AND(E34&lt;&gt;"",A34="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U34" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X34" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C35" t="str">
         <f>IF(B35&lt;&gt;"",VLOOKUP(B35,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3308,15 +3284,15 @@
         <v/>
       </c>
       <c r="O35" t="str">
-        <f>IF(A35&lt;&gt;"",IF(A35="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P35" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q35" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R35" t="str" cm="1">
@@ -3324,31 +3300,31 @@
         <v/>
       </c>
       <c r="S35" t="str">
-        <f>IF(E35&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T35" t="str">
-        <f>IF(AND(E35&lt;&gt;"",A35="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X35" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C36" t="str">
         <f>IF(B36&lt;&gt;"",VLOOKUP(B36,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3373,15 +3349,15 @@
         <v/>
       </c>
       <c r="O36" t="str">
-        <f>IF(A36&lt;&gt;"",IF(A36="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P36" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R36" t="str" cm="1">
@@ -3389,31 +3365,31 @@
         <v/>
       </c>
       <c r="S36" t="str">
-        <f>IF(E36&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T36" t="str">
-        <f>IF(AND(E36&lt;&gt;"",A36="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W36" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X36" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C37" t="str">
         <f>IF(B37&lt;&gt;"",VLOOKUP(B37,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3438,15 +3414,15 @@
         <v/>
       </c>
       <c r="O37" t="str">
-        <f>IF(A37&lt;&gt;"",IF(A37="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P37" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R37" t="str" cm="1">
@@ -3454,31 +3430,31 @@
         <v/>
       </c>
       <c r="S37" t="str">
-        <f>IF(E37&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T37" t="str">
-        <f>IF(AND(E37&lt;&gt;"",A37="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V37" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W37" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X37" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="3:24">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C38" t="str">
         <f>IF(B38&lt;&gt;"",VLOOKUP(B38,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3503,15 +3479,15 @@
         <v/>
       </c>
       <c r="O38" t="str">
-        <f>IF(A38&lt;&gt;"",IF(A38="Entrée",0.366,0.228),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P38" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R38" t="str" cm="1">
@@ -3519,27 +3495,27 @@
         <v/>
       </c>
       <c r="S38" t="str">
-        <f>IF(E38&lt;&gt;"",0,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T38" t="str">
-        <f>IF(AND(E38&lt;&gt;"",A38="Entrée"),65,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="U38" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="V38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="W38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="X38" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3567,16 +3543,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED48872-91E8-49A7-BF70-883F96B227DE}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" customWidth="1"/>
+    <col min="4" max="4" width="26.453125" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75">
+    <row r="1" spans="1:5" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
@@ -3593,7 +3569,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
@@ -3610,7 +3586,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>25</v>
       </c>
@@ -3627,24 +3603,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="12">
-        <v>18.5</v>
-      </c>
-      <c r="D4" s="12">
-        <v>5.18</v>
-      </c>
-      <c r="E4" s="12">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="C4" s="8">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>34</v>
       </c>
@@ -3661,41 +3637,41 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="13">
-        <v>18.7</v>
-      </c>
-      <c r="D6" s="13">
-        <v>5.45</v>
-      </c>
-      <c r="E6" s="13">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="C6" s="8">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8">
+        <v>20</v>
+      </c>
+      <c r="E6" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="13">
-        <v>17.8</v>
-      </c>
-      <c r="D7" s="13">
-        <v>5.3</v>
-      </c>
-      <c r="E7" s="13">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
@@ -3712,7 +3688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
@@ -3729,24 +3705,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="13">
-        <v>14.2</v>
-      </c>
-      <c r="D10" s="13">
-        <v>4.57</v>
-      </c>
-      <c r="E10" s="13">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="C10" s="8">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -3763,7 +3739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -3771,7 +3747,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="8">
-        <v>18.77</v>
+        <v>0</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>
@@ -3780,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -3797,7 +3773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
@@ -3833,13 +3809,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB195B26-F7E2-4470-95CE-93C18E346372}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="74.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" customWidth="1"/>
+    <col min="2" max="2" width="74.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>47</v>
       </c>
@@ -3847,7 +3823,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -3859,7 +3835,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -3867,7 +3843,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>51</v>
       </c>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.vaillant.GPHUB\Documents\GPMLM\SDDEP\Stage\Stage 2026\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D5972E-C4C1-4C96-8AF2-DD2DC40F8E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C4D9DE1-3B8A-4A20-9140-90A2A7987847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-6630" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Declaration" sheetId="1" r:id="rId1"/>
@@ -225,7 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,16 +245,28 @@
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF104861"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -371,11 +378,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -390,6 +412,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -706,9 +730,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -746,7 +770,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -852,7 +876,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -994,7 +1018,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1003,34 +1027,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" customWidth="1"/>
-    <col min="3" max="3" width="48.81640625" customWidth="1"/>
-    <col min="4" max="4" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="18.7265625" customWidth="1"/>
-    <col min="6" max="6" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="48.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="32" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" customWidth="1"/>
     <col min="19" max="19" width="28" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.1796875" customWidth="1"/>
+    <col min="20" max="20" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1104,7 +1128,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1142,11 +1166,11 @@
         <v>115</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:O38" si="2">IF(A2&lt;&gt;"",IF(A2="Entrée",0.366,0.228),"")</f>
+        <f>IF(A2&lt;&gt;"",IF(A2="Entrée",0.366,0.228),"")</f>
         <v>0.36599999999999999</v>
       </c>
       <c r="P2">
-        <f t="shared" ref="P2:P38" si="3">IF(AND(N2&lt;&gt;"",O2&lt;&gt;""),ROUNDUP(N2*O2,2),"")</f>
+        <f t="shared" ref="P2:P38" si="2">IF(AND(N2&lt;&gt;"",O2&lt;&gt;""),ROUNDUP(N2*O2,2),"")</f>
         <v>42.09</v>
       </c>
       <c r="Q2">
@@ -1154,35 +1178,35 @@
         <v>-0.6</v>
       </c>
       <c r="R2" cm="1">
-        <f t="array" ref="R2">IF(E2&lt;&gt;"",IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(Q:QF2),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
+        <f t="array" aca="1" ref="R2" ca="1">IF(E2&lt;&gt;"",IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(Q:QF2),12,31))&lt;=6,0,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=15,-0.1,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=30,-0.15,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=60,-0.2,IF(COUNTIFS($E$2:E2,E2,$F$2:F2,"&gt;="&amp;DATE(YEAR(F2),1,1),$F$2:F2,"&lt;="&amp;DATE(YEAR(F2),12,31))&lt;=120,-0.25,-0.3))))),"")</f>
         <v>0</v>
       </c>
       <c r="S2">
-        <f t="shared" ref="S2:S38" si="4">IF(E2&lt;&gt;"",0,"")</f>
+        <f>IF(E2&lt;&gt;"",0,"")</f>
         <v>0</v>
       </c>
       <c r="T2">
-        <f t="shared" ref="T2:T38" si="5">IF(AND(E2&lt;&gt;"",A2="Entrée"),65,"")</f>
+        <f>IF(AND(E2&lt;&gt;"",A2="Entrée"),65,"")</f>
         <v>65</v>
       </c>
       <c r="U2">
-        <f t="shared" ref="U2:U38" si="6">IF(AND(P2&lt;&gt;"",Q2&lt;&gt;""),ROUNDUP(P2*(1+Q2),2),"")</f>
+        <f t="shared" ref="U2:U38" si="3">IF(AND(P2&lt;&gt;"",Q2&lt;&gt;""),ROUNDUP(P2*(1+Q2),2),"")</f>
         <v>16.84</v>
       </c>
       <c r="V2">
-        <f t="shared" ref="V2:V38" si="7">IF(U2&lt;&gt;"",U2+T2,"")</f>
+        <f t="shared" ref="V2:V38" si="4">IF(U2&lt;&gt;"",U2+T2,"")</f>
         <v>81.84</v>
       </c>
       <c r="W2">
-        <f t="shared" ref="W2:W38" si="8">IF(V2&lt;&gt;"",IF(V2&lt;9,0,IF(V2&lt;=16,16,V2)),"")</f>
+        <f t="shared" ref="W2:W38" si="5">IF(V2&lt;&gt;"",IF(V2&lt;9,0,IF(V2&lt;=16,16,V2)),"")</f>
         <v>81.84</v>
       </c>
       <c r="X2">
-        <f t="shared" ref="X2:X38" si="9">IF(W2&lt;&gt;"",W2,"")</f>
+        <f t="shared" ref="X2:X38" si="6">IF(W2&lt;&gt;"",W2,"")</f>
         <v>81.84</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24">
       <c r="C3" t="str">
         <f>IF(B3&lt;&gt;"",VLOOKUP(B3,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1204,15 +1228,15 @@
         <v/>
       </c>
       <c r="O3" t="str">
+        <f>IF(A3&lt;&gt;"",IF(A3="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q38" si="10">IF(AND(J3&lt;&gt;"",N3&lt;&gt;""),IF(J3/N3&gt;2/15,0,IF(J3/N3&gt;1/10,-0.1,IF(J3/N3&gt;1/20,-0.3,IF(J3/N3&gt;1/40,-0.5,IF(J3/N3&gt;1/100,-0.6,IF(J3/N3&gt;1/250,-0.7,IF(J3/N3&gt;1/500,-0.8,-0.95))))))),"")</f>
+        <f t="shared" ref="Q3:Q38" si="7">IF(AND(J3&lt;&gt;"",N3&lt;&gt;""),IF(J3/N3&gt;2/15,0,IF(J3/N3&gt;1/10,-0.1,IF(J3/N3&gt;1/20,-0.3,IF(J3/N3&gt;1/40,-0.5,IF(J3/N3&gt;1/100,-0.6,IF(J3/N3&gt;1/250,-0.7,IF(J3/N3&gt;1/500,-0.8,-0.95))))))),"")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -1220,31 +1244,31 @@
         <v/>
       </c>
       <c r="S3" t="str">
+        <f>IF(E3&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <f>IF(AND(E3&lt;&gt;"",A3="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T3" t="str">
+      <c r="W3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U3" t="str">
+      <c r="X3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V3" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W3" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:24">
       <c r="C4" t="str">
         <f>IF(B4&lt;&gt;"",VLOOKUP(B4,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1269,15 +1293,15 @@
         <v/>
       </c>
       <c r="O4" t="str">
+        <f>IF(A4&lt;&gt;"",IF(A4="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P4" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R4" t="str" cm="1">
@@ -1285,31 +1309,31 @@
         <v/>
       </c>
       <c r="S4" t="str">
+        <f>IF(E4&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <f>IF(AND(E4&lt;&gt;"",A4="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T4" t="str">
+      <c r="W4" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U4" t="str">
+      <c r="X4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:24">
       <c r="C5" t="str">
         <f>IF(B5&lt;&gt;"",VLOOKUP(B5,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1334,15 +1358,15 @@
         <v/>
       </c>
       <c r="O5" t="str">
+        <f>IF(A5&lt;&gt;"",IF(A5="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P5" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R5" t="str" cm="1">
@@ -1350,31 +1374,31 @@
         <v/>
       </c>
       <c r="S5" t="str">
+        <f>IF(E5&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <f>IF(AND(E5&lt;&gt;"",A5="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V5" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T5" t="str">
+      <c r="W5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U5" t="str">
+      <c r="X5" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V5" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X5" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:24">
       <c r="C6" t="str">
         <f>IF(B6&lt;&gt;"",VLOOKUP(B6,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1399,15 +1423,15 @@
         <v/>
       </c>
       <c r="O6" t="str">
+        <f>IF(A6&lt;&gt;"",IF(A6="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P6" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R6" t="str" cm="1">
@@ -1415,31 +1439,31 @@
         <v/>
       </c>
       <c r="S6" t="str">
+        <f>IF(E6&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <f>IF(AND(E6&lt;&gt;"",A6="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V6" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T6" t="str">
+      <c r="W6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U6" t="str">
+      <c r="X6" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V6" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W6" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X6" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:24">
       <c r="C7" t="str">
         <f>IF(B7&lt;&gt;"",VLOOKUP(B7,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1464,15 +1488,15 @@
         <v/>
       </c>
       <c r="O7" t="str">
+        <f>IF(A7&lt;&gt;"",IF(A7="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P7" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q7" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R7" t="str" cm="1">
@@ -1480,31 +1504,31 @@
         <v/>
       </c>
       <c r="S7" t="str">
+        <f>IF(E7&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <f>IF(AND(E7&lt;&gt;"",A7="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T7" t="str">
+      <c r="W7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U7" t="str">
+      <c r="X7" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V7" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W7" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X7" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:24">
       <c r="C8" t="str">
         <f>IF(B8&lt;&gt;"",VLOOKUP(B8,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1529,15 +1553,15 @@
         <v/>
       </c>
       <c r="O8" t="str">
+        <f>IF(A8&lt;&gt;"",IF(A8="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q8" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R8" t="str" cm="1">
@@ -1545,31 +1569,31 @@
         <v/>
       </c>
       <c r="S8" t="str">
+        <f>IF(E8&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <f>IF(AND(E8&lt;&gt;"",A8="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V8" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T8" t="str">
+      <c r="W8" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U8" t="str">
+      <c r="X8" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V8" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X8" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:24">
       <c r="C9" t="str">
         <f>IF(B9&lt;&gt;"",VLOOKUP(B9,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1594,15 +1618,15 @@
         <v/>
       </c>
       <c r="O9" t="str">
+        <f>IF(A9&lt;&gt;"",IF(A9="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P9" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P9" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R9" t="str" cm="1">
@@ -1610,31 +1634,31 @@
         <v/>
       </c>
       <c r="S9" t="str">
+        <f>IF(E9&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <f>IF(AND(E9&lt;&gt;"",A9="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T9" t="str">
+      <c r="W9" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U9" t="str">
+      <c r="X9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V9" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W9" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X9" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:24">
       <c r="C10" t="str">
         <f>IF(B10&lt;&gt;"",VLOOKUP(B10,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1659,15 +1683,15 @@
         <v/>
       </c>
       <c r="O10" t="str">
+        <f>IF(A10&lt;&gt;"",IF(A10="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R10" t="str" cm="1">
@@ -1675,31 +1699,31 @@
         <v/>
       </c>
       <c r="S10" t="str">
+        <f>IF(E10&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <f>IF(AND(E10&lt;&gt;"",A10="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V10" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T10" t="str">
+      <c r="W10" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U10" t="str">
+      <c r="X10" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W10" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:24">
       <c r="C11" t="str">
         <f>IF(B11&lt;&gt;"",VLOOKUP(B11,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1724,15 +1748,15 @@
         <v/>
       </c>
       <c r="O11" t="str">
+        <f>IF(A11&lt;&gt;"",IF(A11="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P11" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P11" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q11" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R11" t="str" cm="1">
@@ -1740,31 +1764,31 @@
         <v/>
       </c>
       <c r="S11" t="str">
+        <f>IF(E11&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <f>IF(AND(E11&lt;&gt;"",A11="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T11" t="str">
+      <c r="W11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U11" t="str">
+      <c r="X11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V11" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W11" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X11" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:24">
       <c r="C12" t="str">
         <f>IF(B12&lt;&gt;"",VLOOKUP(B12,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1789,15 +1813,15 @@
         <v/>
       </c>
       <c r="O12" t="str">
+        <f>IF(A12&lt;&gt;"",IF(A12="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P12" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q12" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R12" t="str" cm="1">
@@ -1805,31 +1829,31 @@
         <v/>
       </c>
       <c r="S12" t="str">
+        <f>IF(E12&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <f>IF(AND(E12&lt;&gt;"",A12="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V12" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T12" t="str">
+      <c r="W12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U12" t="str">
+      <c r="X12" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V12" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W12" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X12" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:24">
       <c r="C13" t="str">
         <f>IF(B13&lt;&gt;"",VLOOKUP(B13,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1854,15 +1878,15 @@
         <v/>
       </c>
       <c r="O13" t="str">
+        <f>IF(A13&lt;&gt;"",IF(A13="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P13" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R13" t="str" cm="1">
@@ -1870,31 +1894,31 @@
         <v/>
       </c>
       <c r="S13" t="str">
+        <f>IF(E13&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <f>IF(AND(E13&lt;&gt;"",A13="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V13" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T13" t="str">
+      <c r="W13" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U13" t="str">
+      <c r="X13" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V13" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W13" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X13" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:24">
       <c r="C14" t="str">
         <f>IF(B14&lt;&gt;"",VLOOKUP(B14,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1919,15 +1943,15 @@
         <v/>
       </c>
       <c r="O14" t="str">
+        <f>IF(A14&lt;&gt;"",IF(A14="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P14" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P14" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R14" t="str" cm="1">
@@ -1935,31 +1959,31 @@
         <v/>
       </c>
       <c r="S14" t="str">
+        <f>IF(E14&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <f>IF(AND(E14&lt;&gt;"",A14="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V14" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T14" t="str">
+      <c r="W14" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U14" t="str">
+      <c r="X14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V14" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W14" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X14" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:24">
       <c r="C15" t="str">
         <f>IF(B15&lt;&gt;"",VLOOKUP(B15,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1984,15 +2008,15 @@
         <v/>
       </c>
       <c r="O15" t="str">
+        <f>IF(A15&lt;&gt;"",IF(A15="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P15" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R15" t="str" cm="1">
@@ -2000,31 +2024,31 @@
         <v/>
       </c>
       <c r="S15" t="str">
+        <f>IF(E15&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <f>IF(AND(E15&lt;&gt;"",A15="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V15" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T15" t="str">
+      <c r="W15" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U15" t="str">
+      <c r="X15" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V15" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W15" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X15" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:24">
       <c r="C16" t="str">
         <f>IF(B16&lt;&gt;"",VLOOKUP(B16,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2049,15 +2073,15 @@
         <v/>
       </c>
       <c r="O16" t="str">
+        <f>IF(A16&lt;&gt;"",IF(A16="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P16" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q16" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R16" t="str" cm="1">
@@ -2065,31 +2089,31 @@
         <v/>
       </c>
       <c r="S16" t="str">
+        <f>IF(E16&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <f>IF(AND(E16&lt;&gt;"",A16="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T16" t="str">
+      <c r="W16" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U16" t="str">
+      <c r="X16" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X16" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="3:24">
       <c r="C17" t="str">
         <f>IF(B17&lt;&gt;"",VLOOKUP(B17,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2114,15 +2138,15 @@
         <v/>
       </c>
       <c r="O17" t="str">
+        <f>IF(A17&lt;&gt;"",IF(A17="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P17" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P17" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q17" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R17" t="str" cm="1">
@@ -2130,31 +2154,31 @@
         <v/>
       </c>
       <c r="S17" t="str">
+        <f>IF(E17&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <f>IF(AND(E17&lt;&gt;"",A17="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V17" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T17" t="str">
+      <c r="W17" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U17" t="str">
+      <c r="X17" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V17" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W17" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X17" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="3:24">
       <c r="C18" t="str">
         <f>IF(B18&lt;&gt;"",VLOOKUP(B18,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2179,15 +2203,15 @@
         <v/>
       </c>
       <c r="O18" t="str">
+        <f>IF(A18&lt;&gt;"",IF(A18="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P18" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q18" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R18" t="str" cm="1">
@@ -2195,31 +2219,31 @@
         <v/>
       </c>
       <c r="S18" t="str">
+        <f>IF(E18&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <f>IF(AND(E18&lt;&gt;"",A18="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V18" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T18" t="str">
+      <c r="W18" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U18" t="str">
+      <c r="X18" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V18" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X18" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="3:24">
       <c r="C19" t="str">
         <f>IF(B19&lt;&gt;"",VLOOKUP(B19,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2244,15 +2268,15 @@
         <v/>
       </c>
       <c r="O19" t="str">
+        <f>IF(A19&lt;&gt;"",IF(A19="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P19" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P19" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q19" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R19" t="str" cm="1">
@@ -2260,31 +2284,31 @@
         <v/>
       </c>
       <c r="S19" t="str">
+        <f>IF(E19&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <f>IF(AND(E19&lt;&gt;"",A19="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V19" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T19" t="str">
+      <c r="W19" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U19" t="str">
+      <c r="X19" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V19" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W19" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X19" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="3:24">
       <c r="C20" t="str">
         <f>IF(B20&lt;&gt;"",VLOOKUP(B20,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2309,15 +2333,15 @@
         <v/>
       </c>
       <c r="O20" t="str">
+        <f>IF(A20&lt;&gt;"",IF(A20="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P20" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q20" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R20" t="str" cm="1">
@@ -2325,31 +2349,31 @@
         <v/>
       </c>
       <c r="S20" t="str">
+        <f>IF(E20&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <f>IF(AND(E20&lt;&gt;"",A20="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V20" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T20" t="str">
+      <c r="W20" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U20" t="str">
+      <c r="X20" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V20" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W20" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="3:24">
       <c r="C21" t="str">
         <f>IF(B21&lt;&gt;"",VLOOKUP(B21,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2374,15 +2398,15 @@
         <v/>
       </c>
       <c r="O21" t="str">
+        <f>IF(A21&lt;&gt;"",IF(A21="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P21" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R21" t="str" cm="1">
@@ -2390,31 +2414,31 @@
         <v/>
       </c>
       <c r="S21" t="str">
+        <f>IF(E21&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <f>IF(AND(E21&lt;&gt;"",A21="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T21" t="str">
+      <c r="W21" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U21" t="str">
+      <c r="X21" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V21" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W21" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="3:24">
       <c r="C22" t="str">
         <f>IF(B22&lt;&gt;"",VLOOKUP(B22,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2439,15 +2463,15 @@
         <v/>
       </c>
       <c r="O22" t="str">
+        <f>IF(A22&lt;&gt;"",IF(A22="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R22" t="str" cm="1">
@@ -2455,31 +2479,31 @@
         <v/>
       </c>
       <c r="S22" t="str">
+        <f>IF(E22&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <f>IF(AND(E22&lt;&gt;"",A22="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V22" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T22" t="str">
+      <c r="W22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U22" t="str">
+      <c r="X22" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V22" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W22" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X22" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="3:24">
       <c r="C23" t="str">
         <f>IF(B23&lt;&gt;"",VLOOKUP(B23,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2504,15 +2528,15 @@
         <v/>
       </c>
       <c r="O23" t="str">
+        <f>IF(A23&lt;&gt;"",IF(A23="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q23" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R23" t="str" cm="1">
@@ -2520,31 +2544,31 @@
         <v/>
       </c>
       <c r="S23" t="str">
+        <f>IF(E23&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <f>IF(AND(E23&lt;&gt;"",A23="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T23" t="str">
+      <c r="W23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U23" t="str">
+      <c r="X23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V23" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W23" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X23" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="3:24">
       <c r="C24" t="str">
         <f>IF(B24&lt;&gt;"",VLOOKUP(B24,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2569,15 +2593,15 @@
         <v/>
       </c>
       <c r="O24" t="str">
+        <f>IF(A24&lt;&gt;"",IF(A24="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P24" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q24" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R24" t="str" cm="1">
@@ -2585,31 +2609,31 @@
         <v/>
       </c>
       <c r="S24" t="str">
+        <f>IF(E24&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <f>IF(AND(E24&lt;&gt;"",A24="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T24" t="str">
+      <c r="W24" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U24" t="str">
+      <c r="X24" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V24" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W24" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="3:24">
       <c r="C25" t="str">
         <f>IF(B25&lt;&gt;"",VLOOKUP(B25,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2634,15 +2658,15 @@
         <v/>
       </c>
       <c r="O25" t="str">
+        <f>IF(A25&lt;&gt;"",IF(A25="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P25" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P25" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q25" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R25" t="str" cm="1">
@@ -2650,31 +2674,31 @@
         <v/>
       </c>
       <c r="S25" t="str">
+        <f>IF(E25&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <f>IF(AND(E25&lt;&gt;"",A25="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V25" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T25" t="str">
+      <c r="W25" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U25" t="str">
+      <c r="X25" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V25" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X25" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="3:24">
       <c r="C26" t="str">
         <f>IF(B26&lt;&gt;"",VLOOKUP(B26,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2699,15 +2723,15 @@
         <v/>
       </c>
       <c r="O26" t="str">
+        <f>IF(A26&lt;&gt;"",IF(A26="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P26" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P26" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q26" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R26" t="str" cm="1">
@@ -2715,31 +2739,31 @@
         <v/>
       </c>
       <c r="S26" t="str">
+        <f>IF(E26&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <f>IF(AND(E26&lt;&gt;"",A26="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V26" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T26" t="str">
+      <c r="W26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U26" t="str">
+      <c r="X26" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V26" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W26" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X26" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="3:24">
       <c r="C27" t="str">
         <f>IF(B27&lt;&gt;"",VLOOKUP(B27,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2764,15 +2788,15 @@
         <v/>
       </c>
       <c r="O27" t="str">
+        <f>IF(A27&lt;&gt;"",IF(A27="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P27" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q27" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R27" t="str" cm="1">
@@ -2780,31 +2804,31 @@
         <v/>
       </c>
       <c r="S27" t="str">
+        <f>IF(E27&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <f>IF(AND(E27&lt;&gt;"",A27="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T27" t="str">
+      <c r="W27" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U27" t="str">
+      <c r="X27" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V27" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W27" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X27" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="3:24">
       <c r="C28" t="str">
         <f>IF(B28&lt;&gt;"",VLOOKUP(B28,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2829,15 +2853,15 @@
         <v/>
       </c>
       <c r="O28" t="str">
+        <f>IF(A28&lt;&gt;"",IF(A28="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P28" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P28" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q28" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R28" t="str" cm="1">
@@ -2845,31 +2869,31 @@
         <v/>
       </c>
       <c r="S28" t="str">
+        <f>IF(E28&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <f>IF(AND(E28&lt;&gt;"",A28="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V28" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T28" t="str">
+      <c r="W28" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U28" t="str">
+      <c r="X28" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V28" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W28" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X28" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="3:24">
       <c r="C29" t="str">
         <f>IF(B29&lt;&gt;"",VLOOKUP(B29,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2894,15 +2918,15 @@
         <v/>
       </c>
       <c r="O29" t="str">
+        <f>IF(A29&lt;&gt;"",IF(A29="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P29" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q29" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R29" t="str" cm="1">
@@ -2910,31 +2934,31 @@
         <v/>
       </c>
       <c r="S29" t="str">
+        <f>IF(E29&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <f>IF(AND(E29&lt;&gt;"",A29="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V29" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T29" t="str">
+      <c r="W29" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U29" t="str">
+      <c r="X29" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V29" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W29" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X29" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="3:24">
       <c r="C30" t="str">
         <f>IF(B30&lt;&gt;"",VLOOKUP(B30,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2959,15 +2983,15 @@
         <v/>
       </c>
       <c r="O30" t="str">
+        <f>IF(A30&lt;&gt;"",IF(A30="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P30" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P30" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q30" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R30" t="str" cm="1">
@@ -2975,31 +2999,31 @@
         <v/>
       </c>
       <c r="S30" t="str">
+        <f>IF(E30&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <f>IF(AND(E30&lt;&gt;"",A30="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U30" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V30" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T30" t="str">
+      <c r="W30" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U30" t="str">
+      <c r="X30" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V30" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W30" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X30" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="3:24">
       <c r="C31" t="str">
         <f>IF(B31&lt;&gt;"",VLOOKUP(B31,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3024,15 +3048,15 @@
         <v/>
       </c>
       <c r="O31" t="str">
+        <f>IF(A31&lt;&gt;"",IF(A31="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P31" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P31" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q31" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R31" t="str" cm="1">
@@ -3040,31 +3064,31 @@
         <v/>
       </c>
       <c r="S31" t="str">
+        <f>IF(E31&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <f>IF(AND(E31&lt;&gt;"",A31="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V31" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T31" t="str">
+      <c r="W31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U31" t="str">
+      <c r="X31" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V31" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W31" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X31" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="3:24">
       <c r="C32" t="str">
         <f>IF(B32&lt;&gt;"",VLOOKUP(B32,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3089,15 +3113,15 @@
         <v/>
       </c>
       <c r="O32" t="str">
+        <f>IF(A32&lt;&gt;"",IF(A32="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P32" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P32" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q32" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R32" t="str" cm="1">
@@ -3105,31 +3129,31 @@
         <v/>
       </c>
       <c r="S32" t="str">
+        <f>IF(E32&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <f>IF(AND(E32&lt;&gt;"",A32="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U32" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V32" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T32" t="str">
+      <c r="W32" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U32" t="str">
+      <c r="X32" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V32" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W32" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X32" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="3:24">
       <c r="C33" t="str">
         <f>IF(B33&lt;&gt;"",VLOOKUP(B33,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3154,15 +3178,15 @@
         <v/>
       </c>
       <c r="O33" t="str">
+        <f>IF(A33&lt;&gt;"",IF(A33="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P33" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P33" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q33" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R33" t="str" cm="1">
@@ -3170,31 +3194,31 @@
         <v/>
       </c>
       <c r="S33" t="str">
+        <f>IF(E33&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T33" t="str">
+        <f>IF(AND(E33&lt;&gt;"",A33="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U33" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T33" t="str">
+      <c r="W33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U33" t="str">
+      <c r="X33" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V33" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W33" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X33" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="3:24">
       <c r="C34" t="str">
         <f>IF(B34&lt;&gt;"",VLOOKUP(B34,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3219,15 +3243,15 @@
         <v/>
       </c>
       <c r="O34" t="str">
+        <f>IF(A34&lt;&gt;"",IF(A34="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P34" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P34" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q34" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R34" t="str" cm="1">
@@ -3235,31 +3259,31 @@
         <v/>
       </c>
       <c r="S34" t="str">
+        <f>IF(E34&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T34" t="str">
+        <f>IF(AND(E34&lt;&gt;"",A34="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U34" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V34" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T34" t="str">
+      <c r="W34" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U34" t="str">
+      <c r="X34" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V34" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W34" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X34" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="3:24">
       <c r="C35" t="str">
         <f>IF(B35&lt;&gt;"",VLOOKUP(B35,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3284,15 +3308,15 @@
         <v/>
       </c>
       <c r="O35" t="str">
+        <f>IF(A35&lt;&gt;"",IF(A35="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P35" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P35" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R35" t="str" cm="1">
@@ -3300,31 +3324,31 @@
         <v/>
       </c>
       <c r="S35" t="str">
+        <f>IF(E35&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T35" t="str">
+        <f>IF(AND(E35&lt;&gt;"",A35="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U35" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V35" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T35" t="str">
+      <c r="W35" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U35" t="str">
+      <c r="X35" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V35" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W35" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X35" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="3:24">
       <c r="C36" t="str">
         <f>IF(B36&lt;&gt;"",VLOOKUP(B36,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3349,15 +3373,15 @@
         <v/>
       </c>
       <c r="O36" t="str">
+        <f>IF(A36&lt;&gt;"",IF(A36="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P36" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P36" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q36" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R36" t="str" cm="1">
@@ -3365,31 +3389,31 @@
         <v/>
       </c>
       <c r="S36" t="str">
+        <f>IF(E36&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T36" t="str">
+        <f>IF(AND(E36&lt;&gt;"",A36="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U36" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V36" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T36" t="str">
+      <c r="W36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U36" t="str">
+      <c r="X36" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V36" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W36" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X36" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="3:24">
       <c r="C37" t="str">
         <f>IF(B37&lt;&gt;"",VLOOKUP(B37,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3414,15 +3438,15 @@
         <v/>
       </c>
       <c r="O37" t="str">
+        <f>IF(A37&lt;&gt;"",IF(A37="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P37" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P37" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q37" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R37" t="str" cm="1">
@@ -3430,31 +3454,31 @@
         <v/>
       </c>
       <c r="S37" t="str">
+        <f>IF(E37&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <f>IF(AND(E37&lt;&gt;"",A37="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U37" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V37" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T37" t="str">
+      <c r="W37" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U37" t="str">
+      <c r="X37" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V37" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W37" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X37" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="3:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="3:24">
       <c r="C38" t="str">
         <f>IF(B38&lt;&gt;"",VLOOKUP(B38,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3479,15 +3503,15 @@
         <v/>
       </c>
       <c r="O38" t="str">
+        <f>IF(A38&lt;&gt;"",IF(A38="Entrée",0.366,0.228),"")</f>
+        <v/>
+      </c>
+      <c r="P38" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P38" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
       <c r="Q38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R38" t="str" cm="1">
@@ -3495,27 +3519,27 @@
         <v/>
       </c>
       <c r="S38" t="str">
+        <f>IF(E38&lt;&gt;"",0,"")</f>
+        <v/>
+      </c>
+      <c r="T38" t="str">
+        <f>IF(AND(E38&lt;&gt;"",A38="Entrée"),65,"")</f>
+        <v/>
+      </c>
+      <c r="U38" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="V38" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T38" t="str">
+      <c r="W38" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="U38" t="str">
+      <c r="X38" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="V38" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W38" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X38" t="str">
-        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -3543,16 +3567,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED48872-91E8-49A7-BF70-883F96B227DE}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" customWidth="1"/>
-    <col min="4" max="4" width="26.453125" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="18.75">
       <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
@@ -3569,7 +3593,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
@@ -3586,7 +3610,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
         <v>25</v>
       </c>
@@ -3603,24 +3627,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="8">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C4" s="12">
+        <v>18.5</v>
+      </c>
+      <c r="D4" s="12">
+        <v>5.18</v>
+      </c>
+      <c r="E4" s="12">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
         <v>34</v>
       </c>
@@ -3637,41 +3661,41 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="8">
-        <v>20</v>
-      </c>
-      <c r="D6" s="8">
-        <v>20</v>
-      </c>
-      <c r="E6" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C6" s="13">
+        <v>18.7</v>
+      </c>
+      <c r="D6" s="13">
+        <v>5.45</v>
+      </c>
+      <c r="E6" s="13">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C7" s="13">
+        <v>17.8</v>
+      </c>
+      <c r="D7" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
@@ -3688,7 +3712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
@@ -3705,24 +3729,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" s="7" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C10" s="13">
+        <v>14.2</v>
+      </c>
+      <c r="D10" s="13">
+        <v>4.57</v>
+      </c>
+      <c r="E10" s="13">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -3739,7 +3763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -3747,7 +3771,7 @@
         <v>44</v>
       </c>
       <c r="C12" s="8">
-        <v>0</v>
+        <v>18.77</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>
@@ -3756,7 +3780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -3773,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
@@ -3809,13 +3833,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB195B26-F7E2-4470-95CE-93C18E346372}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" customWidth="1"/>
-    <col min="2" max="2" width="74.453125" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="74.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>47</v>
       </c>
@@ -3823,7 +3847,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -3835,7 +3859,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -3843,7 +3867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>51</v>
       </c>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marjory/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.vaillant.GPHUB\Documents\GPMLM\SDDEP\Stage\Stage 2026\Travail\Poissons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB6B10CC-1BE4-6D4A-B3CC-093320CD215E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D05599-6A7E-4B60-8032-B15BB014C145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9240" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Declaration" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="54">
   <si>
     <t xml:space="preserve">Mouvement </t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>Immeuble Frigodom - 1ère étage, ZIP de la Pointe des Grives, 97200, FORT-DE-FRANCE</t>
+  </si>
+  <si>
+    <t>EL SAN JUANERO</t>
   </si>
 </sst>
 </file>
@@ -271,7 +274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -398,11 +401,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -419,6 +448,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,8 +742,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EF6C966-3BDB-42E8-860E-1440AB71A0E5}" name="Tableau13" displayName="Tableau13" ref="A1:E14" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E14" xr:uid="{5EF6C966-3BDB-42E8-860E-1440AB71A0E5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EF6C966-3BDB-42E8-860E-1440AB71A0E5}" name="Tableau13" displayName="Tableau13" ref="A1:E15" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E15" xr:uid="{5EF6C966-3BDB-42E8-860E-1440AB71A0E5}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FEF8928F-5632-49AC-8AA4-1B2179228900}" name="Compagnie " dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{04650E0C-BE4E-4678-A0DD-1DFA856CD2D2}" name="Nom du Navire " dataDxfId="3"/>
@@ -1032,34 +1064,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" customWidth="1"/>
-    <col min="3" max="3" width="48.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" customWidth="1"/>
+    <col min="3" max="3" width="48.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="18.6328125" customWidth="1"/>
+    <col min="6" max="6" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.6328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="32" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" customWidth="1"/>
     <col min="19" max="19" width="28" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.1640625" customWidth="1"/>
+    <col min="20" max="20" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,7 +1165,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1211,7 +1243,7 @@
         <v>81.84</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C3" t="str">
         <f>IF(B3&lt;&gt;"",VLOOKUP(B3,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1273,7 +1305,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C4" t="str">
         <f>IF(B4&lt;&gt;"",VLOOKUP(B4,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1338,7 +1370,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C5" t="str">
         <f>IF(B5&lt;&gt;"",VLOOKUP(B5,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1403,7 +1435,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C6" t="str">
         <f>IF(B6&lt;&gt;"",VLOOKUP(B6,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1468,7 +1500,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C7" t="str">
         <f>IF(B7&lt;&gt;"",VLOOKUP(B7,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1533,7 +1565,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C8" t="str">
         <f>IF(B8&lt;&gt;"",VLOOKUP(B8,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1598,7 +1630,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C9" t="str">
         <f>IF(B9&lt;&gt;"",VLOOKUP(B9,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1663,7 +1695,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C10" t="str">
         <f>IF(B10&lt;&gt;"",VLOOKUP(B10,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1728,7 +1760,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C11" t="str">
         <f>IF(B11&lt;&gt;"",VLOOKUP(B11,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1793,7 +1825,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C12" t="str">
         <f>IF(B12&lt;&gt;"",VLOOKUP(B12,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1858,7 +1890,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C13" t="str">
         <f>IF(B13&lt;&gt;"",VLOOKUP(B13,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1923,7 +1955,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C14" t="str">
         <f>IF(B14&lt;&gt;"",VLOOKUP(B14,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1988,7 +2020,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C15" t="str">
         <f>IF(B15&lt;&gt;"",VLOOKUP(B15,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2053,7 +2085,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C16" t="str">
         <f>IF(B16&lt;&gt;"",VLOOKUP(B16,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2118,7 +2150,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C17" t="str">
         <f>IF(B17&lt;&gt;"",VLOOKUP(B17,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2183,7 +2215,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C18" t="str">
         <f>IF(B18&lt;&gt;"",VLOOKUP(B18,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2248,7 +2280,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C19" t="str">
         <f>IF(B19&lt;&gt;"",VLOOKUP(B19,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2313,7 +2345,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C20" t="str">
         <f>IF(B20&lt;&gt;"",VLOOKUP(B20,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2378,7 +2410,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C21" t="str">
         <f>IF(B21&lt;&gt;"",VLOOKUP(B21,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2443,7 +2475,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C22" t="str">
         <f>IF(B22&lt;&gt;"",VLOOKUP(B22,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2508,7 +2540,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C23" t="str">
         <f>IF(B23&lt;&gt;"",VLOOKUP(B23,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2573,7 +2605,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C24" t="str">
         <f>IF(B24&lt;&gt;"",VLOOKUP(B24,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2638,7 +2670,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C25" t="str">
         <f>IF(B25&lt;&gt;"",VLOOKUP(B25,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2703,7 +2735,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C26" t="str">
         <f>IF(B26&lt;&gt;"",VLOOKUP(B26,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2768,7 +2800,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C27" t="str">
         <f>IF(B27&lt;&gt;"",VLOOKUP(B27,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2833,7 +2865,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C28" t="str">
         <f>IF(B28&lt;&gt;"",VLOOKUP(B28,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2898,7 +2930,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C29" t="str">
         <f>IF(B29&lt;&gt;"",VLOOKUP(B29,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2963,7 +2995,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C30" t="str">
         <f>IF(B30&lt;&gt;"",VLOOKUP(B30,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3028,7 +3060,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C31" t="str">
         <f>IF(B31&lt;&gt;"",VLOOKUP(B31,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3093,7 +3125,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C32" t="str">
         <f>IF(B32&lt;&gt;"",VLOOKUP(B32,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3158,7 +3190,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C33" t="str">
         <f>IF(B33&lt;&gt;"",VLOOKUP(B33,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3223,7 +3255,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C34" t="str">
         <f>IF(B34&lt;&gt;"",VLOOKUP(B34,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3288,7 +3320,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C35" t="str">
         <f>IF(B35&lt;&gt;"",VLOOKUP(B35,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3353,7 +3385,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C36" t="str">
         <f>IF(B36&lt;&gt;"",VLOOKUP(B36,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3418,7 +3450,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C37" t="str">
         <f>IF(B37&lt;&gt;"",VLOOKUP(B37,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3483,7 +3515,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C38" t="str">
         <f>IF(B38&lt;&gt;"",VLOOKUP(B38,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3571,17 +3603,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED48872-91E8-49A7-BF70-883F96B227DE}">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="26.5" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.6328125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="3" max="3" width="27.453125" customWidth="1"/>
+    <col min="4" max="4" width="26.453125" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
@@ -3598,7 +3630,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
@@ -3615,7 +3647,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>25</v>
       </c>
@@ -3632,7 +3664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -3649,7 +3681,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>34</v>
       </c>
@@ -3666,7 +3698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>34</v>
       </c>
@@ -3683,7 +3715,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
@@ -3700,7 +3732,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
@@ -3717,7 +3749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
@@ -3734,7 +3766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>41</v>
       </c>
@@ -3751,7 +3783,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -3768,7 +3800,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -3785,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -3802,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
@@ -3819,9 +3851,24 @@
         <v>2</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="14">
+        <v>15</v>
+      </c>
+      <c r="D15" s="15">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="E15" s="16">
+        <v>1.85</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A14" xr:uid="{E2910900-9C30-4A18-9496-476E3FB8CC0C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{E2910900-9C30-4A18-9496-476E3FB8CC0C}">
       <formula1>"DSK Fish,Poissonnerie Bapte,Delta Transit"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B14" xr:uid="{9CBFDF41-04DC-4A2C-BFA5-AF229712E91E}">
@@ -3838,13 +3885,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB195B26-F7E2-4470-95CE-93C18E346372}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="2" max="2" width="74.5" customWidth="1"/>
+    <col min="1" max="1" width="18.36328125" customWidth="1"/>
+    <col min="2" max="2" width="74.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>47</v>
       </c>
@@ -3852,7 +3899,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -3864,7 +3911,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -3872,7 +3919,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>51</v>
       </c>
